--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>17/10/2026 a las 17:56:55</t>
+    <t>17/10/2026 a las 18:30:57</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>17/10/2026 a las 18:30:57</t>
+    <t>17/10/2026 a las 19:31:00</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>17/10/2026 a las 19:31:00</t>
+    <t>17/10/2026 a las 20:30:54</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>17/10/2026 a las 20:30:54</t>
+    <t>18/10/2026 a las 08:30:59</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -12650,7 +12650,7 @@
         <v>45</v>
       </c>
       <c r="W6" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X6" s="4" t="s">
         <v>46</v>
@@ -12724,7 +12724,7 @@
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
       <c r="W7" s="4">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="X7" s="4" t="s">
         <v>46</v>
@@ -12804,7 +12804,7 @@
         <v>66</v>
       </c>
       <c r="W8" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X8" s="4" t="s">
         <v>46</v>
@@ -12882,7 +12882,7 @@
         <v>74</v>
       </c>
       <c r="W9" s="4">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X9" s="4" t="s">
         <v>46</v>
@@ -12960,7 +12960,7 @@
         <v>74</v>
       </c>
       <c r="W10" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X10" s="4" t="s">
         <v>46</v>
@@ -13038,7 +13038,7 @@
         <v>74</v>
       </c>
       <c r="W11" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X11" s="4" t="s">
         <v>46</v>
@@ -13116,7 +13116,7 @@
         <v>93</v>
       </c>
       <c r="W12" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X12" s="4" t="s">
         <v>46</v>
@@ -13196,7 +13196,7 @@
         <v>98</v>
       </c>
       <c r="W13" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X13" s="4" t="s">
         <v>46</v>
@@ -13270,7 +13270,7 @@
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
       <c r="W14" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X14" s="4" t="s">
         <v>46</v>
@@ -13346,7 +13346,7 @@
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
       <c r="W15" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X15" s="4" t="s">
         <v>46</v>
@@ -13424,7 +13424,7 @@
         <v>116</v>
       </c>
       <c r="W16" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X16" s="4" t="s">
         <v>46</v>
@@ -13504,7 +13504,7 @@
         <v>123</v>
       </c>
       <c r="W17" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X17" s="4" t="s">
         <v>46</v>
@@ -13582,7 +13582,7 @@
         <v>130</v>
       </c>
       <c r="W18" s="4">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X18" s="4" t="s">
         <v>46</v>
@@ -13652,7 +13652,7 @@
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X19" s="4" t="s">
         <v>46</v>
@@ -13726,7 +13726,7 @@
         <v>141</v>
       </c>
       <c r="W20" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X20" s="4" t="s">
         <v>46</v>
@@ -13800,7 +13800,7 @@
         <v>146</v>
       </c>
       <c r="W21" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X21" s="4" t="s">
         <v>46</v>
@@ -13868,7 +13868,7 @@
       <c r="U22" s="4"/>
       <c r="V22" s="4"/>
       <c r="W22" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X22" s="4" t="s">
         <v>46</v>
@@ -13948,7 +13948,7 @@
         <v>74</v>
       </c>
       <c r="W23" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X23" s="4" t="s">
         <v>46</v>
@@ -14024,7 +14024,7 @@
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
       <c r="W24" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X24" s="4" t="s">
         <v>46</v>
@@ -14100,7 +14100,7 @@
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
       <c r="W25" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X25" s="4" t="s">
         <v>46</v>
@@ -14178,7 +14178,7 @@
         <v>141</v>
       </c>
       <c r="W26" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X26" s="4" t="s">
         <v>46</v>
@@ -14254,7 +14254,7 @@
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
       <c r="W27" s="4">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X27" s="4" t="s">
         <v>46</v>
@@ -14330,7 +14330,7 @@
         <v>179</v>
       </c>
       <c r="W28" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X28" s="4" t="s">
         <v>46</v>
@@ -14406,7 +14406,7 @@
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
       <c r="W29" s="4">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="X29" s="4" t="s">
         <v>46</v>
@@ -14486,7 +14486,7 @@
         <v>130</v>
       </c>
       <c r="W30" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X30" s="4" t="s">
         <v>46</v>
@@ -14560,7 +14560,7 @@
         <v>66</v>
       </c>
       <c r="W31" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X31" s="4" t="s">
         <v>46</v>
@@ -14628,7 +14628,7 @@
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
       <c r="W32" s="4">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="X32" s="4" t="s">
         <v>46</v>
@@ -14704,7 +14704,7 @@
         <v>201</v>
       </c>
       <c r="W33" s="4">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X33" s="4" t="s">
         <v>46</v>
@@ -14784,7 +14784,7 @@
         <v>206</v>
       </c>
       <c r="W34" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X34" s="4" t="s">
         <v>46</v>
@@ -14860,7 +14860,7 @@
         <v>212</v>
       </c>
       <c r="W35" s="4">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X35" s="4" t="s">
         <v>46</v>
@@ -14936,7 +14936,7 @@
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
       <c r="W36" s="4">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="X36" s="4" t="s">
         <v>46</v>
@@ -15016,7 +15016,7 @@
         <v>224</v>
       </c>
       <c r="W37" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X37" s="4" t="s">
         <v>46</v>
@@ -15096,7 +15096,7 @@
         <v>45</v>
       </c>
       <c r="W38" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X38" s="4" t="s">
         <v>46</v>
@@ -15174,7 +15174,7 @@
         <v>237</v>
       </c>
       <c r="W39" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X39" s="4" t="s">
         <v>46</v>
@@ -15254,7 +15254,7 @@
         <v>45</v>
       </c>
       <c r="W40" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X40" s="4" t="s">
         <v>46</v>
@@ -15332,7 +15332,7 @@
         <v>245</v>
       </c>
       <c r="W41" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X41" s="4" t="s">
         <v>46</v>
@@ -15406,7 +15406,7 @@
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
       <c r="W42" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X42" s="4" t="s">
         <v>46</v>
@@ -15484,7 +15484,7 @@
         <v>74</v>
       </c>
       <c r="W43" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X43" s="4" t="s">
         <v>46</v>
@@ -15562,7 +15562,7 @@
         <v>130</v>
       </c>
       <c r="W44" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X44" s="4" t="s">
         <v>46</v>
@@ -15640,7 +15640,7 @@
         <v>74</v>
       </c>
       <c r="W45" s="4">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="X45" s="4" t="s">
         <v>46</v>
@@ -15716,7 +15716,7 @@
       <c r="U46" s="4"/>
       <c r="V46" s="4"/>
       <c r="W46" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X46" s="4" t="s">
         <v>46</v>
@@ -15796,7 +15796,7 @@
         <v>74</v>
       </c>
       <c r="W47" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X47" s="4" t="s">
         <v>46</v>
@@ -15876,7 +15876,7 @@
         <v>237</v>
       </c>
       <c r="W48" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X48" s="4" t="s">
         <v>46</v>
@@ -15952,7 +15952,7 @@
       <c r="U49" s="4"/>
       <c r="V49" s="4"/>
       <c r="W49" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X49" s="4" t="s">
         <v>46</v>
@@ -16030,7 +16030,7 @@
         <v>237</v>
       </c>
       <c r="W50" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X50" s="4" t="s">
         <v>46</v>
@@ -16106,7 +16106,7 @@
       <c r="U51" s="4"/>
       <c r="V51" s="4"/>
       <c r="W51" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X51" s="4" t="s">
         <v>46</v>
@@ -16186,7 +16186,7 @@
         <v>74</v>
       </c>
       <c r="W52" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X52" s="4" t="s">
         <v>46</v>
@@ -16264,7 +16264,7 @@
         <v>237</v>
       </c>
       <c r="W53" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X53" s="4" t="s">
         <v>46</v>
@@ -16342,7 +16342,7 @@
         <v>237</v>
       </c>
       <c r="W54" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X54" s="4" t="s">
         <v>46</v>
@@ -16420,7 +16420,7 @@
         <v>237</v>
       </c>
       <c r="W55" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X55" s="4" t="s">
         <v>46</v>
@@ -16498,7 +16498,7 @@
         <v>237</v>
       </c>
       <c r="W56" s="4">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X56" s="4" t="s">
         <v>46</v>
@@ -16568,7 +16568,7 @@
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
       <c r="W57" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X57" s="4" t="s">
         <v>46</v>
@@ -16640,7 +16640,7 @@
         <v>321</v>
       </c>
       <c r="W58" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X58" s="4" t="s">
         <v>322</v>
@@ -16720,7 +16720,7 @@
         <v>328</v>
       </c>
       <c r="W59" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X59" s="4" t="s">
         <v>46</v>
@@ -16798,7 +16798,7 @@
         <v>206</v>
       </c>
       <c r="W60" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X60" s="4" t="s">
         <v>46</v>
@@ -16878,7 +16878,7 @@
         <v>340</v>
       </c>
       <c r="W61" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X61" s="4" t="s">
         <v>46</v>
@@ -16954,7 +16954,7 @@
       <c r="U62" s="4"/>
       <c r="V62" s="4"/>
       <c r="W62" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X62" s="4" t="s">
         <v>46</v>
@@ -17034,7 +17034,7 @@
         <v>350</v>
       </c>
       <c r="W63" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X63" s="4" t="s">
         <v>46</v>
@@ -17114,7 +17114,7 @@
         <v>356</v>
       </c>
       <c r="W64" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X64" s="4" t="s">
         <v>46</v>
@@ -17194,7 +17194,7 @@
         <v>340</v>
       </c>
       <c r="W65" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X65" s="4" t="s">
         <v>46</v>
@@ -17274,7 +17274,7 @@
         <v>245</v>
       </c>
       <c r="W66" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X66" s="4" t="s">
         <v>46</v>
@@ -17348,7 +17348,7 @@
         <v>206</v>
       </c>
       <c r="W67" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X67" s="4" t="s">
         <v>46</v>
@@ -17428,7 +17428,7 @@
         <v>340</v>
       </c>
       <c r="W68" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X68" s="4" t="s">
         <v>46</v>
@@ -17502,7 +17502,7 @@
         <v>340</v>
       </c>
       <c r="W69" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X69" s="4" t="s">
         <v>46</v>
@@ -17582,7 +17582,7 @@
         <v>350</v>
       </c>
       <c r="W70" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X70" s="4" t="s">
         <v>46</v>
@@ -17662,7 +17662,7 @@
         <v>123</v>
       </c>
       <c r="W71" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X71" s="4" t="s">
         <v>46</v>
@@ -17742,7 +17742,7 @@
         <v>237</v>
       </c>
       <c r="W72" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X72" s="4" t="s">
         <v>322</v>
@@ -17818,7 +17818,7 @@
       <c r="U73" s="4"/>
       <c r="V73" s="4"/>
       <c r="W73" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X73" s="4" t="s">
         <v>46</v>
@@ -17896,7 +17896,7 @@
         <v>45</v>
       </c>
       <c r="W74" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X74" s="4" t="s">
         <v>46</v>
@@ -17976,7 +17976,7 @@
         <v>245</v>
       </c>
       <c r="W75" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X75" s="4" t="s">
         <v>46</v>
@@ -18056,7 +18056,7 @@
         <v>245</v>
       </c>
       <c r="W76" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X76" s="4" t="s">
         <v>46</v>
@@ -18134,7 +18134,7 @@
         <v>350</v>
       </c>
       <c r="W77" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X77" s="4" t="s">
         <v>46</v>
@@ -18204,7 +18204,7 @@
       <c r="U78" s="4"/>
       <c r="V78" s="4"/>
       <c r="W78" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X78" s="4" t="s">
         <v>46</v>
@@ -18280,7 +18280,7 @@
       <c r="U79" s="4"/>
       <c r="V79" s="4"/>
       <c r="W79" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="X79" s="4" t="s">
         <v>46</v>
@@ -18358,7 +18358,7 @@
         <v>130</v>
       </c>
       <c r="W80" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X80" s="4" t="s">
         <v>46</v>
@@ -18438,7 +18438,7 @@
         <v>130</v>
       </c>
       <c r="W81" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X81" s="4" t="s">
         <v>46</v>
@@ -18514,7 +18514,7 @@
       <c r="U82" s="4"/>
       <c r="V82" s="4"/>
       <c r="W82" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X82" s="4" t="s">
         <v>46</v>
@@ -18594,7 +18594,7 @@
         <v>340</v>
       </c>
       <c r="W83" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X83" s="4" t="s">
         <v>46</v>
@@ -18664,7 +18664,7 @@
       <c r="U84" s="4"/>
       <c r="V84" s="4"/>
       <c r="W84" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X84" s="4" t="s">
         <v>46</v>
@@ -18742,7 +18742,7 @@
         <v>467</v>
       </c>
       <c r="W85" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X85" s="4" t="s">
         <v>46</v>
@@ -18822,7 +18822,7 @@
         <v>74</v>
       </c>
       <c r="W86" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X86" s="4" t="s">
         <v>46</v>
@@ -18900,7 +18900,7 @@
         <v>130</v>
       </c>
       <c r="W87" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X87" s="4" t="s">
         <v>46</v>
@@ -18978,7 +18978,7 @@
         <v>350</v>
       </c>
       <c r="W88" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X88" s="4" t="s">
         <v>46</v>
@@ -19058,7 +19058,7 @@
         <v>237</v>
       </c>
       <c r="W89" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X89" s="4" t="s">
         <v>46</v>
@@ -19128,7 +19128,7 @@
       <c r="U90" s="4"/>
       <c r="V90" s="4"/>
       <c r="W90" s="4">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="X90" s="4" t="s">
         <v>46</v>
@@ -19198,7 +19198,7 @@
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
       <c r="W91" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X91" s="4" t="s">
         <v>46</v>
@@ -19270,7 +19270,7 @@
         <v>74</v>
       </c>
       <c r="W92" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X92" s="4" t="s">
         <v>46</v>
@@ -19344,7 +19344,7 @@
         <v>212</v>
       </c>
       <c r="W93" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X93" s="4" t="s">
         <v>46</v>
@@ -19414,7 +19414,7 @@
       <c r="U94" s="4"/>
       <c r="V94" s="4"/>
       <c r="W94" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X94" s="4" t="s">
         <v>46</v>
@@ -19482,7 +19482,7 @@
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
       <c r="W95" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X95" s="4" t="s">
         <v>46</v>
@@ -19552,7 +19552,7 @@
       <c r="U96" s="4"/>
       <c r="V96" s="4"/>
       <c r="W96" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X96" s="4" t="s">
         <v>46</v>
@@ -19622,7 +19622,7 @@
       <c r="U97" s="4"/>
       <c r="V97" s="4"/>
       <c r="W97" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X97" s="4" t="s">
         <v>46</v>
@@ -19692,7 +19692,7 @@
       <c r="U98" s="4"/>
       <c r="V98" s="4"/>
       <c r="W98" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X98" s="4" t="s">
         <v>46</v>
@@ -19762,7 +19762,7 @@
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
       <c r="W99" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X99" s="4" t="s">
         <v>46</v>
@@ -19832,7 +19832,7 @@
       <c r="U100" s="4"/>
       <c r="V100" s="4"/>
       <c r="W100" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X100" s="4" t="s">
         <v>46</v>
@@ -19900,7 +19900,7 @@
       <c r="U101" s="4"/>
       <c r="V101" s="4"/>
       <c r="W101" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X101" s="4" t="s">
         <v>46</v>
@@ -19976,7 +19976,7 @@
       <c r="U102" s="4"/>
       <c r="V102" s="4"/>
       <c r="W102" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X102" s="4" t="s">
         <v>46</v>
@@ -20056,7 +20056,7 @@
         <v>212</v>
       </c>
       <c r="W103" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X103" s="4" t="s">
         <v>46</v>
@@ -20130,7 +20130,7 @@
         <v>130</v>
       </c>
       <c r="W104" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X104" s="4" t="s">
         <v>46</v>
@@ -20206,7 +20206,7 @@
       <c r="U105" s="4"/>
       <c r="V105" s="4"/>
       <c r="W105" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X105" s="4" t="s">
         <v>46</v>
@@ -20282,7 +20282,7 @@
       <c r="U106" s="4"/>
       <c r="V106" s="4"/>
       <c r="W106" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X106" s="4" t="s">
         <v>46</v>
@@ -20352,7 +20352,7 @@
       <c r="U107" s="4"/>
       <c r="V107" s="4"/>
       <c r="W107" s="4">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X107" s="4" t="s">
         <v>46</v>
@@ -20424,7 +20424,7 @@
         <v>340</v>
       </c>
       <c r="W108" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X108" s="4" t="s">
         <v>46</v>
@@ -20496,7 +20496,7 @@
         <v>340</v>
       </c>
       <c r="W109" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X109" s="4" t="s">
         <v>46</v>
@@ -20564,7 +20564,7 @@
       <c r="U110" s="4"/>
       <c r="V110" s="4"/>
       <c r="W110" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X110" s="4" t="s">
         <v>46</v>
@@ -20638,7 +20638,7 @@
         <v>557</v>
       </c>
       <c r="W111" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X111" s="4" t="s">
         <v>46</v>
@@ -20712,7 +20712,7 @@
         <v>340</v>
       </c>
       <c r="W112" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X112" s="4" t="s">
         <v>46</v>
@@ -20780,7 +20780,7 @@
       <c r="U113" s="4"/>
       <c r="V113" s="4"/>
       <c r="W113" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X113" s="4" t="s">
         <v>46</v>
@@ -20852,7 +20852,7 @@
       <c r="U114" s="4"/>
       <c r="V114" s="4"/>
       <c r="W114" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X114" s="4" t="s">
         <v>46</v>
@@ -20928,7 +20928,7 @@
       <c r="U115" s="4"/>
       <c r="V115" s="4"/>
       <c r="W115" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X115" s="4" t="s">
         <v>46</v>
@@ -21008,7 +21008,7 @@
         <v>130</v>
       </c>
       <c r="W116" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X116" s="4" t="s">
         <v>46</v>
@@ -21082,7 +21082,7 @@
         <v>340</v>
       </c>
       <c r="W117" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="X117" s="4" t="s">
         <v>46</v>
@@ -21152,7 +21152,7 @@
       <c r="U118" s="4"/>
       <c r="V118" s="4"/>
       <c r="W118" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X118" s="4" t="s">
         <v>46</v>
@@ -21220,7 +21220,7 @@
       <c r="U119" s="4"/>
       <c r="V119" s="4"/>
       <c r="W119" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X119" s="4" t="s">
         <v>46</v>
@@ -21290,7 +21290,7 @@
       <c r="U120" s="4"/>
       <c r="V120" s="4"/>
       <c r="W120" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X120" s="4" t="s">
         <v>46</v>
@@ -21360,7 +21360,7 @@
       <c r="U121" s="4"/>
       <c r="V121" s="4"/>
       <c r="W121" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X121" s="4" t="s">
         <v>46</v>
@@ -21430,7 +21430,7 @@
       <c r="U122" s="4"/>
       <c r="V122" s="4"/>
       <c r="W122" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X122" s="4" t="s">
         <v>46</v>
@@ -21504,7 +21504,7 @@
         <v>340</v>
       </c>
       <c r="W123" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X123" s="4" t="s">
         <v>46</v>
@@ -21578,7 +21578,7 @@
         <v>602</v>
       </c>
       <c r="W124" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X124" s="4" t="s">
         <v>46</v>
@@ -21650,7 +21650,7 @@
         <v>340</v>
       </c>
       <c r="W125" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X125" s="4" t="s">
         <v>46</v>
@@ -21720,7 +21720,7 @@
       <c r="U126" s="4"/>
       <c r="V126" s="4"/>
       <c r="W126" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X126" s="4" t="s">
         <v>46</v>
@@ -21788,7 +21788,7 @@
       <c r="U127" s="4"/>
       <c r="V127" s="4"/>
       <c r="W127" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X127" s="4" t="s">
         <v>46</v>
@@ -21864,7 +21864,7 @@
       <c r="U128" s="4"/>
       <c r="V128" s="4"/>
       <c r="W128" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X128" s="4" t="s">
         <v>46</v>
@@ -21938,7 +21938,7 @@
       <c r="U129" s="4"/>
       <c r="V129" s="4"/>
       <c r="W129" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X129" s="4" t="s">
         <v>46</v>
@@ -22016,7 +22016,7 @@
         <v>45</v>
       </c>
       <c r="W130" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X130" s="4" t="s">
         <v>46</v>
@@ -22092,7 +22092,7 @@
       <c r="U131" s="4"/>
       <c r="V131" s="4"/>
       <c r="W131" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X131" s="4" t="s">
         <v>46</v>
@@ -22170,7 +22170,7 @@
         <v>340</v>
       </c>
       <c r="W132" s="4">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X132" s="4" t="s">
         <v>46</v>
@@ -22246,7 +22246,7 @@
       <c r="U133" s="4"/>
       <c r="V133" s="4"/>
       <c r="W133" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X133" s="4" t="s">
         <v>46</v>
@@ -22326,7 +22326,7 @@
         <v>640</v>
       </c>
       <c r="W134" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X134" s="4" t="s">
         <v>46</v>
@@ -22400,7 +22400,7 @@
       <c r="U135" s="4"/>
       <c r="V135" s="4"/>
       <c r="W135" s="4">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="X135" s="4" t="s">
         <v>46</v>
@@ -22474,7 +22474,7 @@
         <v>130</v>
       </c>
       <c r="W136" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X136" s="4" t="s">
         <v>46</v>
@@ -22548,7 +22548,7 @@
         <v>130</v>
       </c>
       <c r="W137" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X137" s="4" t="s">
         <v>46</v>
@@ -22624,7 +22624,7 @@
       <c r="U138" s="4"/>
       <c r="V138" s="4"/>
       <c r="W138" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X138" s="4" t="s">
         <v>46</v>
@@ -22700,7 +22700,7 @@
       <c r="U139" s="4"/>
       <c r="V139" s="4"/>
       <c r="W139" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X139" s="4" t="s">
         <v>46</v>
@@ -22778,7 +22778,7 @@
         <v>665</v>
       </c>
       <c r="W140" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X140" s="4" t="s">
         <v>46</v>
@@ -22854,7 +22854,7 @@
       <c r="U141" s="4"/>
       <c r="V141" s="4"/>
       <c r="W141" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X141" s="4" t="s">
         <v>46</v>
@@ -22928,7 +22928,7 @@
       <c r="U142" s="4"/>
       <c r="V142" s="4"/>
       <c r="W142" s="4">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="X142" s="4" t="s">
         <v>46</v>
@@ -23004,7 +23004,7 @@
       <c r="U143" s="4"/>
       <c r="V143" s="4"/>
       <c r="W143" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X143" s="4" t="s">
         <v>46</v>
@@ -23078,7 +23078,7 @@
       <c r="U144" s="4"/>
       <c r="V144" s="4"/>
       <c r="W144" s="4">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X144" s="4" t="s">
         <v>46</v>
@@ -23146,7 +23146,7 @@
       <c r="U145" s="4"/>
       <c r="V145" s="4"/>
       <c r="W145" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X145" s="4" t="s">
         <v>46</v>
@@ -23224,7 +23224,7 @@
         <v>206</v>
       </c>
       <c r="W146" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X146" s="4" t="s">
         <v>46</v>
@@ -23300,7 +23300,7 @@
       <c r="U147" s="4"/>
       <c r="V147" s="4"/>
       <c r="W147" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X147" s="4" t="s">
         <v>46</v>
@@ -23380,7 +23380,7 @@
         <v>224</v>
       </c>
       <c r="W148" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X148" s="4" t="s">
         <v>46</v>
@@ -23460,7 +23460,7 @@
         <v>703</v>
       </c>
       <c r="W149" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X149" s="4" t="s">
         <v>46</v>
@@ -23536,7 +23536,7 @@
       <c r="U150" s="4"/>
       <c r="V150" s="4"/>
       <c r="W150" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X150" s="4" t="s">
         <v>46</v>
@@ -23616,7 +23616,7 @@
         <v>237</v>
       </c>
       <c r="W151" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X151" s="4" t="s">
         <v>46</v>
@@ -23694,7 +23694,7 @@
         <v>721</v>
       </c>
       <c r="W152" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X152" s="4" t="s">
         <v>46</v>
@@ -23772,7 +23772,7 @@
         <v>340</v>
       </c>
       <c r="W153" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X153" s="4" t="s">
         <v>46</v>
@@ -23848,7 +23848,7 @@
       <c r="U154" s="4"/>
       <c r="V154" s="4"/>
       <c r="W154" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X154" s="4" t="s">
         <v>322</v>
@@ -23922,7 +23922,7 @@
       <c r="U155" s="4"/>
       <c r="V155" s="4"/>
       <c r="W155" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X155" s="4" t="s">
         <v>46</v>
@@ -23996,7 +23996,7 @@
       <c r="U156" s="4"/>
       <c r="V156" s="4"/>
       <c r="W156" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X156" s="4" t="s">
         <v>46</v>
@@ -24076,7 +24076,7 @@
         <v>340</v>
       </c>
       <c r="W157" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X157" s="4" t="s">
         <v>322</v>
@@ -24156,7 +24156,7 @@
         <v>45</v>
       </c>
       <c r="W158" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X158" s="4" t="s">
         <v>322</v>
@@ -24234,7 +24234,7 @@
         <v>756</v>
       </c>
       <c r="W159" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X159" s="4" t="s">
         <v>46</v>
@@ -24312,7 +24312,7 @@
         <v>350</v>
       </c>
       <c r="W160" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X160" s="4" t="s">
         <v>46</v>
@@ -24388,7 +24388,7 @@
       <c r="U161" s="4"/>
       <c r="V161" s="4"/>
       <c r="W161" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X161" s="4" t="s">
         <v>46</v>
@@ -24464,7 +24464,7 @@
       <c r="U162" s="4"/>
       <c r="V162" s="4"/>
       <c r="W162" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X162" s="4" t="s">
         <v>46</v>
@@ -24542,7 +24542,7 @@
         <v>206</v>
       </c>
       <c r="W163" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X163" s="4" t="s">
         <v>46</v>
@@ -24618,7 +24618,7 @@
       <c r="U164" s="4"/>
       <c r="V164" s="4"/>
       <c r="W164" s="4">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="X164" s="4" t="s">
         <v>46</v>
@@ -24696,7 +24696,7 @@
         <v>557</v>
       </c>
       <c r="W165" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X165" s="4" t="s">
         <v>46</v>
@@ -24770,7 +24770,7 @@
       <c r="U166" s="4"/>
       <c r="V166" s="4"/>
       <c r="W166" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X166" s="4" t="s">
         <v>46</v>
@@ -24848,7 +24848,7 @@
         <v>130</v>
       </c>
       <c r="W167" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X167" s="4" t="s">
         <v>46</v>
@@ -24922,7 +24922,7 @@
       <c r="U168" s="4"/>
       <c r="V168" s="4"/>
       <c r="W168" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X168" s="4" t="s">
         <v>46</v>
@@ -25000,7 +25000,7 @@
         <v>350</v>
       </c>
       <c r="W169" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X169" s="4" t="s">
         <v>46</v>
@@ -25076,7 +25076,7 @@
       <c r="U170" s="4"/>
       <c r="V170" s="4"/>
       <c r="W170" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X170" s="4" t="s">
         <v>46</v>
@@ -25152,7 +25152,7 @@
       <c r="U171" s="4"/>
       <c r="V171" s="4"/>
       <c r="W171" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X171" s="4" t="s">
         <v>46</v>
@@ -25232,7 +25232,7 @@
         <v>206</v>
       </c>
       <c r="W172" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X172" s="4" t="s">
         <v>46</v>
@@ -25310,7 +25310,7 @@
         <v>237</v>
       </c>
       <c r="W173" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X173" s="4" t="s">
         <v>46</v>
@@ -25386,7 +25386,7 @@
       <c r="U174" s="4"/>
       <c r="V174" s="4"/>
       <c r="W174" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X174" s="4" t="s">
         <v>46</v>
@@ -25460,7 +25460,7 @@
       <c r="U175" s="4"/>
       <c r="V175" s="4"/>
       <c r="W175" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X175" s="4" t="s">
         <v>46</v>
@@ -25538,7 +25538,7 @@
         <v>237</v>
       </c>
       <c r="W176" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X176" s="4" t="s">
         <v>46</v>
@@ -25614,7 +25614,7 @@
       <c r="U177" s="4"/>
       <c r="V177" s="4"/>
       <c r="W177" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X177" s="4" t="s">
         <v>46</v>
@@ -25690,7 +25690,7 @@
       <c r="U178" s="4"/>
       <c r="V178" s="4"/>
       <c r="W178" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X178" s="4" t="s">
         <v>46</v>
@@ -25766,7 +25766,7 @@
       <c r="U179" s="4"/>
       <c r="V179" s="4"/>
       <c r="W179" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X179" s="4" t="s">
         <v>46</v>
@@ -25846,7 +25846,7 @@
         <v>838</v>
       </c>
       <c r="W180" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X180" s="4" t="s">
         <v>46</v>
@@ -25926,7 +25926,7 @@
         <v>45</v>
       </c>
       <c r="W181" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X181" s="4" t="s">
         <v>46</v>
@@ -25996,7 +25996,7 @@
       <c r="U182" s="4"/>
       <c r="V182" s="4"/>
       <c r="W182" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X182" s="4" t="s">
         <v>46</v>
@@ -26066,7 +26066,7 @@
       <c r="U183" s="4"/>
       <c r="V183" s="4"/>
       <c r="W183" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X183" s="4" t="s">
         <v>46</v>
@@ -26136,7 +26136,7 @@
       <c r="U184" s="4"/>
       <c r="V184" s="4"/>
       <c r="W184" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X184" s="4" t="s">
         <v>46</v>
@@ -26206,7 +26206,7 @@
       <c r="U185" s="4"/>
       <c r="V185" s="4"/>
       <c r="W185" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X185" s="4" t="s">
         <v>46</v>
@@ -26280,7 +26280,7 @@
         <v>340</v>
       </c>
       <c r="W186" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X186" s="4" t="s">
         <v>46</v>
@@ -26360,7 +26360,7 @@
         <v>45</v>
       </c>
       <c r="W187" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X187" s="4" t="s">
         <v>46</v>
@@ -26436,7 +26436,7 @@
       <c r="U188" s="4"/>
       <c r="V188" s="4"/>
       <c r="W188" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X188" s="4" t="s">
         <v>322</v>
@@ -26508,7 +26508,7 @@
       <c r="U189" s="4"/>
       <c r="V189" s="4"/>
       <c r="W189" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X189" s="4" t="s">
         <v>46</v>
@@ -26582,7 +26582,7 @@
       <c r="U190" s="4"/>
       <c r="V190" s="4"/>
       <c r="W190" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X190" s="4" t="s">
         <v>46</v>
@@ -26658,7 +26658,7 @@
       <c r="U191" s="4"/>
       <c r="V191" s="4"/>
       <c r="W191" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X191" s="4" t="s">
         <v>46</v>
@@ -26732,7 +26732,7 @@
       <c r="U192" s="4"/>
       <c r="V192" s="4"/>
       <c r="W192" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X192" s="4" t="s">
         <v>46</v>
@@ -26806,7 +26806,7 @@
       <c r="U193" s="4"/>
       <c r="V193" s="4"/>
       <c r="W193" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X193" s="4" t="s">
         <v>46</v>
@@ -26884,7 +26884,7 @@
         <v>892</v>
       </c>
       <c r="W194" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X194" s="4" t="s">
         <v>46</v>
@@ -26962,7 +26962,7 @@
         <v>130</v>
       </c>
       <c r="W195" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X195" s="4" t="s">
         <v>46</v>
@@ -27038,7 +27038,7 @@
       <c r="U196" s="4"/>
       <c r="V196" s="4"/>
       <c r="W196" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X196" s="4" t="s">
         <v>46</v>
@@ -27118,7 +27118,7 @@
         <v>45</v>
       </c>
       <c r="W197" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X197" s="4" t="s">
         <v>46</v>
@@ -27196,7 +27196,7 @@
         <v>212</v>
       </c>
       <c r="W198" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X198" s="4" t="s">
         <v>46</v>
@@ -27274,7 +27274,7 @@
         <v>45</v>
       </c>
       <c r="W199" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X199" s="4" t="s">
         <v>46</v>
@@ -27350,7 +27350,7 @@
       <c r="U200" s="4"/>
       <c r="V200" s="4"/>
       <c r="W200" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X200" s="4" t="s">
         <v>46</v>
@@ -27426,7 +27426,7 @@
       <c r="U201" s="4"/>
       <c r="V201" s="4"/>
       <c r="W201" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X201" s="4" t="s">
         <v>46</v>
@@ -27502,7 +27502,7 @@
       <c r="U202" s="4"/>
       <c r="V202" s="4"/>
       <c r="W202" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X202" s="4" t="s">
         <v>46</v>
@@ -27582,7 +27582,7 @@
         <v>321</v>
       </c>
       <c r="W203" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X203" s="4" t="s">
         <v>46</v>
@@ -27662,7 +27662,7 @@
         <v>237</v>
       </c>
       <c r="W204" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X204" s="4" t="s">
         <v>46</v>
@@ -27736,7 +27736,7 @@
       <c r="U205" s="4"/>
       <c r="V205" s="4"/>
       <c r="W205" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X205" s="4" t="s">
         <v>46</v>
@@ -27812,7 +27812,7 @@
       <c r="U206" s="4"/>
       <c r="V206" s="4"/>
       <c r="W206" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X206" s="4" t="s">
         <v>46</v>
@@ -27892,7 +27892,7 @@
         <v>45</v>
       </c>
       <c r="W207" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X207" s="4" t="s">
         <v>46</v>
@@ -27972,7 +27972,7 @@
         <v>45</v>
       </c>
       <c r="W208" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X208" s="4" t="s">
         <v>46</v>
@@ -28052,7 +28052,7 @@
         <v>206</v>
       </c>
       <c r="W209" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X209" s="4" t="s">
         <v>46</v>
@@ -28128,7 +28128,7 @@
       <c r="U210" s="4"/>
       <c r="V210" s="4"/>
       <c r="W210" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X210" s="4" t="s">
         <v>46</v>
@@ -28204,7 +28204,7 @@
       <c r="U211" s="4"/>
       <c r="V211" s="4"/>
       <c r="W211" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X211" s="4" t="s">
         <v>46</v>
@@ -28280,7 +28280,7 @@
       <c r="U212" s="4"/>
       <c r="V212" s="4"/>
       <c r="W212" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X212" s="4" t="s">
         <v>46</v>
@@ -28356,7 +28356,7 @@
       <c r="U213" s="4"/>
       <c r="V213" s="4"/>
       <c r="W213" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X213" s="4" t="s">
         <v>46</v>
@@ -28430,7 +28430,7 @@
       <c r="U214" s="4"/>
       <c r="V214" s="4"/>
       <c r="W214" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X214" s="4" t="s">
         <v>46</v>
@@ -28506,7 +28506,7 @@
       <c r="U215" s="4"/>
       <c r="V215" s="4"/>
       <c r="W215" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X215" s="4" t="s">
         <v>46</v>
@@ -28586,7 +28586,7 @@
         <v>350</v>
       </c>
       <c r="W216" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X216" s="4" t="s">
         <v>46</v>
@@ -28662,7 +28662,7 @@
       <c r="U217" s="4"/>
       <c r="V217" s="4"/>
       <c r="W217" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X217" s="4" t="s">
         <v>46</v>
@@ -28742,7 +28742,7 @@
         <v>224</v>
       </c>
       <c r="W218" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X218" s="4" t="s">
         <v>46</v>
@@ -28818,7 +28818,7 @@
       <c r="U219" s="4"/>
       <c r="V219" s="4"/>
       <c r="W219" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X219" s="4" t="s">
         <v>46</v>
@@ -28894,7 +28894,7 @@
       <c r="U220" s="4"/>
       <c r="V220" s="4"/>
       <c r="W220" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X220" s="4" t="s">
         <v>46</v>
@@ -28970,7 +28970,7 @@
       <c r="U221" s="4"/>
       <c r="V221" s="4"/>
       <c r="W221" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X221" s="4" t="s">
         <v>46</v>
@@ -29050,7 +29050,7 @@
         <v>224</v>
       </c>
       <c r="W222" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X222" s="4" t="s">
         <v>46</v>
@@ -29126,7 +29126,7 @@
       <c r="U223" s="4"/>
       <c r="V223" s="4"/>
       <c r="W223" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X223" s="4" t="s">
         <v>46</v>
@@ -29202,7 +29202,7 @@
       <c r="U224" s="4"/>
       <c r="V224" s="4"/>
       <c r="W224" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X224" s="4" t="s">
         <v>46</v>
@@ -29278,7 +29278,7 @@
       <c r="U225" s="4"/>
       <c r="V225" s="4"/>
       <c r="W225" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X225" s="4" t="s">
         <v>46</v>
@@ -29354,7 +29354,7 @@
       <c r="U226" s="4"/>
       <c r="V226" s="4"/>
       <c r="W226" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X226" s="4" t="s">
         <v>46</v>
@@ -29430,7 +29430,7 @@
       <c r="U227" s="4"/>
       <c r="V227" s="4"/>
       <c r="W227" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X227" s="4" t="s">
         <v>46</v>
@@ -29510,7 +29510,7 @@
         <v>1008</v>
       </c>
       <c r="W228" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X228" s="4" t="s">
         <v>46</v>
@@ -29590,7 +29590,7 @@
         <v>1013</v>
       </c>
       <c r="W229" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X229" s="4" t="s">
         <v>46</v>
@@ -29666,7 +29666,7 @@
       <c r="U230" s="4"/>
       <c r="V230" s="4"/>
       <c r="W230" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X230" s="4" t="s">
         <v>46</v>
@@ -29744,7 +29744,7 @@
         <v>45</v>
       </c>
       <c r="W231" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X231" s="4" t="s">
         <v>46</v>
@@ -29822,7 +29822,7 @@
         <v>45</v>
       </c>
       <c r="W232" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X232" s="4" t="s">
         <v>46</v>
@@ -29898,7 +29898,7 @@
       <c r="U233" s="4"/>
       <c r="V233" s="4"/>
       <c r="W233" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X233" s="4" t="s">
         <v>46</v>
@@ -29974,7 +29974,7 @@
       <c r="U234" s="4"/>
       <c r="V234" s="4"/>
       <c r="W234" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X234" s="4" t="s">
         <v>46</v>
@@ -30050,7 +30050,7 @@
       <c r="U235" s="4"/>
       <c r="V235" s="4"/>
       <c r="W235" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X235" s="4" t="s">
         <v>46</v>
@@ -30130,7 +30130,7 @@
         <v>45</v>
       </c>
       <c r="W236" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X236" s="4" t="s">
         <v>46</v>
@@ -30206,7 +30206,7 @@
       <c r="U237" s="4"/>
       <c r="V237" s="4"/>
       <c r="W237" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X237" s="4" t="s">
         <v>322</v>
@@ -30282,7 +30282,7 @@
       <c r="U238" s="4"/>
       <c r="V238" s="4"/>
       <c r="W238" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X238" s="4" t="s">
         <v>46</v>
@@ -30358,7 +30358,7 @@
       <c r="U239" s="4"/>
       <c r="V239" s="4"/>
       <c r="W239" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X239" s="4" t="s">
         <v>46</v>
@@ -30436,7 +30436,7 @@
         <v>356</v>
       </c>
       <c r="W240" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X240" s="4" t="s">
         <v>46</v>
@@ -30514,7 +30514,7 @@
         <v>130</v>
       </c>
       <c r="W241" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X241" s="4" t="s">
         <v>46</v>
@@ -30588,7 +30588,7 @@
       <c r="U242" s="4"/>
       <c r="V242" s="4"/>
       <c r="W242" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X242" s="4" t="s">
         <v>46</v>
@@ -30664,7 +30664,7 @@
       <c r="U243" s="4"/>
       <c r="V243" s="4"/>
       <c r="W243" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X243" s="4" t="s">
         <v>322</v>
@@ -30740,7 +30740,7 @@
       <c r="U244" s="4"/>
       <c r="V244" s="4"/>
       <c r="W244" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X244" s="4" t="s">
         <v>46</v>
@@ -30820,7 +30820,7 @@
         <v>340</v>
       </c>
       <c r="W245" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X245" s="4" t="s">
         <v>46</v>
@@ -30896,7 +30896,7 @@
       <c r="U246" s="4"/>
       <c r="V246" s="4"/>
       <c r="W246" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X246" s="4" t="s">
         <v>46</v>
@@ -30970,7 +30970,7 @@
       <c r="U247" s="4"/>
       <c r="V247" s="4"/>
       <c r="W247" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X247" s="4" t="s">
         <v>46</v>
@@ -31048,7 +31048,7 @@
         <v>237</v>
       </c>
       <c r="W248" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X248" s="4" t="s">
         <v>46</v>
@@ -31122,7 +31122,7 @@
       <c r="U249" s="4"/>
       <c r="V249" s="4"/>
       <c r="W249" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X249" s="4" t="s">
         <v>46</v>
@@ -31198,7 +31198,7 @@
         <v>1101</v>
       </c>
       <c r="W250" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X250" s="4" t="s">
         <v>46</v>
@@ -31276,7 +31276,7 @@
         <v>237</v>
       </c>
       <c r="W251" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X251" s="4" t="s">
         <v>46</v>
@@ -31352,7 +31352,7 @@
       <c r="U252" s="4"/>
       <c r="V252" s="4"/>
       <c r="W252" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X252" s="4" t="s">
         <v>46</v>
@@ -31432,7 +31432,7 @@
         <v>45</v>
       </c>
       <c r="W253" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X253" s="4" t="s">
         <v>46</v>
@@ -31512,7 +31512,7 @@
         <v>350</v>
       </c>
       <c r="W254" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X254" s="4" t="s">
         <v>46</v>
@@ -31588,7 +31588,7 @@
       <c r="U255" s="4"/>
       <c r="V255" s="4"/>
       <c r="W255" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X255" s="4" t="s">
         <v>46</v>
@@ -31664,7 +31664,7 @@
       <c r="U256" s="4"/>
       <c r="V256" s="4"/>
       <c r="W256" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X256" s="4" t="s">
         <v>46</v>
@@ -31740,7 +31740,7 @@
       <c r="U257" s="4"/>
       <c r="V257" s="4"/>
       <c r="W257" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X257" s="4" t="s">
         <v>46</v>
@@ -31820,7 +31820,7 @@
         <v>340</v>
       </c>
       <c r="W258" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X258" s="4" t="s">
         <v>46</v>
@@ -31900,7 +31900,7 @@
         <v>340</v>
       </c>
       <c r="W259" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X259" s="4" t="s">
         <v>46</v>
@@ -31976,7 +31976,7 @@
         <v>45</v>
       </c>
       <c r="W260" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X260" s="4" t="s">
         <v>46</v>
@@ -32050,7 +32050,7 @@
       <c r="U261" s="4"/>
       <c r="V261" s="4"/>
       <c r="W261" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X261" s="4" t="s">
         <v>46</v>
@@ -32126,7 +32126,7 @@
       <c r="U262" s="4"/>
       <c r="V262" s="4"/>
       <c r="W262" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X262" s="4" t="s">
         <v>46</v>
@@ -32202,7 +32202,7 @@
         <v>45</v>
       </c>
       <c r="W263" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X263" s="4" t="s">
         <v>46</v>
@@ -32282,7 +32282,7 @@
         <v>45</v>
       </c>
       <c r="W264" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X264" s="4" t="s">
         <v>46</v>
@@ -32362,7 +32362,7 @@
         <v>212</v>
       </c>
       <c r="W265" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X265" s="4" t="s">
         <v>46</v>
@@ -32438,7 +32438,7 @@
       <c r="U266" s="4"/>
       <c r="V266" s="4"/>
       <c r="W266" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X266" s="4" t="s">
         <v>46</v>
@@ -32512,7 +32512,7 @@
       <c r="U267" s="4"/>
       <c r="V267" s="4"/>
       <c r="W267" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X267" s="4" t="s">
         <v>46</v>
@@ -32592,7 +32592,7 @@
         <v>45</v>
       </c>
       <c r="W268" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X268" s="4" t="s">
         <v>46</v>
@@ -32668,7 +32668,7 @@
       <c r="U269" s="4"/>
       <c r="V269" s="4"/>
       <c r="W269" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X269" s="4" t="s">
         <v>46</v>
@@ -32748,7 +32748,7 @@
         <v>224</v>
       </c>
       <c r="W270" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X270" s="4" t="s">
         <v>46</v>
@@ -32824,7 +32824,7 @@
       <c r="U271" s="4"/>
       <c r="V271" s="4"/>
       <c r="W271" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X271" s="4" t="s">
         <v>46</v>
@@ -32904,7 +32904,7 @@
         <v>237</v>
       </c>
       <c r="W272" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X272" s="4" t="s">
         <v>46</v>
@@ -32984,7 +32984,7 @@
         <v>721</v>
       </c>
       <c r="W273" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X273" s="4" t="s">
         <v>46</v>
@@ -33064,7 +33064,7 @@
         <v>237</v>
       </c>
       <c r="W274" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X274" s="4" t="s">
         <v>46</v>
@@ -33142,7 +33142,7 @@
         <v>237</v>
       </c>
       <c r="W275" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X275" s="4" t="s">
         <v>46</v>
@@ -33218,7 +33218,7 @@
       <c r="U276" s="4"/>
       <c r="V276" s="4"/>
       <c r="W276" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X276" s="4" t="s">
         <v>46</v>
@@ -33292,7 +33292,7 @@
       <c r="U277" s="4"/>
       <c r="V277" s="4"/>
       <c r="W277" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X277" s="4" t="s">
         <v>46</v>
@@ -33368,7 +33368,7 @@
       <c r="U278" s="4"/>
       <c r="V278" s="4"/>
       <c r="W278" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X278" s="4" t="s">
         <v>322</v>
@@ -33448,7 +33448,7 @@
         <v>321</v>
       </c>
       <c r="W279" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X279" s="4" t="s">
         <v>46</v>
@@ -33522,7 +33522,7 @@
       <c r="U280" s="4"/>
       <c r="V280" s="4"/>
       <c r="W280" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X280" s="4" t="s">
         <v>46</v>
@@ -33602,7 +33602,7 @@
         <v>245</v>
       </c>
       <c r="W281" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X281" s="4" t="s">
         <v>46</v>
@@ -33682,7 +33682,7 @@
         <v>93</v>
       </c>
       <c r="W282" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X282" s="4" t="s">
         <v>46</v>
@@ -33758,7 +33758,7 @@
       <c r="U283" s="4"/>
       <c r="V283" s="4"/>
       <c r="W283" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X283" s="4" t="s">
         <v>46</v>
@@ -33828,7 +33828,7 @@
       <c r="U284" s="4"/>
       <c r="V284" s="4"/>
       <c r="W284" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X284" s="4" t="s">
         <v>46</v>
@@ -33898,7 +33898,7 @@
       <c r="U285" s="4"/>
       <c r="V285" s="4"/>
       <c r="W285" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X285" s="4" t="s">
         <v>322</v>
@@ -33966,7 +33966,7 @@
       <c r="U286" s="4"/>
       <c r="V286" s="4"/>
       <c r="W286" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X286" s="4" t="s">
         <v>46</v>
@@ -34040,7 +34040,7 @@
       <c r="U287" s="4"/>
       <c r="V287" s="4"/>
       <c r="W287" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X287" s="4" t="s">
         <v>46</v>
@@ -34116,7 +34116,7 @@
       <c r="U288" s="4"/>
       <c r="V288" s="4"/>
       <c r="W288" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X288" s="4" t="s">
         <v>46</v>
@@ -34192,7 +34192,7 @@
       <c r="U289" s="4"/>
       <c r="V289" s="4"/>
       <c r="W289" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X289" s="4" t="s">
         <v>46</v>
@@ -34272,7 +34272,7 @@
         <v>1248</v>
       </c>
       <c r="W290" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X290" s="4" t="s">
         <v>46</v>
@@ -34352,7 +34352,7 @@
         <v>245</v>
       </c>
       <c r="W291" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X291" s="4" t="s">
         <v>46</v>
@@ -34432,7 +34432,7 @@
         <v>245</v>
       </c>
       <c r="W292" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X292" s="4" t="s">
         <v>46</v>
@@ -34512,7 +34512,7 @@
         <v>245</v>
       </c>
       <c r="W293" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X293" s="4" t="s">
         <v>46</v>
@@ -34592,7 +34592,7 @@
         <v>340</v>
       </c>
       <c r="W294" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X294" s="4" t="s">
         <v>46</v>
@@ -34672,7 +34672,7 @@
         <v>721</v>
       </c>
       <c r="W295" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X295" s="4" t="s">
         <v>46</v>
@@ -34748,7 +34748,7 @@
       <c r="U296" s="4"/>
       <c r="V296" s="4"/>
       <c r="W296" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X296" s="4" t="s">
         <v>46</v>
@@ -34822,7 +34822,7 @@
       <c r="U297" s="4"/>
       <c r="V297" s="4"/>
       <c r="W297" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X297" s="4" t="s">
         <v>46</v>
@@ -34896,7 +34896,7 @@
       <c r="U298" s="4"/>
       <c r="V298" s="4"/>
       <c r="W298" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X298" s="4" t="s">
         <v>46</v>
@@ -34972,7 +34972,7 @@
       <c r="U299" s="4"/>
       <c r="V299" s="4"/>
       <c r="W299" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X299" s="4" t="s">
         <v>46</v>
@@ -35048,7 +35048,7 @@
       <c r="U300" s="4"/>
       <c r="V300" s="4"/>
       <c r="W300" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X300" s="4" t="s">
         <v>46</v>
@@ -35124,7 +35124,7 @@
       <c r="U301" s="4"/>
       <c r="V301" s="4"/>
       <c r="W301" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X301" s="4" t="s">
         <v>46</v>
@@ -35204,7 +35204,7 @@
         <v>45</v>
       </c>
       <c r="W302" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X302" s="4" t="s">
         <v>46</v>
@@ -35284,7 +35284,7 @@
         <v>224</v>
       </c>
       <c r="W303" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X303" s="4" t="s">
         <v>322</v>
@@ -35360,7 +35360,7 @@
       <c r="U304" s="4"/>
       <c r="V304" s="4"/>
       <c r="W304" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X304" s="4" t="s">
         <v>46</v>
@@ -35430,7 +35430,7 @@
       <c r="U305" s="4"/>
       <c r="V305" s="4"/>
       <c r="W305" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X305" s="4" t="s">
         <v>46</v>
@@ -35502,7 +35502,7 @@
       <c r="U306" s="4"/>
       <c r="V306" s="4"/>
       <c r="W306" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X306" s="4" t="s">
         <v>46</v>
@@ -35582,7 +35582,7 @@
         <v>130</v>
       </c>
       <c r="W307" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X307" s="4" t="s">
         <v>46</v>
@@ -35660,7 +35660,7 @@
         <v>237</v>
       </c>
       <c r="W308" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X308" s="4" t="s">
         <v>46</v>
@@ -35736,7 +35736,7 @@
       <c r="U309" s="4"/>
       <c r="V309" s="4"/>
       <c r="W309" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X309" s="4" t="s">
         <v>46</v>
@@ -35816,7 +35816,7 @@
         <v>45</v>
       </c>
       <c r="W310" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X310" s="4" t="s">
         <v>46</v>
@@ -35896,7 +35896,7 @@
         <v>224</v>
       </c>
       <c r="W311" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X311" s="4" t="s">
         <v>46</v>
@@ -35974,7 +35974,7 @@
         <v>1344</v>
       </c>
       <c r="W312" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X312" s="4" t="s">
         <v>46</v>
@@ -36050,7 +36050,7 @@
       <c r="U313" s="4"/>
       <c r="V313" s="4"/>
       <c r="W313" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X313" s="4" t="s">
         <v>322</v>
@@ -36126,7 +36126,7 @@
       <c r="U314" s="4"/>
       <c r="V314" s="4"/>
       <c r="W314" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X314" s="4" t="s">
         <v>322</v>
@@ -36196,7 +36196,7 @@
       <c r="U315" s="4"/>
       <c r="V315" s="4"/>
       <c r="W315" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X315" s="4" t="s">
         <v>46</v>
@@ -36272,7 +36272,7 @@
       <c r="U316" s="4"/>
       <c r="V316" s="4"/>
       <c r="W316" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X316" s="4" t="s">
         <v>46</v>
@@ -36346,7 +36346,7 @@
       <c r="U317" s="4"/>
       <c r="V317" s="4"/>
       <c r="W317" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X317" s="4" t="s">
         <v>322</v>
@@ -36422,7 +36422,7 @@
       <c r="U318" s="4"/>
       <c r="V318" s="4"/>
       <c r="W318" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X318" s="4" t="s">
         <v>46</v>
@@ -36498,7 +36498,7 @@
       <c r="U319" s="4"/>
       <c r="V319" s="4"/>
       <c r="W319" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X319" s="4" t="s">
         <v>46</v>
@@ -36576,7 +36576,7 @@
         <v>340</v>
       </c>
       <c r="W320" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X320" s="4" t="s">
         <v>322</v>
@@ -36652,7 +36652,7 @@
       <c r="U321" s="4"/>
       <c r="V321" s="4"/>
       <c r="W321" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X321" s="4" t="s">
         <v>322</v>
@@ -36732,7 +36732,7 @@
         <v>340</v>
       </c>
       <c r="W322" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X322" s="4" t="s">
         <v>46</v>
@@ -36808,7 +36808,7 @@
       <c r="U323" s="4"/>
       <c r="V323" s="4"/>
       <c r="W323" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X323" s="4" t="s">
         <v>46</v>
@@ -36884,7 +36884,7 @@
       <c r="U324" s="4"/>
       <c r="V324" s="4"/>
       <c r="W324" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X324" s="4" t="s">
         <v>46</v>
@@ -36956,7 +36956,7 @@
       <c r="U325" s="4"/>
       <c r="V325" s="4"/>
       <c r="W325" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X325" s="4" t="s">
         <v>322</v>
@@ -37032,7 +37032,7 @@
       <c r="U326" s="4"/>
       <c r="V326" s="4"/>
       <c r="W326" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X326" s="4" t="s">
         <v>322</v>
@@ -37108,7 +37108,7 @@
       <c r="U327" s="4"/>
       <c r="V327" s="4"/>
       <c r="W327" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X327" s="4" t="s">
         <v>322</v>
@@ -37184,7 +37184,7 @@
       <c r="U328" s="4"/>
       <c r="V328" s="4"/>
       <c r="W328" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X328" s="4" t="s">
         <v>1418</v>
@@ -37262,7 +37262,7 @@
         <v>45</v>
       </c>
       <c r="W329" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X329" s="4" t="s">
         <v>46</v>
@@ -37342,7 +37342,7 @@
         <v>1427</v>
       </c>
       <c r="W330" s="4">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X330" s="4" t="s">
         <v>46</v>
@@ -37418,7 +37418,7 @@
       <c r="U331" s="4"/>
       <c r="V331" s="4"/>
       <c r="W331" s="4">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="X331" s="4" t="s">
         <v>46</v>
@@ -37498,7 +37498,7 @@
         <v>340</v>
       </c>
       <c r="W332" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X332" s="4" t="s">
         <v>46</v>
@@ -37574,7 +37574,7 @@
       <c r="U333" s="4"/>
       <c r="V333" s="4"/>
       <c r="W333" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X333" s="4" t="s">
         <v>46</v>
@@ -37650,7 +37650,7 @@
       <c r="U334" s="4"/>
       <c r="V334" s="4"/>
       <c r="W334" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X334" s="4" t="s">
         <v>46</v>
@@ -37726,7 +37726,7 @@
       <c r="U335" s="4"/>
       <c r="V335" s="4"/>
       <c r="W335" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X335" s="4" t="s">
         <v>46</v>
@@ -37806,7 +37806,7 @@
         <v>1447</v>
       </c>
       <c r="W336" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X336" s="4" t="s">
         <v>46</v>
@@ -37882,7 +37882,7 @@
       <c r="U337" s="4"/>
       <c r="V337" s="4"/>
       <c r="W337" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X337" s="4" t="s">
         <v>46</v>
@@ -37962,7 +37962,7 @@
         <v>45</v>
       </c>
       <c r="W338" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X338" s="4" t="s">
         <v>46</v>
@@ -38038,7 +38038,7 @@
       <c r="U339" s="4"/>
       <c r="V339" s="4"/>
       <c r="W339" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X339" s="4" t="s">
         <v>322</v>
@@ -38116,7 +38116,7 @@
         <v>237</v>
       </c>
       <c r="W340" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X340" s="4" t="s">
         <v>322</v>
@@ -38192,7 +38192,7 @@
       <c r="U341" s="4"/>
       <c r="V341" s="4"/>
       <c r="W341" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X341" s="4" t="s">
         <v>322</v>
@@ -38266,7 +38266,7 @@
       <c r="U342" s="4"/>
       <c r="V342" s="4"/>
       <c r="W342" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X342" s="4" t="s">
         <v>322</v>
@@ -38346,7 +38346,7 @@
         <v>1472</v>
       </c>
       <c r="W343" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X343" s="4" t="s">
         <v>46</v>
@@ -38422,7 +38422,7 @@
       <c r="U344" s="4"/>
       <c r="V344" s="4"/>
       <c r="W344" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X344" s="4" t="s">
         <v>322</v>
@@ -38496,7 +38496,7 @@
       <c r="U345" s="4"/>
       <c r="V345" s="4"/>
       <c r="W345" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X345" s="4" t="s">
         <v>46</v>
@@ -38574,7 +38574,7 @@
         <v>224</v>
       </c>
       <c r="W346" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X346" s="4" t="s">
         <v>46</v>
@@ -38654,7 +38654,7 @@
         <v>356</v>
       </c>
       <c r="W347" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X347" s="4" t="s">
         <v>322</v>
@@ -38728,7 +38728,7 @@
       <c r="U348" s="4"/>
       <c r="V348" s="4"/>
       <c r="W348" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X348" s="4" t="s">
         <v>322</v>
@@ -38804,7 +38804,7 @@
       <c r="U349" s="4"/>
       <c r="V349" s="4"/>
       <c r="W349" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X349" s="4" t="s">
         <v>322</v>
@@ -38878,7 +38878,7 @@
       <c r="U350" s="4"/>
       <c r="V350" s="4"/>
       <c r="W350" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X350" s="4" t="s">
         <v>322</v>
@@ -38958,7 +38958,7 @@
         <v>1498</v>
       </c>
       <c r="W351" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X351" s="4" t="s">
         <v>322</v>
@@ -39036,7 +39036,7 @@
         <v>45</v>
       </c>
       <c r="W352" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X352" s="4" t="s">
         <v>322</v>
@@ -39114,7 +39114,7 @@
         <v>98</v>
       </c>
       <c r="W353" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X353" s="4" t="s">
         <v>46</v>
@@ -39190,7 +39190,7 @@
       <c r="U354" s="4"/>
       <c r="V354" s="4"/>
       <c r="W354" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X354" s="4" t="s">
         <v>46</v>
@@ -39270,7 +39270,7 @@
         <v>237</v>
       </c>
       <c r="W355" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X355" s="4" t="s">
         <v>46</v>
@@ -39350,7 +39350,7 @@
         <v>340</v>
       </c>
       <c r="W356" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X356" s="4" t="s">
         <v>322</v>
@@ -39430,7 +39430,7 @@
         <v>237</v>
       </c>
       <c r="W357" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X357" s="4" t="s">
         <v>322</v>
@@ -39510,7 +39510,7 @@
         <v>45</v>
       </c>
       <c r="W358" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X358" s="4" t="s">
         <v>322</v>
@@ -39590,7 +39590,7 @@
         <v>206</v>
       </c>
       <c r="W359" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X359" s="4" t="s">
         <v>322</v>
@@ -39666,7 +39666,7 @@
       <c r="U360" s="4"/>
       <c r="V360" s="4"/>
       <c r="W360" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X360" s="4" t="s">
         <v>46</v>
@@ -39746,7 +39746,7 @@
         <v>45</v>
       </c>
       <c r="W361" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X361" s="4" t="s">
         <v>322</v>
@@ -39822,7 +39822,7 @@
       <c r="U362" s="4"/>
       <c r="V362" s="4"/>
       <c r="W362" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X362" s="4" t="s">
         <v>46</v>
@@ -39902,7 +39902,7 @@
         <v>321</v>
       </c>
       <c r="W363" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X363" s="4" t="s">
         <v>322</v>
@@ -39978,7 +39978,7 @@
       <c r="U364" s="4"/>
       <c r="V364" s="4"/>
       <c r="W364" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X364" s="4" t="s">
         <v>46</v>
@@ -40054,7 +40054,7 @@
       <c r="U365" s="4"/>
       <c r="V365" s="4"/>
       <c r="W365" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X365" s="4" t="s">
         <v>322</v>
@@ -40130,7 +40130,7 @@
       <c r="U366" s="4"/>
       <c r="V366" s="4"/>
       <c r="W366" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X366" s="4" t="s">
         <v>322</v>
@@ -40206,7 +40206,7 @@
       <c r="U367" s="4"/>
       <c r="V367" s="4"/>
       <c r="W367" s="4">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X367" s="4" t="s">
         <v>46</v>
@@ -40286,7 +40286,7 @@
         <v>245</v>
       </c>
       <c r="W368" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X368" s="4" t="s">
         <v>46</v>
@@ -40362,7 +40362,7 @@
       <c r="U369" s="4"/>
       <c r="V369" s="4"/>
       <c r="W369" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X369" s="4" t="s">
         <v>322</v>
@@ -40434,7 +40434,7 @@
       <c r="U370" s="4"/>
       <c r="V370" s="4"/>
       <c r="W370" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X370" s="4" t="s">
         <v>46</v>
@@ -40512,7 +40512,7 @@
         <v>321</v>
       </c>
       <c r="W371" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X371" s="4" t="s">
         <v>46</v>
@@ -40590,7 +40590,7 @@
         <v>321</v>
       </c>
       <c r="W372" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X372" s="4" t="s">
         <v>46</v>
@@ -40668,7 +40668,7 @@
         <v>340</v>
       </c>
       <c r="W373" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X373" s="4" t="s">
         <v>46</v>
@@ -40748,7 +40748,7 @@
         <v>340</v>
       </c>
       <c r="W374" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X374" s="4" t="s">
         <v>322</v>
@@ -40824,7 +40824,7 @@
       <c r="U375" s="4"/>
       <c r="V375" s="4"/>
       <c r="W375" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X375" s="4" t="s">
         <v>322</v>
@@ -40898,7 +40898,7 @@
       <c r="U376" s="4"/>
       <c r="V376" s="4"/>
       <c r="W376" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X376" s="4" t="s">
         <v>46</v>
@@ -40972,7 +40972,7 @@
       <c r="U377" s="4"/>
       <c r="V377" s="4"/>
       <c r="W377" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X377" s="4" t="s">
         <v>46</v>
@@ -41042,7 +41042,7 @@
       <c r="U378" s="4"/>
       <c r="V378" s="4"/>
       <c r="W378" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X378" s="4" t="s">
         <v>322</v>
@@ -41116,7 +41116,7 @@
       <c r="U379" s="4"/>
       <c r="V379" s="4"/>
       <c r="W379" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X379" s="4" t="s">
         <v>322</v>
@@ -41192,7 +41192,7 @@
       <c r="U380" s="4"/>
       <c r="V380" s="4"/>
       <c r="W380" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X380" s="4" t="s">
         <v>46</v>
@@ -41268,7 +41268,7 @@
       <c r="U381" s="4"/>
       <c r="V381" s="4"/>
       <c r="W381" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X381" s="4" t="s">
         <v>322</v>
@@ -41342,7 +41342,7 @@
       <c r="U382" s="4"/>
       <c r="V382" s="4"/>
       <c r="W382" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X382" s="4" t="s">
         <v>322</v>
@@ -41422,7 +41422,7 @@
         <v>45</v>
       </c>
       <c r="W383" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X383" s="4" t="s">
         <v>322</v>
@@ -41496,7 +41496,7 @@
       <c r="U384" s="4"/>
       <c r="V384" s="4"/>
       <c r="W384" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X384" s="4" t="s">
         <v>46</v>
@@ -41574,7 +41574,7 @@
         <v>245</v>
       </c>
       <c r="W385" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X385" s="4" t="s">
         <v>46</v>
@@ -41650,7 +41650,7 @@
       <c r="U386" s="4"/>
       <c r="V386" s="4"/>
       <c r="W386" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X386" s="4" t="s">
         <v>46</v>
@@ -41724,7 +41724,7 @@
       <c r="U387" s="4"/>
       <c r="V387" s="4"/>
       <c r="W387" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X387" s="4" t="s">
         <v>322</v>
@@ -41800,7 +41800,7 @@
       <c r="U388" s="4"/>
       <c r="V388" s="4"/>
       <c r="W388" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X388" s="4" t="s">
         <v>322</v>
@@ -41874,7 +41874,7 @@
       <c r="U389" s="4"/>
       <c r="V389" s="4"/>
       <c r="W389" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X389" s="4" t="s">
         <v>322</v>
@@ -41954,7 +41954,7 @@
         <v>141</v>
       </c>
       <c r="W390" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X390" s="4" t="s">
         <v>322</v>
@@ -42030,7 +42030,7 @@
       <c r="U391" s="4"/>
       <c r="V391" s="4"/>
       <c r="W391" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X391" s="4" t="s">
         <v>322</v>
@@ -42108,7 +42108,7 @@
         <v>321</v>
       </c>
       <c r="W392" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X392" s="4" t="s">
         <v>322</v>
@@ -42188,7 +42188,7 @@
         <v>245</v>
       </c>
       <c r="W393" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X393" s="4" t="s">
         <v>46</v>
@@ -42268,7 +42268,7 @@
         <v>721</v>
       </c>
       <c r="W394" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X394" s="4" t="s">
         <v>46</v>
@@ -42344,7 +42344,7 @@
       <c r="U395" s="4"/>
       <c r="V395" s="4"/>
       <c r="W395" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X395" s="4" t="s">
         <v>322</v>
@@ -42420,7 +42420,7 @@
       <c r="U396" s="4"/>
       <c r="V396" s="4"/>
       <c r="W396" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X396" s="4" t="s">
         <v>46</v>
@@ -42496,7 +42496,7 @@
       <c r="U397" s="4"/>
       <c r="V397" s="4"/>
       <c r="W397" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X397" s="4" t="s">
         <v>322</v>
@@ -42576,7 +42576,7 @@
         <v>130</v>
       </c>
       <c r="W398" s="4">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X398" s="4" t="s">
         <v>46</v>
@@ -42652,7 +42652,7 @@
       <c r="U399" s="4"/>
       <c r="V399" s="4"/>
       <c r="W399" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X399" s="4" t="s">
         <v>322</v>
@@ -42728,7 +42728,7 @@
       <c r="U400" s="4"/>
       <c r="V400" s="4"/>
       <c r="W400" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X400" s="4" t="s">
         <v>46</v>
@@ -42802,7 +42802,7 @@
       <c r="U401" s="4"/>
       <c r="V401" s="4"/>
       <c r="W401" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X401" s="4" t="s">
         <v>322</v>
@@ -42876,7 +42876,7 @@
       <c r="U402" s="4"/>
       <c r="V402" s="4"/>
       <c r="W402" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X402" s="4" t="s">
         <v>322</v>
@@ -42952,7 +42952,7 @@
         <v>321</v>
       </c>
       <c r="W403" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X403" s="4" t="s">
         <v>46</v>
@@ -43030,7 +43030,7 @@
         <v>340</v>
       </c>
       <c r="W404" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X404" s="4" t="s">
         <v>46</v>
@@ -43104,7 +43104,7 @@
       <c r="U405" s="4"/>
       <c r="V405" s="4"/>
       <c r="W405" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X405" s="4" t="s">
         <v>46</v>
@@ -43182,7 +43182,7 @@
         <v>340</v>
       </c>
       <c r="W406" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X406" s="4" t="s">
         <v>46</v>
@@ -43262,7 +43262,7 @@
         <v>123</v>
       </c>
       <c r="W407" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X407" s="4" t="s">
         <v>46</v>
@@ -43342,7 +43342,7 @@
         <v>1248</v>
       </c>
       <c r="W408" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X408" s="4" t="s">
         <v>46</v>
@@ -43418,7 +43418,7 @@
       <c r="U409" s="4"/>
       <c r="V409" s="4"/>
       <c r="W409" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X409" s="4" t="s">
         <v>46</v>
@@ -43498,7 +43498,7 @@
         <v>321</v>
       </c>
       <c r="W410" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X410" s="4" t="s">
         <v>46</v>
@@ -43578,7 +43578,7 @@
         <v>721</v>
       </c>
       <c r="W411" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X411" s="4" t="s">
         <v>46</v>
@@ -43658,7 +43658,7 @@
         <v>224</v>
       </c>
       <c r="W412" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X412" s="4" t="s">
         <v>46</v>
@@ -43738,7 +43738,7 @@
         <v>1741</v>
       </c>
       <c r="W413" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X413" s="4" t="s">
         <v>46</v>
@@ -43816,7 +43816,7 @@
         <v>340</v>
       </c>
       <c r="W414" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X414" s="4" t="s">
         <v>46</v>
@@ -43894,7 +43894,7 @@
         <v>1741</v>
       </c>
       <c r="W415" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X415" s="4" t="s">
         <v>46</v>
@@ -43970,7 +43970,7 @@
       <c r="U416" s="4"/>
       <c r="V416" s="4"/>
       <c r="W416" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X416" s="4" t="s">
         <v>46</v>
@@ -44048,7 +44048,7 @@
         <v>321</v>
       </c>
       <c r="W417" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X417" s="4" t="s">
         <v>46</v>
@@ -44126,7 +44126,7 @@
         <v>557</v>
       </c>
       <c r="W418" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X418" s="4" t="s">
         <v>46</v>
@@ -44204,7 +44204,7 @@
         <v>245</v>
       </c>
       <c r="W419" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X419" s="4" t="s">
         <v>46</v>
@@ -44282,7 +44282,7 @@
         <v>721</v>
       </c>
       <c r="W420" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X420" s="4" t="s">
         <v>46</v>
@@ -44352,7 +44352,7 @@
       <c r="U421" s="4"/>
       <c r="V421" s="4"/>
       <c r="W421" s="4">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="X421" s="4" t="s">
         <v>46</v>
@@ -44424,7 +44424,7 @@
         <v>1498</v>
       </c>
       <c r="W422" s="4">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="X422" s="4" t="s">
         <v>46</v>
@@ -44492,7 +44492,7 @@
       <c r="U423" s="4"/>
       <c r="V423" s="4"/>
       <c r="W423" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X423" s="4" t="s">
         <v>46</v>
@@ -44564,7 +44564,7 @@
         <v>340</v>
       </c>
       <c r="W424" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X424" s="4" t="s">
         <v>46</v>
@@ -44632,7 +44632,7 @@
       <c r="U425" s="4"/>
       <c r="V425" s="4"/>
       <c r="W425" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X425" s="4" t="s">
         <v>46</v>
@@ -44704,7 +44704,7 @@
         <v>237</v>
       </c>
       <c r="W426" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X426" s="4" t="s">
         <v>46</v>
@@ -44780,7 +44780,7 @@
         <v>340</v>
       </c>
       <c r="W427" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X427" s="4" t="s">
         <v>46</v>
@@ -44850,7 +44850,7 @@
       <c r="U428" s="4"/>
       <c r="V428" s="4"/>
       <c r="W428" s="4">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="X428" s="4" t="s">
         <v>46</v>
@@ -44924,7 +44924,7 @@
       <c r="U429" s="4"/>
       <c r="V429" s="4"/>
       <c r="W429" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X429" s="4" t="s">
         <v>46</v>
@@ -45000,7 +45000,7 @@
       <c r="U430" s="4"/>
       <c r="V430" s="4"/>
       <c r="W430" s="4">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X430" s="4" t="s">
         <v>46</v>
@@ -45080,7 +45080,7 @@
         <v>237</v>
       </c>
       <c r="W431" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X431" s="4" t="s">
         <v>46</v>
@@ -45156,7 +45156,7 @@
       <c r="U432" s="4"/>
       <c r="V432" s="4"/>
       <c r="W432" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X432" s="4" t="s">
         <v>46</v>
@@ -45230,7 +45230,7 @@
       <c r="U433" s="4"/>
       <c r="V433" s="4"/>
       <c r="W433" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X433" s="4" t="s">
         <v>46</v>
@@ -45304,7 +45304,7 @@
       <c r="U434" s="4"/>
       <c r="V434" s="4"/>
       <c r="W434" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X434" s="4" t="s">
         <v>46</v>
@@ -45382,7 +45382,7 @@
         <v>237</v>
       </c>
       <c r="W435" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X435" s="4" t="s">
         <v>46</v>
@@ -45462,7 +45462,7 @@
         <v>245</v>
       </c>
       <c r="W436" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X436" s="4" t="s">
         <v>46</v>
@@ -45542,7 +45542,7 @@
         <v>212</v>
       </c>
       <c r="W437" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X437" s="4" t="s">
         <v>46</v>
@@ -45616,7 +45616,7 @@
         <v>74</v>
       </c>
       <c r="W438" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X438" s="4" t="s">
         <v>46</v>
@@ -45690,7 +45690,7 @@
       <c r="U439" s="4"/>
       <c r="V439" s="4"/>
       <c r="W439" s="4">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X439" s="4" t="s">
         <v>46</v>
@@ -45762,7 +45762,7 @@
       <c r="U440" s="4"/>
       <c r="V440" s="4"/>
       <c r="W440" s="4">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X440" s="4" t="s">
         <v>46</v>
@@ -45840,7 +45840,7 @@
         <v>224</v>
       </c>
       <c r="W441" s="4">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="X441" s="4" t="s">
         <v>46</v>
@@ -45920,7 +45920,7 @@
         <v>1839</v>
       </c>
       <c r="W442" s="4">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X442" s="4" t="s">
         <v>46</v>
@@ -45998,7 +45998,7 @@
         <v>703</v>
       </c>
       <c r="W443" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="X443" s="4" t="s">
         <v>46</v>
@@ -46078,7 +46078,7 @@
         <v>74</v>
       </c>
       <c r="W444" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X444" s="4" t="s">
         <v>46</v>
@@ -46150,7 +46150,7 @@
       <c r="U445" s="4"/>
       <c r="V445" s="4"/>
       <c r="W445" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X445" s="4" t="s">
         <v>46</v>
@@ -46228,7 +46228,7 @@
         <v>721</v>
       </c>
       <c r="W446" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X446" s="4" t="s">
         <v>46</v>
@@ -46308,7 +46308,7 @@
         <v>340</v>
       </c>
       <c r="W447" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X447" s="4" t="s">
         <v>46</v>
@@ -46382,7 +46382,7 @@
       <c r="U448" s="4"/>
       <c r="V448" s="4"/>
       <c r="W448" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X448" s="4" t="s">
         <v>46</v>
@@ -46462,7 +46462,7 @@
         <v>340</v>
       </c>
       <c r="W449" s="4">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X449" s="4" t="s">
         <v>46</v>
@@ -46538,7 +46538,7 @@
       <c r="U450" s="4"/>
       <c r="V450" s="4"/>
       <c r="W450" s="4">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X450" s="4" t="s">
         <v>46</v>
@@ -46606,7 +46606,7 @@
       <c r="U451" s="4"/>
       <c r="V451" s="4"/>
       <c r="W451" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X451" s="4" t="s">
         <v>46</v>
@@ -46674,7 +46674,7 @@
       <c r="U452" s="4"/>
       <c r="V452" s="4"/>
       <c r="W452" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X452" s="4" t="s">
         <v>46</v>
@@ -46742,7 +46742,7 @@
       <c r="U453" s="4"/>
       <c r="V453" s="4"/>
       <c r="W453" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X453" s="4" t="s">
         <v>46</v>
@@ -46810,7 +46810,7 @@
       <c r="U454" s="4"/>
       <c r="V454" s="4"/>
       <c r="W454" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X454" s="4" t="s">
         <v>46</v>
@@ -46878,7 +46878,7 @@
       <c r="U455" s="4"/>
       <c r="V455" s="4"/>
       <c r="W455" s="4">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="X455" s="4" t="s">
         <v>46</v>
@@ -46946,7 +46946,7 @@
       <c r="U456" s="4"/>
       <c r="V456" s="4"/>
       <c r="W456" s="4">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="X456" s="4" t="s">
         <v>46</v>
@@ -47014,7 +47014,7 @@
       <c r="U457" s="4"/>
       <c r="V457" s="4"/>
       <c r="W457" s="4">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="X457" s="4" t="s">
         <v>46</v>
@@ -47082,7 +47082,7 @@
       <c r="U458" s="4"/>
       <c r="V458" s="4"/>
       <c r="W458" s="4">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="X458" s="4" t="s">
         <v>46</v>
@@ -47150,7 +47150,7 @@
       <c r="U459" s="4"/>
       <c r="V459" s="4"/>
       <c r="W459" s="4">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X459" s="4" t="s">
         <v>46</v>
@@ -47220,7 +47220,7 @@
       <c r="U460" s="4"/>
       <c r="V460" s="4"/>
       <c r="W460" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X460" s="4" t="s">
         <v>46</v>
@@ -47290,7 +47290,7 @@
       <c r="U461" s="4"/>
       <c r="V461" s="4"/>
       <c r="W461" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X461" s="4" t="s">
         <v>46</v>
@@ -47366,7 +47366,7 @@
       <c r="U462" s="4"/>
       <c r="V462" s="4"/>
       <c r="W462" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X462" s="4" t="s">
         <v>46</v>
@@ -47440,7 +47440,7 @@
         <v>130</v>
       </c>
       <c r="W463" s="4">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X463" s="4" t="s">
         <v>46</v>
@@ -47514,7 +47514,7 @@
         <v>206</v>
       </c>
       <c r="W464" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X464" s="4" t="s">
         <v>46</v>
@@ -47584,7 +47584,7 @@
       <c r="U465" s="4"/>
       <c r="V465" s="4"/>
       <c r="W465" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X465" s="4" t="s">
         <v>322</v>
@@ -47660,7 +47660,7 @@
       <c r="U466" s="4"/>
       <c r="V466" s="4"/>
       <c r="W466" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X466" s="4" t="s">
         <v>46</v>
@@ -47740,7 +47740,7 @@
         <v>212</v>
       </c>
       <c r="W467" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X467" s="4" t="s">
         <v>46</v>
@@ -47814,7 +47814,7 @@
       <c r="U468" s="4"/>
       <c r="V468" s="4"/>
       <c r="W468" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X468" s="4" t="s">
         <v>322</v>
@@ -47894,7 +47894,7 @@
         <v>130</v>
       </c>
       <c r="W469" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X469" s="4" t="s">
         <v>46</v>
@@ -47972,7 +47972,7 @@
         <v>1937</v>
       </c>
       <c r="W470" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X470" s="4" t="s">
         <v>46</v>
@@ -48046,7 +48046,7 @@
       <c r="U471" s="4"/>
       <c r="V471" s="4"/>
       <c r="W471" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X471" s="4" t="s">
         <v>46</v>
@@ -48126,7 +48126,7 @@
         <v>123</v>
       </c>
       <c r="W472" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X472" s="4" t="s">
         <v>46</v>
@@ -48202,7 +48202,7 @@
         <v>340</v>
       </c>
       <c r="W473" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X473" s="4" t="s">
         <v>46</v>
@@ -48278,7 +48278,7 @@
       <c r="U474" s="4"/>
       <c r="V474" s="4"/>
       <c r="W474" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X474" s="4" t="s">
         <v>322</v>
@@ -48354,7 +48354,7 @@
       <c r="U475" s="4"/>
       <c r="V475" s="4"/>
       <c r="W475" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X475" s="4" t="s">
         <v>46</v>
@@ -48434,7 +48434,7 @@
         <v>1958</v>
       </c>
       <c r="W476" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X476" s="4" t="s">
         <v>322</v>
@@ -48510,7 +48510,7 @@
       <c r="U477" s="4"/>
       <c r="V477" s="4"/>
       <c r="W477" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X477" s="4" t="s">
         <v>46</v>
@@ -48590,7 +48590,7 @@
         <v>340</v>
       </c>
       <c r="W478" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X478" s="4" t="s">
         <v>46</v>
@@ -48670,7 +48670,7 @@
         <v>340</v>
       </c>
       <c r="W479" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X479" s="4" t="s">
         <v>46</v>
@@ -48744,7 +48744,7 @@
       <c r="U480" s="4"/>
       <c r="V480" s="4"/>
       <c r="W480" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X480" s="4" t="s">
         <v>46</v>
@@ -48820,7 +48820,7 @@
       <c r="U481" s="4"/>
       <c r="V481" s="4"/>
       <c r="W481" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X481" s="4" t="s">
         <v>46</v>
@@ -48894,7 +48894,7 @@
         <v>212</v>
       </c>
       <c r="W482" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X482" s="4" t="s">
         <v>46</v>
@@ -48974,7 +48974,7 @@
         <v>557</v>
       </c>
       <c r="W483" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X483" s="4" t="s">
         <v>46</v>
@@ -49050,7 +49050,7 @@
       <c r="U484" s="4"/>
       <c r="V484" s="4"/>
       <c r="W484" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X484" s="4" t="s">
         <v>46</v>
@@ -49124,7 +49124,7 @@
       <c r="U485" s="4"/>
       <c r="V485" s="4"/>
       <c r="W485" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X485" s="4" t="s">
         <v>322</v>
@@ -49204,7 +49204,7 @@
         <v>237</v>
       </c>
       <c r="W486" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X486" s="4" t="s">
         <v>46</v>
@@ -49284,7 +49284,7 @@
         <v>130</v>
       </c>
       <c r="W487" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X487" s="4" t="s">
         <v>46</v>
@@ -49360,7 +49360,7 @@
       <c r="U488" s="4"/>
       <c r="V488" s="4"/>
       <c r="W488" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X488" s="4" t="s">
         <v>46</v>
@@ -49440,7 +49440,7 @@
         <v>340</v>
       </c>
       <c r="W489" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X489" s="4" t="s">
         <v>46</v>
@@ -49516,7 +49516,7 @@
       <c r="U490" s="4"/>
       <c r="V490" s="4"/>
       <c r="W490" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X490" s="4" t="s">
         <v>46</v>
@@ -49592,7 +49592,7 @@
       <c r="U491" s="4"/>
       <c r="V491" s="4"/>
       <c r="W491" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X491" s="4" t="s">
         <v>46</v>
@@ -49670,7 +49670,7 @@
         <v>602</v>
       </c>
       <c r="W492" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X492" s="4" t="s">
         <v>322</v>
@@ -49750,7 +49750,7 @@
         <v>224</v>
       </c>
       <c r="W493" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X493" s="4" t="s">
         <v>46</v>
@@ -49824,7 +49824,7 @@
       <c r="U494" s="4"/>
       <c r="V494" s="4"/>
       <c r="W494" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X494" s="4" t="s">
         <v>46</v>
@@ -49904,7 +49904,7 @@
         <v>1013</v>
       </c>
       <c r="W495" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X495" s="4" t="s">
         <v>322</v>
@@ -49984,7 +49984,7 @@
         <v>74</v>
       </c>
       <c r="W496" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X496" s="4" t="s">
         <v>322</v>
@@ -50060,7 +50060,7 @@
       <c r="U497" s="4"/>
       <c r="V497" s="4"/>
       <c r="W497" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X497" s="4" t="s">
         <v>46</v>
@@ -50138,7 +50138,7 @@
         <v>721</v>
       </c>
       <c r="W498" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X498" s="4" t="s">
         <v>46</v>
@@ -50212,7 +50212,7 @@
       <c r="U499" s="4"/>
       <c r="V499" s="4"/>
       <c r="W499" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X499" s="4" t="s">
         <v>46</v>
@@ -50292,7 +50292,7 @@
         <v>340</v>
       </c>
       <c r="W500" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X500" s="4" t="s">
         <v>46</v>
@@ -50368,7 +50368,7 @@
       <c r="U501" s="4"/>
       <c r="V501" s="4"/>
       <c r="W501" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X501" s="4" t="s">
         <v>46</v>
@@ -50444,7 +50444,7 @@
       <c r="U502" s="4"/>
       <c r="V502" s="4"/>
       <c r="W502" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X502" s="4" t="s">
         <v>46</v>
@@ -50520,7 +50520,7 @@
       <c r="U503" s="4"/>
       <c r="V503" s="4"/>
       <c r="W503" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X503" s="4" t="s">
         <v>46</v>
@@ -50596,7 +50596,7 @@
       <c r="U504" s="4"/>
       <c r="V504" s="4"/>
       <c r="W504" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X504" s="4" t="s">
         <v>46</v>
@@ -50676,7 +50676,7 @@
         <v>721</v>
       </c>
       <c r="W505" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X505" s="4" t="s">
         <v>46</v>
@@ -50752,7 +50752,7 @@
       <c r="U506" s="4"/>
       <c r="V506" s="4"/>
       <c r="W506" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X506" s="4" t="s">
         <v>46</v>
@@ -50830,7 +50830,7 @@
         <v>224</v>
       </c>
       <c r="W507" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X507" s="4" t="s">
         <v>46</v>
@@ -50906,7 +50906,7 @@
       <c r="U508" s="4"/>
       <c r="V508" s="4"/>
       <c r="W508" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X508" s="4" t="s">
         <v>46</v>
@@ -50982,7 +50982,7 @@
       <c r="U509" s="4"/>
       <c r="V509" s="4"/>
       <c r="W509" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X509" s="4" t="s">
         <v>46</v>
@@ -51062,7 +51062,7 @@
         <v>2088</v>
       </c>
       <c r="W510" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X510" s="4" t="s">
         <v>46</v>
@@ -51136,7 +51136,7 @@
       <c r="U511" s="4"/>
       <c r="V511" s="4"/>
       <c r="W511" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X511" s="4" t="s">
         <v>46</v>
@@ -51212,7 +51212,7 @@
       <c r="U512" s="4"/>
       <c r="V512" s="4"/>
       <c r="W512" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X512" s="4" t="s">
         <v>46</v>
@@ -51288,7 +51288,7 @@
       <c r="U513" s="4"/>
       <c r="V513" s="4"/>
       <c r="W513" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X513" s="4" t="s">
         <v>46</v>
@@ -51366,7 +51366,7 @@
         <v>2088</v>
       </c>
       <c r="W514" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X514" s="4" t="s">
         <v>46</v>
@@ -51446,7 +51446,7 @@
         <v>45</v>
       </c>
       <c r="W515" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X515" s="4" t="s">
         <v>46</v>
@@ -51526,7 +51526,7 @@
         <v>146</v>
       </c>
       <c r="W516" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X516" s="4" t="s">
         <v>46</v>
@@ -51600,7 +51600,7 @@
       <c r="U517" s="4"/>
       <c r="V517" s="4"/>
       <c r="W517" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X517" s="4" t="s">
         <v>46</v>
@@ -51680,7 +51680,7 @@
         <v>340</v>
       </c>
       <c r="W518" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X518" s="4" t="s">
         <v>46</v>
@@ -51756,7 +51756,7 @@
       <c r="U519" s="4"/>
       <c r="V519" s="4"/>
       <c r="W519" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X519" s="4" t="s">
         <v>46</v>
@@ -51830,7 +51830,7 @@
       <c r="U520" s="4"/>
       <c r="V520" s="4"/>
       <c r="W520" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X520" s="4" t="s">
         <v>46</v>
@@ -51902,7 +51902,7 @@
       <c r="U521" s="4"/>
       <c r="V521" s="4"/>
       <c r="W521" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X521" s="4" t="s">
         <v>46</v>
@@ -51982,7 +51982,7 @@
         <v>838</v>
       </c>
       <c r="W522" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X522" s="4" t="s">
         <v>46</v>
@@ -52056,7 +52056,7 @@
       <c r="U523" s="4"/>
       <c r="V523" s="4"/>
       <c r="W523" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X523" s="4" t="s">
         <v>322</v>
@@ -52132,7 +52132,7 @@
       <c r="U524" s="4"/>
       <c r="V524" s="4"/>
       <c r="W524" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X524" s="4" t="s">
         <v>46</v>
@@ -52208,7 +52208,7 @@
       <c r="U525" s="4"/>
       <c r="V525" s="4"/>
       <c r="W525" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X525" s="4" t="s">
         <v>46</v>
@@ -52288,7 +52288,7 @@
         <v>130</v>
       </c>
       <c r="W526" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X526" s="4" t="s">
         <v>322</v>
@@ -52366,7 +52366,7 @@
         <v>123</v>
       </c>
       <c r="W527" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X527" s="4" t="s">
         <v>46</v>
@@ -52440,7 +52440,7 @@
       <c r="U528" s="4"/>
       <c r="V528" s="4"/>
       <c r="W528" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X528" s="4" t="s">
         <v>46</v>
@@ -52518,7 +52518,7 @@
         <v>245</v>
       </c>
       <c r="W529" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X529" s="4" t="s">
         <v>46</v>
@@ -52594,7 +52594,7 @@
       <c r="U530" s="4"/>
       <c r="V530" s="4"/>
       <c r="W530" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X530" s="4" t="s">
         <v>46</v>
@@ -52672,7 +52672,7 @@
         <v>224</v>
       </c>
       <c r="W531" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X531" s="4" t="s">
         <v>322</v>
@@ -52752,7 +52752,7 @@
         <v>237</v>
       </c>
       <c r="W532" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X532" s="4" t="s">
         <v>322</v>
@@ -52828,7 +52828,7 @@
       <c r="U533" s="4"/>
       <c r="V533" s="4"/>
       <c r="W533" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X533" s="4" t="s">
         <v>322</v>
@@ -52908,7 +52908,7 @@
         <v>224</v>
       </c>
       <c r="W534" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X534" s="4" t="s">
         <v>322</v>
@@ -52988,7 +52988,7 @@
         <v>340</v>
       </c>
       <c r="W535" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X535" s="4" t="s">
         <v>46</v>
@@ -53064,7 +53064,7 @@
       <c r="U536" s="4"/>
       <c r="V536" s="4"/>
       <c r="W536" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X536" s="4" t="s">
         <v>46</v>
@@ -53138,7 +53138,7 @@
       <c r="U537" s="4"/>
       <c r="V537" s="4"/>
       <c r="W537" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X537" s="4" t="s">
         <v>322</v>
@@ -53212,7 +53212,7 @@
       <c r="U538" s="4"/>
       <c r="V538" s="4"/>
       <c r="W538" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X538" s="4" t="s">
         <v>322</v>
@@ -53290,7 +53290,7 @@
         <v>237</v>
       </c>
       <c r="W539" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X539" s="4" t="s">
         <v>322</v>
@@ -53366,7 +53366,7 @@
       <c r="U540" s="4"/>
       <c r="V540" s="4"/>
       <c r="W540" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X540" s="4" t="s">
         <v>322</v>
@@ -53442,7 +53442,7 @@
       <c r="U541" s="4"/>
       <c r="V541" s="4"/>
       <c r="W541" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X541" s="4" t="s">
         <v>46</v>
@@ -53518,7 +53518,7 @@
       <c r="U542" s="4"/>
       <c r="V542" s="4"/>
       <c r="W542" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X542" s="4" t="s">
         <v>322</v>
@@ -53598,7 +53598,7 @@
         <v>340</v>
       </c>
       <c r="W543" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X543" s="4" t="s">
         <v>322</v>
@@ -53674,7 +53674,7 @@
       <c r="U544" s="4"/>
       <c r="V544" s="4"/>
       <c r="W544" s="4">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X544" s="4" t="s">
         <v>46</v>
@@ -53750,7 +53750,7 @@
       <c r="U545" s="4"/>
       <c r="V545" s="4"/>
       <c r="W545" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X545" s="4" t="s">
         <v>322</v>
@@ -53826,7 +53826,7 @@
       <c r="U546" s="4"/>
       <c r="V546" s="4"/>
       <c r="W546" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X546" s="4" t="s">
         <v>322</v>
@@ -53906,7 +53906,7 @@
         <v>557</v>
       </c>
       <c r="W547" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X547" s="4" t="s">
         <v>46</v>
@@ -53982,7 +53982,7 @@
       <c r="U548" s="4"/>
       <c r="V548" s="4"/>
       <c r="W548" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X548" s="4" t="s">
         <v>322</v>
@@ -54056,7 +54056,7 @@
       <c r="U549" s="4"/>
       <c r="V549" s="4"/>
       <c r="W549" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X549" s="4" t="s">
         <v>46</v>
@@ -54132,7 +54132,7 @@
       <c r="U550" s="4"/>
       <c r="V550" s="4"/>
       <c r="W550" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X550" s="4" t="s">
         <v>46</v>
@@ -54212,7 +54212,7 @@
         <v>2088</v>
       </c>
       <c r="W551" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X551" s="4" t="s">
         <v>46</v>
@@ -54292,7 +54292,7 @@
         <v>557</v>
       </c>
       <c r="W552" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X552" s="4" t="s">
         <v>46</v>
@@ -54372,7 +54372,7 @@
         <v>130</v>
       </c>
       <c r="W553" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X553" s="4" t="s">
         <v>46</v>
@@ -54452,7 +54452,7 @@
         <v>206</v>
       </c>
       <c r="W554" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X554" s="4" t="s">
         <v>46</v>
@@ -54528,7 +54528,7 @@
       <c r="U555" s="4"/>
       <c r="V555" s="4"/>
       <c r="W555" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X555" s="4" t="s">
         <v>46</v>
@@ -54608,7 +54608,7 @@
         <v>2088</v>
       </c>
       <c r="W556" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X556" s="4" t="s">
         <v>46</v>
@@ -54686,7 +54686,7 @@
         <v>206</v>
       </c>
       <c r="W557" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X557" s="4" t="s">
         <v>46</v>
@@ -54766,7 +54766,7 @@
         <v>2250</v>
       </c>
       <c r="W558" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X558" s="4" t="s">
         <v>46</v>
@@ -54842,7 +54842,7 @@
       <c r="U559" s="4"/>
       <c r="V559" s="4"/>
       <c r="W559" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X559" s="4" t="s">
         <v>46</v>
@@ -54918,7 +54918,7 @@
       <c r="U560" s="4"/>
       <c r="V560" s="4"/>
       <c r="W560" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X560" s="4" t="s">
         <v>46</v>
@@ -54994,7 +54994,7 @@
       <c r="U561" s="4"/>
       <c r="V561" s="4"/>
       <c r="W561" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X561" s="4" t="s">
         <v>46</v>
@@ -55070,7 +55070,7 @@
       <c r="U562" s="4"/>
       <c r="V562" s="4"/>
       <c r="W562" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X562" s="4" t="s">
         <v>46</v>
@@ -55148,7 +55148,7 @@
         <v>224</v>
       </c>
       <c r="W563" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X563" s="4" t="s">
         <v>46</v>
@@ -55224,7 +55224,7 @@
       <c r="U564" s="4"/>
       <c r="V564" s="4"/>
       <c r="W564" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X564" s="4" t="s">
         <v>46</v>
@@ -55300,7 +55300,7 @@
       <c r="U565" s="4"/>
       <c r="V565" s="4"/>
       <c r="W565" s="4">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="X565" s="4" t="s">
         <v>46</v>
@@ -55376,7 +55376,7 @@
       <c r="U566" s="4"/>
       <c r="V566" s="4"/>
       <c r="W566" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X566" s="4" t="s">
         <v>46</v>
@@ -55454,7 +55454,7 @@
         <v>721</v>
       </c>
       <c r="W567" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X567" s="4" t="s">
         <v>46</v>
@@ -55530,7 +55530,7 @@
         <v>602</v>
       </c>
       <c r="W568" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X568" s="4" t="s">
         <v>46</v>
@@ -55606,7 +55606,7 @@
       <c r="U569" s="4"/>
       <c r="V569" s="4"/>
       <c r="W569" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X569" s="4" t="s">
         <v>46</v>
@@ -55686,7 +55686,7 @@
         <v>206</v>
       </c>
       <c r="W570" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X570" s="4" t="s">
         <v>46</v>
@@ -55766,7 +55766,7 @@
         <v>340</v>
       </c>
       <c r="W571" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X571" s="4" t="s">
         <v>46</v>
@@ -55842,7 +55842,7 @@
       <c r="U572" s="4"/>
       <c r="V572" s="4"/>
       <c r="W572" s="4">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="X572" s="4" t="s">
         <v>46</v>
@@ -55918,7 +55918,7 @@
       <c r="U573" s="4"/>
       <c r="V573" s="4"/>
       <c r="W573" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X573" s="4" t="s">
         <v>46</v>
@@ -55998,7 +55998,7 @@
         <v>224</v>
       </c>
       <c r="W574" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X574" s="4" t="s">
         <v>46</v>
@@ -56072,7 +56072,7 @@
         <v>130</v>
       </c>
       <c r="W575" s="4">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="X575" s="4" t="s">
         <v>46</v>
@@ -56146,7 +56146,7 @@
         <v>74</v>
       </c>
       <c r="W576" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X576" s="4" t="s">
         <v>46</v>
@@ -56224,7 +56224,7 @@
         <v>2320</v>
       </c>
       <c r="W577" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X577" s="4" t="s">
         <v>46</v>
@@ -56300,7 +56300,7 @@
       <c r="U578" s="4"/>
       <c r="V578" s="4"/>
       <c r="W578" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X578" s="4" t="s">
         <v>46</v>
@@ -56378,7 +56378,7 @@
         <v>66</v>
       </c>
       <c r="W579" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X579" s="4" t="s">
         <v>322</v>
@@ -56446,7 +56446,7 @@
       <c r="U580" s="4"/>
       <c r="V580" s="4"/>
       <c r="W580" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X580" s="4" t="s">
         <v>46</v>
@@ -56520,7 +56520,7 @@
       <c r="U581" s="4"/>
       <c r="V581" s="4"/>
       <c r="W581" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X581" s="4" t="s">
         <v>322</v>
@@ -56600,7 +56600,7 @@
         <v>224</v>
       </c>
       <c r="W582" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X582" s="4" t="s">
         <v>46</v>
@@ -56680,7 +56680,7 @@
         <v>1741</v>
       </c>
       <c r="W583" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X583" s="4" t="s">
         <v>46</v>
@@ -56760,7 +56760,7 @@
         <v>245</v>
       </c>
       <c r="W584" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X584" s="4" t="s">
         <v>46</v>
@@ -56838,7 +56838,7 @@
         <v>237</v>
       </c>
       <c r="W585" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X585" s="4" t="s">
         <v>46</v>
@@ -56914,7 +56914,7 @@
       <c r="U586" s="4"/>
       <c r="V586" s="4"/>
       <c r="W586" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X586" s="4" t="s">
         <v>46</v>
@@ -56990,7 +56990,7 @@
       <c r="U587" s="4"/>
       <c r="V587" s="4"/>
       <c r="W587" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X587" s="4" t="s">
         <v>46</v>
@@ -57068,7 +57068,7 @@
         <v>237</v>
       </c>
       <c r="W588" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X588" s="4" t="s">
         <v>46</v>
@@ -57144,7 +57144,7 @@
       <c r="U589" s="4"/>
       <c r="V589" s="4"/>
       <c r="W589" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X589" s="4" t="s">
         <v>322</v>
@@ -57220,7 +57220,7 @@
       <c r="U590" s="4"/>
       <c r="V590" s="4"/>
       <c r="W590" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X590" s="4" t="s">
         <v>46</v>
@@ -57294,7 +57294,7 @@
       <c r="U591" s="4"/>
       <c r="V591" s="4"/>
       <c r="W591" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X591" s="4" t="s">
         <v>46</v>
@@ -57370,7 +57370,7 @@
       <c r="U592" s="4"/>
       <c r="V592" s="4"/>
       <c r="W592" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X592" s="4" t="s">
         <v>322</v>
@@ -57448,7 +57448,7 @@
         <v>1248</v>
       </c>
       <c r="W593" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X593" s="4" t="s">
         <v>46</v>
@@ -57524,7 +57524,7 @@
       <c r="U594" s="4"/>
       <c r="V594" s="4"/>
       <c r="W594" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X594" s="4" t="s">
         <v>46</v>
@@ -57602,7 +57602,7 @@
         <v>45</v>
       </c>
       <c r="W595" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X595" s="4" t="s">
         <v>46</v>
@@ -57678,7 +57678,7 @@
       <c r="U596" s="4"/>
       <c r="V596" s="4"/>
       <c r="W596" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X596" s="4" t="s">
         <v>46</v>
@@ -57752,7 +57752,7 @@
         <v>356</v>
       </c>
       <c r="W597" s="4">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X597" s="4" t="s">
         <v>46</v>
@@ -57826,7 +57826,7 @@
         <v>74</v>
       </c>
       <c r="W598" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X598" s="4" t="s">
         <v>46</v>
@@ -57900,7 +57900,7 @@
         <v>74</v>
       </c>
       <c r="W599" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X599" s="4" t="s">
         <v>46</v>
@@ -57974,7 +57974,7 @@
       <c r="U600" s="4"/>
       <c r="V600" s="4"/>
       <c r="W600" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X600" s="4" t="s">
         <v>322</v>
@@ -58050,7 +58050,7 @@
       <c r="U601" s="4"/>
       <c r="V601" s="4"/>
       <c r="W601" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X601" s="4" t="s">
         <v>46</v>
@@ -58126,7 +58126,7 @@
       <c r="U602" s="4"/>
       <c r="V602" s="4"/>
       <c r="W602" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X602" s="4" t="s">
         <v>46</v>
@@ -58206,7 +58206,7 @@
         <v>224</v>
       </c>
       <c r="W603" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X603" s="4" t="s">
         <v>46</v>
@@ -58284,7 +58284,7 @@
         <v>224</v>
       </c>
       <c r="W604" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X604" s="4" t="s">
         <v>46</v>
@@ -58364,7 +58364,7 @@
         <v>224</v>
       </c>
       <c r="W605" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X605" s="4" t="s">
         <v>46</v>
@@ -58438,7 +58438,7 @@
       <c r="U606" s="4"/>
       <c r="V606" s="4"/>
       <c r="W606" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X606" s="4" t="s">
         <v>46</v>
@@ -58514,7 +58514,7 @@
       <c r="U607" s="4"/>
       <c r="V607" s="4"/>
       <c r="W607" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X607" s="4" t="s">
         <v>46</v>
@@ -58592,7 +58592,7 @@
         <v>237</v>
       </c>
       <c r="W608" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X608" s="4" t="s">
         <v>46</v>
@@ -58670,7 +58670,7 @@
         <v>340</v>
       </c>
       <c r="W609" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X609" s="4" t="s">
         <v>46</v>
@@ -58750,7 +58750,7 @@
         <v>245</v>
       </c>
       <c r="W610" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X610" s="4" t="s">
         <v>46</v>
@@ -58830,7 +58830,7 @@
         <v>130</v>
       </c>
       <c r="W611" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X611" s="4" t="s">
         <v>46</v>
@@ -58904,7 +58904,7 @@
       <c r="U612" s="4"/>
       <c r="V612" s="4"/>
       <c r="W612" s="4">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="X612" s="4" t="s">
         <v>46</v>
@@ -58980,7 +58980,7 @@
       <c r="U613" s="4"/>
       <c r="V613" s="4"/>
       <c r="W613" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X613" s="4" t="s">
         <v>46</v>
@@ -59060,7 +59060,7 @@
         <v>340</v>
       </c>
       <c r="W614" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X614" s="4" t="s">
         <v>46</v>
@@ -59136,7 +59136,7 @@
       <c r="U615" s="4"/>
       <c r="V615" s="4"/>
       <c r="W615" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X615" s="4" t="s">
         <v>46</v>
@@ -59216,7 +59216,7 @@
         <v>224</v>
       </c>
       <c r="W616" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X616" s="4" t="s">
         <v>46</v>
@@ -59292,7 +59292,7 @@
       <c r="U617" s="4"/>
       <c r="V617" s="4"/>
       <c r="W617" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X617" s="4" t="s">
         <v>46</v>
@@ -59362,7 +59362,7 @@
       <c r="U618" s="4"/>
       <c r="V618" s="4"/>
       <c r="W618" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X618" s="4" t="s">
         <v>46</v>
@@ -59430,7 +59430,7 @@
       <c r="U619" s="4"/>
       <c r="V619" s="4"/>
       <c r="W619" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X619" s="4" t="s">
         <v>46</v>
@@ -59510,7 +59510,7 @@
         <v>245</v>
       </c>
       <c r="W620" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X620" s="4" t="s">
         <v>46</v>
@@ -59590,7 +59590,7 @@
         <v>45</v>
       </c>
       <c r="W621" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X621" s="4" t="s">
         <v>46</v>
@@ -59670,7 +59670,7 @@
         <v>130</v>
       </c>
       <c r="W622" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X622" s="4" t="s">
         <v>46</v>
@@ -59750,7 +59750,7 @@
         <v>206</v>
       </c>
       <c r="W623" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X623" s="4" t="s">
         <v>46</v>
@@ -59830,7 +59830,7 @@
         <v>130</v>
       </c>
       <c r="W624" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X624" s="4" t="s">
         <v>46</v>
@@ -59910,7 +59910,7 @@
         <v>45</v>
       </c>
       <c r="W625" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X625" s="4" t="s">
         <v>46</v>
@@ -59986,7 +59986,7 @@
       <c r="U626" s="4"/>
       <c r="V626" s="4"/>
       <c r="W626" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X626" s="4" t="s">
         <v>46</v>
@@ -60062,7 +60062,7 @@
       <c r="U627" s="4"/>
       <c r="V627" s="4"/>
       <c r="W627" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X627" s="4" t="s">
         <v>46</v>
@@ -60138,7 +60138,7 @@
       <c r="U628" s="4"/>
       <c r="V628" s="4"/>
       <c r="W628" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X628" s="4" t="s">
         <v>46</v>
@@ -60214,7 +60214,7 @@
       <c r="U629" s="4"/>
       <c r="V629" s="4"/>
       <c r="W629" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X629" s="4" t="s">
         <v>46</v>
@@ -60290,7 +60290,7 @@
       <c r="U630" s="4"/>
       <c r="V630" s="4"/>
       <c r="W630" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X630" s="4" t="s">
         <v>46</v>
@@ -60368,7 +60368,7 @@
         <v>557</v>
       </c>
       <c r="W631" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X631" s="4" t="s">
         <v>46</v>
@@ -60448,7 +60448,7 @@
         <v>130</v>
       </c>
       <c r="W632" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X632" s="4" t="s">
         <v>46</v>
@@ -60524,7 +60524,7 @@
       <c r="U633" s="4"/>
       <c r="V633" s="4"/>
       <c r="W633" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X633" s="4" t="s">
         <v>46</v>
@@ -60604,7 +60604,7 @@
         <v>45</v>
       </c>
       <c r="W634" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X634" s="4" t="s">
         <v>46</v>
@@ -60684,7 +60684,7 @@
         <v>2544</v>
       </c>
       <c r="W635" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X635" s="4" t="s">
         <v>46</v>
@@ -60760,7 +60760,7 @@
       <c r="U636" s="4"/>
       <c r="V636" s="4"/>
       <c r="W636" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X636" s="4" t="s">
         <v>46</v>
@@ -60836,7 +60836,7 @@
       <c r="U637" s="4"/>
       <c r="V637" s="4"/>
       <c r="W637" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X637" s="4" t="s">
         <v>322</v>
@@ -60912,7 +60912,7 @@
       <c r="U638" s="4"/>
       <c r="V638" s="4"/>
       <c r="W638" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X638" s="4" t="s">
         <v>46</v>
@@ -60990,7 +60990,7 @@
         <v>45</v>
       </c>
       <c r="W639" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X639" s="4" t="s">
         <v>46</v>
@@ -61070,7 +61070,7 @@
         <v>224</v>
       </c>
       <c r="W640" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X640" s="4" t="s">
         <v>46</v>
@@ -61140,7 +61140,7 @@
       <c r="U641" s="4"/>
       <c r="V641" s="4"/>
       <c r="W641" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X641" s="4" t="s">
         <v>46</v>
@@ -61208,7 +61208,7 @@
       <c r="U642" s="4"/>
       <c r="V642" s="4"/>
       <c r="W642" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X642" s="4" t="s">
         <v>46</v>
@@ -61276,7 +61276,7 @@
       <c r="U643" s="4"/>
       <c r="V643" s="4"/>
       <c r="W643" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X643" s="4" t="s">
         <v>46</v>
@@ -61356,7 +61356,7 @@
         <v>45</v>
       </c>
       <c r="W644" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X644" s="4" t="s">
         <v>46</v>
@@ -61436,7 +61436,7 @@
         <v>340</v>
       </c>
       <c r="W645" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X645" s="4" t="s">
         <v>46</v>
@@ -61516,7 +61516,7 @@
         <v>340</v>
       </c>
       <c r="W646" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X646" s="4" t="s">
         <v>46</v>
@@ -61590,7 +61590,7 @@
       <c r="U647" s="4"/>
       <c r="V647" s="4"/>
       <c r="W647" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X647" s="4" t="s">
         <v>46</v>
@@ -61666,7 +61666,7 @@
       <c r="U648" s="4"/>
       <c r="V648" s="4"/>
       <c r="W648" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X648" s="4" t="s">
         <v>46</v>
@@ -61746,7 +61746,7 @@
         <v>224</v>
       </c>
       <c r="W649" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X649" s="4" t="s">
         <v>46</v>
@@ -61822,7 +61822,7 @@
       <c r="U650" s="4"/>
       <c r="V650" s="4"/>
       <c r="W650" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="X650" s="4" t="s">
         <v>46</v>
@@ -61902,7 +61902,7 @@
         <v>237</v>
       </c>
       <c r="W651" s="4">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="X651" s="4" t="s">
         <v>46</v>
@@ -61982,7 +61982,7 @@
         <v>892</v>
       </c>
       <c r="W652" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X652" s="4" t="s">
         <v>46</v>
@@ -62060,7 +62060,7 @@
         <v>2612</v>
       </c>
       <c r="W653" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X653" s="4" t="s">
         <v>46</v>
@@ -62140,7 +62140,7 @@
         <v>2617</v>
       </c>
       <c r="W654" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X654" s="4" t="s">
         <v>46</v>
@@ -62220,7 +62220,7 @@
         <v>557</v>
       </c>
       <c r="W655" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X655" s="4" t="s">
         <v>322</v>
@@ -62298,7 +62298,7 @@
         <v>2627</v>
       </c>
       <c r="W656" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X656" s="4" t="s">
         <v>46</v>
@@ -62376,7 +62376,7 @@
         <v>224</v>
       </c>
       <c r="W657" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X657" s="4" t="s">
         <v>46</v>
@@ -62452,7 +62452,7 @@
       <c r="U658" s="4"/>
       <c r="V658" s="4"/>
       <c r="W658" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X658" s="4" t="s">
         <v>46</v>
@@ -62528,7 +62528,7 @@
       <c r="U659" s="4"/>
       <c r="V659" s="4"/>
       <c r="W659" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X659" s="4" t="s">
         <v>322</v>
@@ -62604,7 +62604,7 @@
       <c r="U660" s="4"/>
       <c r="V660" s="4"/>
       <c r="W660" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X660" s="4" t="s">
         <v>46</v>
@@ -62684,7 +62684,7 @@
         <v>237</v>
       </c>
       <c r="W661" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X661" s="4" t="s">
         <v>46</v>
@@ -62762,7 +62762,7 @@
         <v>237</v>
       </c>
       <c r="W662" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X662" s="4" t="s">
         <v>46</v>
@@ -62838,7 +62838,7 @@
       <c r="U663" s="4"/>
       <c r="V663" s="4"/>
       <c r="W663" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X663" s="4" t="s">
         <v>322</v>
@@ -62914,7 +62914,7 @@
       <c r="U664" s="4"/>
       <c r="V664" s="4"/>
       <c r="W664" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X664" s="4" t="s">
         <v>322</v>
@@ -62994,7 +62994,7 @@
         <v>721</v>
       </c>
       <c r="W665" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X665" s="4" t="s">
         <v>46</v>
@@ -63066,7 +63066,7 @@
         <v>245</v>
       </c>
       <c r="W666" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X666" s="4" t="s">
         <v>46</v>
@@ -63140,7 +63140,7 @@
       <c r="U667" s="4"/>
       <c r="V667" s="4"/>
       <c r="W667" s="4">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="X667" s="4" t="s">
         <v>46</v>
@@ -63220,7 +63220,7 @@
         <v>340</v>
       </c>
       <c r="W668" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X668" s="4" t="s">
         <v>46</v>
@@ -63296,7 +63296,7 @@
       <c r="U669" s="4"/>
       <c r="V669" s="4"/>
       <c r="W669" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X669" s="4" t="s">
         <v>46</v>
@@ -63370,7 +63370,7 @@
       <c r="U670" s="4"/>
       <c r="V670" s="4"/>
       <c r="W670" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X670" s="4" t="s">
         <v>46</v>
@@ -63450,7 +63450,7 @@
         <v>2690</v>
       </c>
       <c r="W671" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X671" s="4" t="s">
         <v>46</v>
@@ -63530,7 +63530,7 @@
         <v>130</v>
       </c>
       <c r="W672" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X672" s="4" t="s">
         <v>322</v>
@@ -63608,7 +63608,7 @@
         <v>340</v>
       </c>
       <c r="W673" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X673" s="4" t="s">
         <v>46</v>
@@ -63688,7 +63688,7 @@
         <v>224</v>
       </c>
       <c r="W674" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X674" s="4" t="s">
         <v>46</v>
@@ -63762,7 +63762,7 @@
       <c r="U675" s="4"/>
       <c r="V675" s="4"/>
       <c r="W675" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X675" s="4" t="s">
         <v>46</v>
@@ -63838,7 +63838,7 @@
         <v>130</v>
       </c>
       <c r="W676" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X676" s="4" t="s">
         <v>46</v>
@@ -63908,7 +63908,7 @@
       <c r="U677" s="4"/>
       <c r="V677" s="4"/>
       <c r="W677" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X677" s="4" t="s">
         <v>46</v>
@@ -63986,7 +63986,7 @@
         <v>340</v>
       </c>
       <c r="W678" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X678" s="4" t="s">
         <v>46</v>
@@ -64062,7 +64062,7 @@
       <c r="U679" s="4"/>
       <c r="V679" s="4"/>
       <c r="W679" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X679" s="4" t="s">
         <v>46</v>
@@ -64140,7 +64140,7 @@
         <v>224</v>
       </c>
       <c r="W680" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X680" s="4" t="s">
         <v>46</v>
@@ -64216,7 +64216,7 @@
       <c r="U681" s="4"/>
       <c r="V681" s="4"/>
       <c r="W681" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X681" s="4" t="s">
         <v>46</v>
@@ -64296,7 +64296,7 @@
         <v>340</v>
       </c>
       <c r="W682" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X682" s="4" t="s">
         <v>46</v>
@@ -64376,7 +64376,7 @@
         <v>224</v>
       </c>
       <c r="W683" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X683" s="4" t="s">
         <v>322</v>
@@ -64452,7 +64452,7 @@
       <c r="U684" s="4"/>
       <c r="V684" s="4"/>
       <c r="W684" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X684" s="4" t="s">
         <v>46</v>
@@ -64532,7 +64532,7 @@
         <v>2745</v>
       </c>
       <c r="W685" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X685" s="4" t="s">
         <v>46</v>
@@ -64612,7 +64612,7 @@
         <v>130</v>
       </c>
       <c r="W686" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X686" s="4" t="s">
         <v>322</v>
@@ -64686,7 +64686,7 @@
       <c r="U687" s="4"/>
       <c r="V687" s="4"/>
       <c r="W687" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X687" s="4" t="s">
         <v>46</v>
@@ -64760,7 +64760,7 @@
       <c r="U688" s="4"/>
       <c r="V688" s="4"/>
       <c r="W688" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X688" s="4" t="s">
         <v>46</v>
@@ -64832,7 +64832,7 @@
       <c r="U689" s="4"/>
       <c r="V689" s="4"/>
       <c r="W689" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X689" s="4" t="s">
         <v>46</v>
@@ -64908,7 +64908,7 @@
       <c r="U690" s="4"/>
       <c r="V690" s="4"/>
       <c r="W690" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X690" s="4" t="s">
         <v>46</v>
@@ -64988,7 +64988,7 @@
         <v>245</v>
       </c>
       <c r="W691" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X691" s="4" t="s">
         <v>46</v>
@@ -65068,7 +65068,7 @@
         <v>130</v>
       </c>
       <c r="W692" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X692" s="4" t="s">
         <v>46</v>
@@ -65144,7 +65144,7 @@
       <c r="U693" s="4"/>
       <c r="V693" s="4"/>
       <c r="W693" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X693" s="4" t="s">
         <v>46</v>
@@ -65212,7 +65212,7 @@
       <c r="U694" s="4"/>
       <c r="V694" s="4"/>
       <c r="W694" s="4">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="X694" s="4" t="s">
         <v>46</v>
@@ -65286,7 +65286,7 @@
       <c r="U695" s="4"/>
       <c r="V695" s="4"/>
       <c r="W695" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X695" s="4" t="s">
         <v>46</v>
@@ -65362,7 +65362,7 @@
       <c r="U696" s="4"/>
       <c r="V696" s="4"/>
       <c r="W696" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X696" s="4" t="s">
         <v>46</v>
@@ -65442,7 +65442,7 @@
         <v>340</v>
       </c>
       <c r="W697" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X697" s="4" t="s">
         <v>46</v>
@@ -65518,7 +65518,7 @@
       <c r="U698" s="4"/>
       <c r="V698" s="4"/>
       <c r="W698" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X698" s="4" t="s">
         <v>46</v>
@@ -65594,7 +65594,7 @@
       <c r="U699" s="4"/>
       <c r="V699" s="4"/>
       <c r="W699" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X699" s="4" t="s">
         <v>46</v>
@@ -65670,7 +65670,7 @@
       <c r="U700" s="4"/>
       <c r="V700" s="4"/>
       <c r="W700" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X700" s="4" t="s">
         <v>46</v>
@@ -65750,7 +65750,7 @@
         <v>340</v>
       </c>
       <c r="W701" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X701" s="4" t="s">
         <v>46</v>
@@ -65826,7 +65826,7 @@
       <c r="U702" s="4"/>
       <c r="V702" s="4"/>
       <c r="W702" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X702" s="4" t="s">
         <v>46</v>
@@ -65906,7 +65906,7 @@
         <v>130</v>
       </c>
       <c r="W703" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X703" s="4" t="s">
         <v>46</v>
@@ -65982,7 +65982,7 @@
       <c r="U704" s="4"/>
       <c r="V704" s="4"/>
       <c r="W704" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X704" s="4" t="s">
         <v>46</v>
@@ -66056,7 +66056,7 @@
       <c r="U705" s="4"/>
       <c r="V705" s="4"/>
       <c r="W705" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X705" s="4" t="s">
         <v>322</v>
@@ -66130,7 +66130,7 @@
       <c r="U706" s="4"/>
       <c r="V706" s="4"/>
       <c r="W706" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X706" s="4" t="s">
         <v>46</v>
@@ -66204,7 +66204,7 @@
       <c r="U707" s="4"/>
       <c r="V707" s="4"/>
       <c r="W707" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X707" s="4" t="s">
         <v>322</v>
@@ -66278,7 +66278,7 @@
       <c r="U708" s="4"/>
       <c r="V708" s="4"/>
       <c r="W708" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X708" s="4" t="s">
         <v>322</v>
@@ -66352,7 +66352,7 @@
       <c r="U709" s="4"/>
       <c r="V709" s="4"/>
       <c r="W709" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X709" s="4" t="s">
         <v>46</v>
@@ -66428,7 +66428,7 @@
       <c r="U710" s="4"/>
       <c r="V710" s="4"/>
       <c r="W710" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X710" s="4" t="s">
         <v>46</v>
@@ -66498,7 +66498,7 @@
       <c r="U711" s="4"/>
       <c r="V711" s="4"/>
       <c r="W711" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X711" s="4" t="s">
         <v>46</v>
@@ -66572,7 +66572,7 @@
       <c r="U712" s="4"/>
       <c r="V712" s="4"/>
       <c r="W712" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X712" s="4" t="s">
         <v>322</v>
@@ -66646,7 +66646,7 @@
       <c r="U713" s="4"/>
       <c r="V713" s="4"/>
       <c r="W713" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X713" s="4" t="s">
         <v>46</v>
@@ -66720,7 +66720,7 @@
       <c r="U714" s="4"/>
       <c r="V714" s="4"/>
       <c r="W714" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X714" s="4" t="s">
         <v>46</v>
@@ -66798,7 +66798,7 @@
         <v>2849</v>
       </c>
       <c r="W715" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X715" s="4" t="s">
         <v>322</v>
@@ -66878,7 +66878,7 @@
         <v>2849</v>
       </c>
       <c r="W716" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X716" s="4" t="s">
         <v>46</v>
@@ -66954,7 +66954,7 @@
       <c r="U717" s="4"/>
       <c r="V717" s="4"/>
       <c r="W717" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X717" s="4" t="s">
         <v>46</v>
@@ -67030,7 +67030,7 @@
       <c r="U718" s="4"/>
       <c r="V718" s="4"/>
       <c r="W718" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X718" s="4" t="s">
         <v>46</v>
@@ -67104,7 +67104,7 @@
       <c r="U719" s="4"/>
       <c r="V719" s="4"/>
       <c r="W719" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X719" s="4" t="s">
         <v>46</v>
@@ -67184,7 +67184,7 @@
         <v>206</v>
       </c>
       <c r="W720" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X720" s="4" t="s">
         <v>46</v>
@@ -67254,7 +67254,7 @@
       <c r="U721" s="4"/>
       <c r="V721" s="4"/>
       <c r="W721" s="4">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X721" s="4" t="s">
         <v>46</v>
@@ -67330,7 +67330,7 @@
         <v>224</v>
       </c>
       <c r="W722" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X722" s="4" t="s">
         <v>46</v>
@@ -67410,7 +67410,7 @@
         <v>237</v>
       </c>
       <c r="W723" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X723" s="4" t="s">
         <v>46</v>
@@ -67490,7 +67490,7 @@
         <v>224</v>
       </c>
       <c r="W724" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X724" s="4" t="s">
         <v>46</v>
@@ -67566,7 +67566,7 @@
       <c r="U725" s="4"/>
       <c r="V725" s="4"/>
       <c r="W725" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X725" s="4" t="s">
         <v>46</v>
@@ -67644,7 +67644,7 @@
         <v>224</v>
       </c>
       <c r="W726" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X726" s="4" t="s">
         <v>322</v>
@@ -67722,7 +67722,7 @@
         <v>224</v>
       </c>
       <c r="W727" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X727" s="4" t="s">
         <v>322</v>
@@ -67798,7 +67798,7 @@
       <c r="U728" s="4"/>
       <c r="V728" s="4"/>
       <c r="W728" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X728" s="4" t="s">
         <v>46</v>
@@ -67878,7 +67878,7 @@
         <v>45</v>
       </c>
       <c r="W729" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X729" s="4" t="s">
         <v>322</v>
@@ -67956,7 +67956,7 @@
         <v>340</v>
       </c>
       <c r="W730" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X730" s="4" t="s">
         <v>322</v>
@@ -68030,7 +68030,7 @@
       <c r="U731" s="4"/>
       <c r="V731" s="4"/>
       <c r="W731" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X731" s="4" t="s">
         <v>322</v>
@@ -68108,7 +68108,7 @@
         <v>237</v>
       </c>
       <c r="W732" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X732" s="4" t="s">
         <v>322</v>
@@ -68188,7 +68188,7 @@
         <v>340</v>
       </c>
       <c r="W733" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X733" s="4" t="s">
         <v>322</v>
@@ -68264,7 +68264,7 @@
       <c r="U734" s="4"/>
       <c r="V734" s="4"/>
       <c r="W734" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X734" s="4" t="s">
         <v>322</v>
@@ -68338,7 +68338,7 @@
       <c r="U735" s="4"/>
       <c r="V735" s="4"/>
       <c r="W735" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X735" s="4" t="s">
         <v>322</v>
@@ -68418,7 +68418,7 @@
         <v>45</v>
       </c>
       <c r="W736" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X736" s="4" t="s">
         <v>322</v>
@@ -68494,7 +68494,7 @@
       <c r="U737" s="4"/>
       <c r="V737" s="4"/>
       <c r="W737" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X737" s="4" t="s">
         <v>46</v>
@@ -68570,7 +68570,7 @@
       <c r="U738" s="4"/>
       <c r="V738" s="4"/>
       <c r="W738" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X738" s="4" t="s">
         <v>46</v>
@@ -68650,7 +68650,7 @@
         <v>237</v>
       </c>
       <c r="W739" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X739" s="4" t="s">
         <v>46</v>
@@ -68728,7 +68728,7 @@
         <v>2942</v>
       </c>
       <c r="W740" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X740" s="4" t="s">
         <v>46</v>
@@ -68802,7 +68802,7 @@
       <c r="U741" s="4"/>
       <c r="V741" s="4"/>
       <c r="W741" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X741" s="4" t="s">
         <v>46</v>
@@ -68878,7 +68878,7 @@
       <c r="U742" s="4"/>
       <c r="V742" s="4"/>
       <c r="W742" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X742" s="4" t="s">
         <v>46</v>
@@ -68958,7 +68958,7 @@
         <v>245</v>
       </c>
       <c r="W743" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X743" s="4" t="s">
         <v>322</v>
@@ -69036,7 +69036,7 @@
         <v>237</v>
       </c>
       <c r="W744" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X744" s="4" t="s">
         <v>46</v>
@@ -69114,7 +69114,7 @@
         <v>45</v>
       </c>
       <c r="W745" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X745" s="4" t="s">
         <v>322</v>
@@ -69186,7 +69186,7 @@
       <c r="U746" s="4"/>
       <c r="V746" s="4"/>
       <c r="W746" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X746" s="4" t="s">
         <v>322</v>
@@ -69260,7 +69260,7 @@
       <c r="U747" s="4"/>
       <c r="V747" s="4"/>
       <c r="W747" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X747" s="4" t="s">
         <v>46</v>
@@ -69336,7 +69336,7 @@
       <c r="U748" s="4"/>
       <c r="V748" s="4"/>
       <c r="W748" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X748" s="4" t="s">
         <v>46</v>
@@ -69412,7 +69412,7 @@
       <c r="U749" s="4"/>
       <c r="V749" s="4"/>
       <c r="W749" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X749" s="4" t="s">
         <v>46</v>
@@ -69488,7 +69488,7 @@
       <c r="U750" s="4"/>
       <c r="V750" s="4"/>
       <c r="W750" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X750" s="4" t="s">
         <v>46</v>
@@ -69568,7 +69568,7 @@
         <v>245</v>
       </c>
       <c r="W751" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X751" s="4" t="s">
         <v>46</v>
@@ -69644,7 +69644,7 @@
         <v>1248</v>
       </c>
       <c r="W752" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X752" s="4" t="s">
         <v>322</v>
@@ -69724,7 +69724,7 @@
         <v>74</v>
       </c>
       <c r="W753" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X753" s="4" t="s">
         <v>46</v>
@@ -69800,7 +69800,7 @@
       <c r="U754" s="4"/>
       <c r="V754" s="4"/>
       <c r="W754" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X754" s="4" t="s">
         <v>46</v>
@@ -69874,7 +69874,7 @@
       <c r="U755" s="4"/>
       <c r="V755" s="4"/>
       <c r="W755" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X755" s="4" t="s">
         <v>46</v>
@@ -69948,7 +69948,7 @@
       <c r="U756" s="4"/>
       <c r="V756" s="4"/>
       <c r="W756" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X756" s="4" t="s">
         <v>46</v>
@@ -70028,7 +70028,7 @@
         <v>340</v>
       </c>
       <c r="W757" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X757" s="4" t="s">
         <v>46</v>
@@ -70104,7 +70104,7 @@
       <c r="U758" s="4"/>
       <c r="V758" s="4"/>
       <c r="W758" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X758" s="4" t="s">
         <v>46</v>
@@ -70184,7 +70184,7 @@
         <v>224</v>
       </c>
       <c r="W759" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X759" s="4" t="s">
         <v>322</v>
@@ -70260,7 +70260,7 @@
       <c r="U760" s="4"/>
       <c r="V760" s="4"/>
       <c r="W760" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X760" s="4" t="s">
         <v>46</v>
@@ -70336,7 +70336,7 @@
       <c r="U761" s="4"/>
       <c r="V761" s="4"/>
       <c r="W761" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X761" s="4" t="s">
         <v>46</v>
@@ -70416,7 +70416,7 @@
         <v>1498</v>
       </c>
       <c r="W762" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X762" s="4" t="s">
         <v>46</v>
@@ -70490,7 +70490,7 @@
       <c r="U763" s="4"/>
       <c r="V763" s="4"/>
       <c r="W763" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X763" s="4" t="s">
         <v>46</v>
@@ -70566,7 +70566,7 @@
       <c r="U764" s="4"/>
       <c r="V764" s="4"/>
       <c r="W764" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X764" s="4" t="s">
         <v>46</v>
@@ -70646,7 +70646,7 @@
         <v>3038</v>
       </c>
       <c r="W765" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X765" s="4" t="s">
         <v>46</v>
@@ -70722,7 +70722,7 @@
       <c r="U766" s="4"/>
       <c r="V766" s="4"/>
       <c r="W766" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X766" s="4" t="s">
         <v>46</v>
@@ -70798,7 +70798,7 @@
       <c r="U767" s="4"/>
       <c r="V767" s="4"/>
       <c r="W767" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X767" s="4" t="s">
         <v>46</v>
@@ -70872,7 +70872,7 @@
       <c r="U768" s="4"/>
       <c r="V768" s="4"/>
       <c r="W768" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X768" s="4" t="s">
         <v>46</v>
@@ -70950,7 +70950,7 @@
         <v>340</v>
       </c>
       <c r="W769" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X769" s="4" t="s">
         <v>46</v>
@@ -71030,7 +71030,7 @@
         <v>340</v>
       </c>
       <c r="W770" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X770" s="4" t="s">
         <v>46</v>
@@ -71104,7 +71104,7 @@
       <c r="U771" s="4"/>
       <c r="V771" s="4"/>
       <c r="W771" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X771" s="4" t="s">
         <v>322</v>
@@ -71180,7 +71180,7 @@
       <c r="U772" s="4"/>
       <c r="V772" s="4"/>
       <c r="W772" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X772" s="4" t="s">
         <v>46</v>
@@ -71260,7 +71260,7 @@
         <v>130</v>
       </c>
       <c r="W773" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X773" s="4" t="s">
         <v>46</v>
@@ -71340,7 +71340,7 @@
         <v>206</v>
       </c>
       <c r="W774" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X774" s="4" t="s">
         <v>322</v>
@@ -71416,7 +71416,7 @@
       <c r="U775" s="4"/>
       <c r="V775" s="4"/>
       <c r="W775" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X775" s="4" t="s">
         <v>46</v>
@@ -71490,7 +71490,7 @@
       <c r="U776" s="4"/>
       <c r="V776" s="4"/>
       <c r="W776" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X776" s="4" t="s">
         <v>46</v>
@@ -71566,7 +71566,7 @@
       <c r="U777" s="4"/>
       <c r="V777" s="4"/>
       <c r="W777" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X777" s="4" t="s">
         <v>46</v>
@@ -71640,7 +71640,7 @@
       <c r="U778" s="4"/>
       <c r="V778" s="4"/>
       <c r="W778" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X778" s="4" t="s">
         <v>46</v>
@@ -71718,7 +71718,7 @@
         <v>340</v>
       </c>
       <c r="W779" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X779" s="4" t="s">
         <v>46</v>
@@ -71798,7 +71798,7 @@
         <v>2849</v>
       </c>
       <c r="W780" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X780" s="4" t="s">
         <v>46</v>
@@ -71878,7 +71878,7 @@
         <v>45</v>
       </c>
       <c r="W781" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X781" s="4" t="s">
         <v>322</v>
@@ -71954,7 +71954,7 @@
       <c r="U782" s="4"/>
       <c r="V782" s="4"/>
       <c r="W782" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X782" s="4" t="s">
         <v>46</v>
@@ -72034,7 +72034,7 @@
         <v>2849</v>
       </c>
       <c r="W783" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X783" s="4" t="s">
         <v>322</v>
@@ -72114,7 +72114,7 @@
         <v>356</v>
       </c>
       <c r="W784" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X784" s="4" t="s">
         <v>46</v>
@@ -72190,7 +72190,7 @@
       <c r="U785" s="4"/>
       <c r="V785" s="4"/>
       <c r="W785" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X785" s="4" t="s">
         <v>46</v>
@@ -72268,7 +72268,7 @@
         <v>45</v>
       </c>
       <c r="W786" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X786" s="4" t="s">
         <v>322</v>
@@ -72342,7 +72342,7 @@
       <c r="U787" s="4"/>
       <c r="V787" s="4"/>
       <c r="W787" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X787" s="4" t="s">
         <v>46</v>
@@ -72422,7 +72422,7 @@
         <v>340</v>
       </c>
       <c r="W788" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X788" s="4" t="s">
         <v>46</v>
@@ -72498,7 +72498,7 @@
       <c r="U789" s="4"/>
       <c r="V789" s="4"/>
       <c r="W789" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X789" s="4" t="s">
         <v>322</v>
@@ -72578,7 +72578,7 @@
         <v>74</v>
       </c>
       <c r="W790" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X790" s="4" t="s">
         <v>46</v>
@@ -72658,7 +72658,7 @@
         <v>130</v>
       </c>
       <c r="W791" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X791" s="4" t="s">
         <v>46</v>
@@ -72738,7 +72738,7 @@
         <v>237</v>
       </c>
       <c r="W792" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X792" s="4" t="s">
         <v>46</v>
@@ -72814,7 +72814,7 @@
       <c r="U793" s="4"/>
       <c r="V793" s="4"/>
       <c r="W793" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X793" s="4" t="s">
         <v>46</v>
@@ -72890,7 +72890,7 @@
       <c r="U794" s="4"/>
       <c r="V794" s="4"/>
       <c r="W794" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X794" s="4" t="s">
         <v>46</v>
@@ -72968,7 +72968,7 @@
         <v>340</v>
       </c>
       <c r="W795" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X795" s="4" t="s">
         <v>46</v>
@@ -73046,7 +73046,7 @@
         <v>206</v>
       </c>
       <c r="W796" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X796" s="4" t="s">
         <v>46</v>
@@ -73122,7 +73122,7 @@
       <c r="U797" s="4"/>
       <c r="V797" s="4"/>
       <c r="W797" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X797" s="4" t="s">
         <v>46</v>
@@ -73198,7 +73198,7 @@
       <c r="U798" s="4"/>
       <c r="V798" s="4"/>
       <c r="W798" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X798" s="4" t="s">
         <v>46</v>
@@ -73276,7 +73276,7 @@
         <v>557</v>
       </c>
       <c r="W799" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X799" s="4" t="s">
         <v>46</v>
@@ -73352,7 +73352,7 @@
       <c r="U800" s="4"/>
       <c r="V800" s="4"/>
       <c r="W800" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X800" s="4" t="s">
         <v>46</v>
@@ -73426,7 +73426,7 @@
         <v>602</v>
       </c>
       <c r="W801" s="4">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="X801" s="4" t="s">
         <v>46</v>
@@ -73498,7 +73498,7 @@
         <v>340</v>
       </c>
       <c r="W802" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X802" s="4" t="s">
         <v>46</v>
@@ -73566,7 +73566,7 @@
       <c r="U803" s="4"/>
       <c r="V803" s="4"/>
       <c r="W803" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X803" s="4" t="s">
         <v>46</v>
@@ -73642,7 +73642,7 @@
       <c r="U804" s="4"/>
       <c r="V804" s="4"/>
       <c r="W804" s="4">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X804" s="4" t="s">
         <v>46</v>
@@ -73718,7 +73718,7 @@
         <v>340</v>
       </c>
       <c r="W805" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X805" s="4" t="s">
         <v>322</v>
@@ -73796,7 +73796,7 @@
         <v>237</v>
       </c>
       <c r="W806" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X806" s="4" t="s">
         <v>46</v>
@@ -73872,7 +73872,7 @@
       <c r="U807" s="4"/>
       <c r="V807" s="4"/>
       <c r="W807" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X807" s="4" t="s">
         <v>46</v>
@@ -73952,7 +73952,7 @@
         <v>130</v>
       </c>
       <c r="W808" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X808" s="4" t="s">
         <v>46</v>
@@ -74026,7 +74026,7 @@
       <c r="U809" s="4"/>
       <c r="V809" s="4"/>
       <c r="W809" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X809" s="4" t="s">
         <v>46</v>
@@ -74102,7 +74102,7 @@
       <c r="U810" s="4"/>
       <c r="V810" s="4"/>
       <c r="W810" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X810" s="4" t="s">
         <v>46</v>
@@ -74182,7 +74182,7 @@
         <v>340</v>
       </c>
       <c r="W811" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X811" s="4" t="s">
         <v>46</v>
@@ -74262,7 +74262,7 @@
         <v>237</v>
       </c>
       <c r="W812" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X812" s="4" t="s">
         <v>46</v>
@@ -74338,7 +74338,7 @@
       <c r="U813" s="4"/>
       <c r="V813" s="4"/>
       <c r="W813" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X813" s="4" t="s">
         <v>322</v>
@@ -74414,7 +74414,7 @@
         <v>237</v>
       </c>
       <c r="W814" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X814" s="4" t="s">
         <v>322</v>
@@ -74490,7 +74490,7 @@
       <c r="U815" s="4"/>
       <c r="V815" s="4"/>
       <c r="W815" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X815" s="4" t="s">
         <v>322</v>
@@ -74570,7 +74570,7 @@
         <v>45</v>
       </c>
       <c r="W816" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X816" s="4" t="s">
         <v>46</v>
@@ -74650,7 +74650,7 @@
         <v>340</v>
       </c>
       <c r="W817" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X817" s="4" t="s">
         <v>46</v>
@@ -74730,7 +74730,7 @@
         <v>224</v>
       </c>
       <c r="W818" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X818" s="4" t="s">
         <v>46</v>
@@ -74810,7 +74810,7 @@
         <v>3240</v>
       </c>
       <c r="W819" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X819" s="4" t="s">
         <v>46</v>
@@ -74890,7 +74890,7 @@
         <v>237</v>
       </c>
       <c r="W820" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X820" s="4" t="s">
         <v>46</v>
@@ -74964,7 +74964,7 @@
       <c r="U821" s="4"/>
       <c r="V821" s="4"/>
       <c r="W821" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X821" s="4" t="s">
         <v>46</v>
@@ -75040,7 +75040,7 @@
       <c r="U822" s="4"/>
       <c r="V822" s="4"/>
       <c r="W822" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X822" s="4" t="s">
         <v>46</v>
@@ -75120,7 +75120,7 @@
         <v>1472</v>
       </c>
       <c r="W823" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X823" s="4" t="s">
         <v>46</v>
@@ -75200,7 +75200,7 @@
         <v>3262</v>
       </c>
       <c r="W824" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X824" s="4" t="s">
         <v>46</v>
@@ -75280,7 +75280,7 @@
         <v>3267</v>
       </c>
       <c r="W825" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X825" s="4" t="s">
         <v>46</v>
@@ -75356,7 +75356,7 @@
       <c r="U826" s="4"/>
       <c r="V826" s="4"/>
       <c r="W826" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X826" s="4" t="s">
         <v>46</v>
@@ -75434,7 +75434,7 @@
         <v>2088</v>
       </c>
       <c r="W827" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X827" s="4" t="s">
         <v>46</v>
@@ -75512,7 +75512,7 @@
         <v>237</v>
       </c>
       <c r="W828" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X828" s="4" t="s">
         <v>46</v>
@@ -75588,7 +75588,7 @@
       <c r="U829" s="4"/>
       <c r="V829" s="4"/>
       <c r="W829" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X829" s="4" t="s">
         <v>46</v>
@@ -75658,7 +75658,7 @@
       <c r="U830" s="4"/>
       <c r="V830" s="4"/>
       <c r="W830" s="4">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="X830" s="4" t="s">
         <v>46</v>
@@ -75732,7 +75732,7 @@
       <c r="U831" s="4"/>
       <c r="V831" s="4"/>
       <c r="W831" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X831" s="4" t="s">
         <v>46</v>
@@ -75808,7 +75808,7 @@
       <c r="U832" s="4"/>
       <c r="V832" s="4"/>
       <c r="W832" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X832" s="4" t="s">
         <v>46</v>
@@ -75886,7 +75886,7 @@
         <v>212</v>
       </c>
       <c r="W833" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X833" s="4" t="s">
         <v>322</v>
@@ -75962,7 +75962,7 @@
       <c r="U834" s="4"/>
       <c r="V834" s="4"/>
       <c r="W834" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X834" s="4" t="s">
         <v>46</v>
@@ -76042,7 +76042,7 @@
         <v>340</v>
       </c>
       <c r="W835" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X835" s="4" t="s">
         <v>46</v>
@@ -76120,7 +76120,7 @@
         <v>130</v>
       </c>
       <c r="W836" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X836" s="4" t="s">
         <v>322</v>
@@ -76198,7 +76198,7 @@
         <v>74</v>
       </c>
       <c r="W837" s="4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="X837" s="4" t="s">
         <v>46</v>
@@ -76274,7 +76274,7 @@
       <c r="U838" s="4"/>
       <c r="V838" s="4"/>
       <c r="W838" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X838" s="4" t="s">
         <v>322</v>
@@ -76354,7 +76354,7 @@
         <v>237</v>
       </c>
       <c r="W839" s="4">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="X839" s="4" t="s">
         <v>46</v>
@@ -76430,7 +76430,7 @@
       <c r="U840" s="4"/>
       <c r="V840" s="4"/>
       <c r="W840" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X840" s="4" t="s">
         <v>322</v>
@@ -76508,7 +76508,7 @@
         <v>340</v>
       </c>
       <c r="W841" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X841" s="4" t="s">
         <v>322</v>
@@ -76588,7 +76588,7 @@
         <v>237</v>
       </c>
       <c r="W842" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X842" s="4" t="s">
         <v>322</v>
@@ -76662,7 +76662,7 @@
       <c r="U843" s="4"/>
       <c r="V843" s="4"/>
       <c r="W843" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X843" s="4" t="s">
         <v>322</v>
@@ -76738,7 +76738,7 @@
       <c r="U844" s="4"/>
       <c r="V844" s="4"/>
       <c r="W844" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X844" s="4" t="s">
         <v>46</v>
@@ -76808,7 +76808,7 @@
       <c r="U845" s="4"/>
       <c r="V845" s="4"/>
       <c r="W845" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X845" s="4" t="s">
         <v>46</v>
@@ -76886,7 +76886,7 @@
         <v>665</v>
       </c>
       <c r="W846" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X846" s="4" t="s">
         <v>46</v>
@@ -76960,7 +76960,7 @@
       <c r="U847" s="4"/>
       <c r="V847" s="4"/>
       <c r="W847" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X847" s="4" t="s">
         <v>46</v>
@@ -77034,7 +77034,7 @@
       <c r="U848" s="4"/>
       <c r="V848" s="4"/>
       <c r="W848" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X848" s="4" t="s">
         <v>46</v>
@@ -77112,7 +77112,7 @@
         <v>130</v>
       </c>
       <c r="W849" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X849" s="4" t="s">
         <v>46</v>
@@ -77188,7 +77188,7 @@
       <c r="U850" s="4"/>
       <c r="V850" s="4"/>
       <c r="W850" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X850" s="4" t="s">
         <v>46</v>
@@ -77268,7 +77268,7 @@
         <v>3357</v>
       </c>
       <c r="W851" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X851" s="4" t="s">
         <v>46</v>
@@ -77342,7 +77342,7 @@
       <c r="U852" s="4"/>
       <c r="V852" s="4"/>
       <c r="W852" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X852" s="4" t="s">
         <v>46</v>
@@ -77418,7 +77418,7 @@
       <c r="U853" s="4"/>
       <c r="V853" s="4"/>
       <c r="W853" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X853" s="4" t="s">
         <v>46</v>
@@ -77494,7 +77494,7 @@
       <c r="U854" s="4"/>
       <c r="V854" s="4"/>
       <c r="W854" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X854" s="4" t="s">
         <v>46</v>
@@ -77570,7 +77570,7 @@
       <c r="U855" s="4"/>
       <c r="V855" s="4"/>
       <c r="W855" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X855" s="4" t="s">
         <v>46</v>
@@ -77646,7 +77646,7 @@
       <c r="U856" s="4"/>
       <c r="V856" s="4"/>
       <c r="W856" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X856" s="4" t="s">
         <v>46</v>
@@ -77720,7 +77720,7 @@
       <c r="U857" s="4"/>
       <c r="V857" s="4"/>
       <c r="W857" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X857" s="4" t="s">
         <v>46</v>
@@ -77798,7 +77798,7 @@
         <v>45</v>
       </c>
       <c r="W858" s="4">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X858" s="4" t="s">
         <v>46</v>
@@ -77874,7 +77874,7 @@
       <c r="U859" s="4"/>
       <c r="V859" s="4"/>
       <c r="W859" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X859" s="4" t="s">
         <v>46</v>
@@ -77952,7 +77952,7 @@
         <v>340</v>
       </c>
       <c r="W860" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X860" s="4" t="s">
         <v>322</v>
@@ -78026,7 +78026,7 @@
       <c r="U861" s="4"/>
       <c r="V861" s="4"/>
       <c r="W861" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X861" s="4" t="s">
         <v>46</v>
@@ -78102,7 +78102,7 @@
       <c r="U862" s="4"/>
       <c r="V862" s="4"/>
       <c r="W862" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X862" s="4" t="s">
         <v>46</v>
@@ -78178,7 +78178,7 @@
       <c r="U863" s="4"/>
       <c r="V863" s="4"/>
       <c r="W863" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X863" s="4" t="s">
         <v>46</v>
@@ -78258,7 +78258,7 @@
         <v>602</v>
       </c>
       <c r="W864" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X864" s="4" t="s">
         <v>46</v>
@@ -78334,7 +78334,7 @@
       <c r="U865" s="4"/>
       <c r="V865" s="4"/>
       <c r="W865" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X865" s="4" t="s">
         <v>46</v>
@@ -78410,7 +78410,7 @@
       <c r="U866" s="4"/>
       <c r="V866" s="4"/>
       <c r="W866" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X866" s="4" t="s">
         <v>46</v>
@@ -78488,7 +78488,7 @@
         <v>340</v>
       </c>
       <c r="W867" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X867" s="4" t="s">
         <v>46</v>
@@ -78564,7 +78564,7 @@
       <c r="U868" s="4"/>
       <c r="V868" s="4"/>
       <c r="W868" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X868" s="4" t="s">
         <v>46</v>
@@ -78640,7 +78640,7 @@
       <c r="U869" s="4"/>
       <c r="V869" s="4"/>
       <c r="W869" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X869" s="4" t="s">
         <v>46</v>
@@ -78718,7 +78718,7 @@
         <v>356</v>
       </c>
       <c r="W870" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X870" s="4" t="s">
         <v>46</v>
@@ -78798,7 +78798,7 @@
         <v>356</v>
       </c>
       <c r="W871" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X871" s="4" t="s">
         <v>46</v>
@@ -78878,7 +78878,7 @@
         <v>356</v>
       </c>
       <c r="W872" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X872" s="4" t="s">
         <v>46</v>
@@ -78958,7 +78958,7 @@
         <v>602</v>
       </c>
       <c r="W873" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="X873" s="4" t="s">
         <v>46</v>
@@ -79038,7 +79038,7 @@
         <v>245</v>
       </c>
       <c r="W874" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X874" s="4" t="s">
         <v>46</v>
@@ -79118,7 +79118,7 @@
         <v>224</v>
       </c>
       <c r="W875" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X875" s="4" t="s">
         <v>322</v>
@@ -79194,7 +79194,7 @@
       <c r="U876" s="4"/>
       <c r="V876" s="4"/>
       <c r="W876" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X876" s="4" t="s">
         <v>46</v>
@@ -79270,7 +79270,7 @@
       <c r="U877" s="4"/>
       <c r="V877" s="4"/>
       <c r="W877" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X877" s="4" t="s">
         <v>46</v>
@@ -79350,7 +79350,7 @@
         <v>224</v>
       </c>
       <c r="W878" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X878" s="4" t="s">
         <v>46</v>
@@ -79420,7 +79420,7 @@
       <c r="U879" s="4"/>
       <c r="V879" s="4"/>
       <c r="W879" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X879" s="4" t="s">
         <v>46</v>
@@ -79490,7 +79490,7 @@
       <c r="U880" s="4"/>
       <c r="V880" s="4"/>
       <c r="W880" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X880" s="4" t="s">
         <v>46</v>
@@ -79560,7 +79560,7 @@
       <c r="U881" s="4"/>
       <c r="V881" s="4"/>
       <c r="W881" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X881" s="4" t="s">
         <v>46</v>
@@ -79640,7 +79640,7 @@
         <v>340</v>
       </c>
       <c r="W882" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X882" s="4" t="s">
         <v>46</v>
@@ -79720,7 +79720,7 @@
         <v>3475</v>
       </c>
       <c r="W883" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X883" s="4" t="s">
         <v>46</v>
@@ -79796,7 +79796,7 @@
       <c r="U884" s="4"/>
       <c r="V884" s="4"/>
       <c r="W884" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X884" s="4" t="s">
         <v>46</v>
@@ -79872,7 +79872,7 @@
       <c r="U885" s="4"/>
       <c r="V885" s="4"/>
       <c r="W885" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X885" s="4" t="s">
         <v>46</v>
@@ -79946,7 +79946,7 @@
       <c r="U886" s="4"/>
       <c r="V886" s="4"/>
       <c r="W886" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X886" s="4" t="s">
         <v>46</v>
@@ -80022,7 +80022,7 @@
       <c r="U887" s="4"/>
       <c r="V887" s="4"/>
       <c r="W887" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X887" s="4" t="s">
         <v>46</v>
@@ -80096,7 +80096,7 @@
       <c r="U888" s="4"/>
       <c r="V888" s="4"/>
       <c r="W888" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X888" s="4" t="s">
         <v>46</v>
@@ -80172,7 +80172,7 @@
       <c r="U889" s="4"/>
       <c r="V889" s="4"/>
       <c r="W889" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X889" s="4" t="s">
         <v>46</v>
@@ -80246,7 +80246,7 @@
       <c r="U890" s="4"/>
       <c r="V890" s="4"/>
       <c r="W890" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X890" s="4" t="s">
         <v>46</v>
@@ -80326,7 +80326,7 @@
         <v>74</v>
       </c>
       <c r="W891" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X891" s="4" t="s">
         <v>46</v>
@@ -80404,7 +80404,7 @@
         <v>3038</v>
       </c>
       <c r="W892" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X892" s="4" t="s">
         <v>46</v>
@@ -80482,7 +80482,7 @@
         <v>237</v>
       </c>
       <c r="W893" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X893" s="4" t="s">
         <v>46</v>
@@ -80558,7 +80558,7 @@
       <c r="U894" s="4"/>
       <c r="V894" s="4"/>
       <c r="W894" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X894" s="4" t="s">
         <v>46</v>
@@ -80638,7 +80638,7 @@
         <v>45</v>
       </c>
       <c r="W895" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="X895" s="4" t="s">
         <v>46</v>
@@ -80714,7 +80714,7 @@
       <c r="U896" s="4"/>
       <c r="V896" s="4"/>
       <c r="W896" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X896" s="4" t="s">
         <v>46</v>
@@ -80794,7 +80794,7 @@
         <v>721</v>
       </c>
       <c r="W897" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X897" s="4" t="s">
         <v>46</v>
@@ -80870,7 +80870,7 @@
       <c r="U898" s="4"/>
       <c r="V898" s="4"/>
       <c r="W898" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X898" s="4" t="s">
         <v>322</v>
@@ -80946,7 +80946,7 @@
       <c r="U899" s="4"/>
       <c r="V899" s="4"/>
       <c r="W899" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X899" s="4" t="s">
         <v>322</v>
@@ -81026,7 +81026,7 @@
         <v>557</v>
       </c>
       <c r="W900" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X900" s="4" t="s">
         <v>322</v>
@@ -81102,7 +81102,7 @@
       <c r="U901" s="4"/>
       <c r="V901" s="4"/>
       <c r="W901" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X901" s="4" t="s">
         <v>322</v>
@@ -81182,7 +81182,7 @@
         <v>340</v>
       </c>
       <c r="W902" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X902" s="4" t="s">
         <v>322</v>
@@ -81256,7 +81256,7 @@
       <c r="U903" s="4"/>
       <c r="V903" s="4"/>
       <c r="W903" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X903" s="4" t="s">
         <v>46</v>
@@ -81326,7 +81326,7 @@
       <c r="U904" s="4"/>
       <c r="V904" s="4"/>
       <c r="W904" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X904" s="4" t="s">
         <v>46</v>
@@ -81400,7 +81400,7 @@
       <c r="U905" s="4"/>
       <c r="V905" s="4"/>
       <c r="W905" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X905" s="4" t="s">
         <v>46</v>
@@ -81474,7 +81474,7 @@
       <c r="U906" s="4"/>
       <c r="V906" s="4"/>
       <c r="W906" s="4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X906" s="4" t="s">
         <v>46</v>
@@ -81550,7 +81550,7 @@
       <c r="U907" s="4"/>
       <c r="V907" s="4"/>
       <c r="W907" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X907" s="4" t="s">
         <v>46</v>
@@ -81630,7 +81630,7 @@
         <v>237</v>
       </c>
       <c r="W908" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X908" s="4" t="s">
         <v>46</v>
@@ -81708,7 +81708,7 @@
         <v>2612</v>
       </c>
       <c r="W909" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X909" s="4" t="s">
         <v>46</v>
@@ -81782,7 +81782,7 @@
         <v>224</v>
       </c>
       <c r="W910" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X910" s="4" t="s">
         <v>46</v>
@@ -81856,7 +81856,7 @@
         <v>237</v>
       </c>
       <c r="W911" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X911" s="4" t="s">
         <v>46</v>
@@ -81934,7 +81934,7 @@
         <v>340</v>
       </c>
       <c r="W912" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X912" s="4" t="s">
         <v>46</v>
@@ -82014,7 +82014,7 @@
         <v>237</v>
       </c>
       <c r="W913" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="X913" s="4" t="s">
         <v>46</v>
@@ -82094,7 +82094,7 @@
         <v>237</v>
       </c>
       <c r="W914" s="4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X914" s="4" t="s">
         <v>46</v>
@@ -82164,7 +82164,7 @@
       <c r="U915" s="4"/>
       <c r="V915" s="4"/>
       <c r="W915" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X915" s="4" t="s">
         <v>46</v>
@@ -82244,7 +82244,7 @@
         <v>340</v>
       </c>
       <c r="W916" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X916" s="4" t="s">
         <v>46</v>
@@ -82314,7 +82314,7 @@
       <c r="U917" s="4"/>
       <c r="V917" s="4"/>
       <c r="W917" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X917" s="4" t="s">
         <v>46</v>
@@ -82390,7 +82390,7 @@
       <c r="U918" s="4"/>
       <c r="V918" s="4"/>
       <c r="W918" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X918" s="4" t="s">
         <v>46</v>
@@ -82460,7 +82460,7 @@
       <c r="U919" s="4"/>
       <c r="V919" s="4"/>
       <c r="W919" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X919" s="4" t="s">
         <v>46</v>
@@ -82530,7 +82530,7 @@
       <c r="U920" s="4"/>
       <c r="V920" s="4"/>
       <c r="W920" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X920" s="4" t="s">
         <v>46</v>
@@ -82606,7 +82606,7 @@
       <c r="U921" s="4"/>
       <c r="V921" s="4"/>
       <c r="W921" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X921" s="4" t="s">
         <v>322</v>
@@ -82684,7 +82684,7 @@
         <v>45</v>
       </c>
       <c r="W922" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X922" s="4" t="s">
         <v>46</v>
@@ -82758,7 +82758,7 @@
       <c r="U923" s="4"/>
       <c r="V923" s="4"/>
       <c r="W923" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X923" s="4" t="s">
         <v>46</v>
@@ -82838,7 +82838,7 @@
         <v>116</v>
       </c>
       <c r="W924" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X924" s="4" t="s">
         <v>46</v>
@@ -82910,7 +82910,7 @@
       <c r="U925" s="4"/>
       <c r="V925" s="4"/>
       <c r="W925" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X925" s="4" t="s">
         <v>46</v>
@@ -82990,7 +82990,7 @@
         <v>130</v>
       </c>
       <c r="W926" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X926" s="4" t="s">
         <v>322</v>
@@ -83064,7 +83064,7 @@
       <c r="U927" s="4"/>
       <c r="V927" s="4"/>
       <c r="W927" s="4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X927" s="4" t="s">
         <v>322</v>
@@ -83142,7 +83142,7 @@
         <v>356</v>
       </c>
       <c r="W928" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X928" s="4" t="s">
         <v>46</v>
@@ -83214,7 +83214,7 @@
       <c r="U929" s="4"/>
       <c r="V929" s="4"/>
       <c r="W929" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X929" s="4" t="s">
         <v>46</v>
@@ -83290,7 +83290,7 @@
         <v>2617</v>
       </c>
       <c r="W930" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X930" s="4" t="s">
         <v>46</v>
@@ -83362,7 +83362,7 @@
       <c r="U931" s="4"/>
       <c r="V931" s="4"/>
       <c r="W931" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X931" s="4" t="s">
         <v>46</v>
@@ -83436,7 +83436,7 @@
       <c r="U932" s="4"/>
       <c r="V932" s="4"/>
       <c r="W932" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X932" s="4" t="s">
         <v>46</v>
@@ -83510,7 +83510,7 @@
       <c r="U933" s="4"/>
       <c r="V933" s="4"/>
       <c r="W933" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X933" s="4" t="s">
         <v>46</v>
@@ -83586,7 +83586,7 @@
       <c r="U934" s="4"/>
       <c r="V934" s="4"/>
       <c r="W934" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X934" s="4" t="s">
         <v>46</v>
@@ -83660,7 +83660,7 @@
       <c r="U935" s="4"/>
       <c r="V935" s="4"/>
       <c r="W935" s="4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X935" s="4" t="s">
         <v>46</v>
@@ -83730,7 +83730,7 @@
       <c r="U936" s="4"/>
       <c r="V936" s="4"/>
       <c r="W936" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X936" s="4" t="s">
         <v>322</v>
@@ -83804,7 +83804,7 @@
         <v>321</v>
       </c>
       <c r="W937" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X937" s="4" t="s">
         <v>46</v>
@@ -83882,7 +83882,7 @@
         <v>237</v>
       </c>
       <c r="W938" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X938" s="4" t="s">
         <v>46</v>
@@ -83958,7 +83958,7 @@
       <c r="U939" s="4"/>
       <c r="V939" s="4"/>
       <c r="W939" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X939" s="4" t="s">
         <v>46</v>
@@ -84038,7 +84038,7 @@
         <v>756</v>
       </c>
       <c r="W940" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X940" s="4" t="s">
         <v>46</v>
@@ -84112,7 +84112,7 @@
       <c r="U941" s="4"/>
       <c r="V941" s="4"/>
       <c r="W941" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X941" s="4" t="s">
         <v>46</v>
@@ -84188,7 +84188,7 @@
       <c r="U942" s="4"/>
       <c r="V942" s="4"/>
       <c r="W942" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X942" s="4" t="s">
         <v>46</v>
@@ -84262,7 +84262,7 @@
       <c r="U943" s="4"/>
       <c r="V943" s="4"/>
       <c r="W943" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X943" s="4" t="s">
         <v>46</v>
@@ -84340,7 +84340,7 @@
         <v>340</v>
       </c>
       <c r="W944" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X944" s="4" t="s">
         <v>46</v>
@@ -84418,7 +84418,7 @@
         <v>3717</v>
       </c>
       <c r="W945" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X945" s="4" t="s">
         <v>46</v>
@@ -84496,7 +84496,7 @@
         <v>3724</v>
       </c>
       <c r="W946" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X946" s="4" t="s">
         <v>46</v>
@@ -84576,7 +84576,7 @@
         <v>141</v>
       </c>
       <c r="W947" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X947" s="4" t="s">
         <v>322</v>
@@ -84656,7 +84656,7 @@
         <v>340</v>
       </c>
       <c r="W948" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X948" s="4" t="s">
         <v>46</v>
@@ -84732,7 +84732,7 @@
       <c r="U949" s="4"/>
       <c r="V949" s="4"/>
       <c r="W949" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X949" s="4" t="s">
         <v>46</v>
@@ -84812,7 +84812,7 @@
         <v>340</v>
       </c>
       <c r="W950" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X950" s="4" t="s">
         <v>46</v>
@@ -84880,7 +84880,7 @@
       <c r="U951" s="4"/>
       <c r="V951" s="4"/>
       <c r="W951" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X951" s="4" t="s">
         <v>46</v>
@@ -84950,7 +84950,7 @@
       <c r="U952" s="4"/>
       <c r="V952" s="4"/>
       <c r="W952" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X952" s="4" t="s">
         <v>46</v>
@@ -85030,7 +85030,7 @@
         <v>237</v>
       </c>
       <c r="W953" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X953" s="4" t="s">
         <v>46</v>
@@ -85106,7 +85106,7 @@
       <c r="U954" s="4"/>
       <c r="V954" s="4"/>
       <c r="W954" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X954" s="4" t="s">
         <v>322</v>
@@ -85180,7 +85180,7 @@
         <v>321</v>
       </c>
       <c r="W955" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X955" s="4" t="s">
         <v>46</v>
@@ -85258,7 +85258,7 @@
         <v>141</v>
       </c>
       <c r="W956" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X956" s="4" t="s">
         <v>46</v>
@@ -85336,7 +85336,7 @@
         <v>224</v>
       </c>
       <c r="W957" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X957" s="4" t="s">
         <v>322</v>
@@ -85406,7 +85406,7 @@
       <c r="U958" s="4"/>
       <c r="V958" s="4"/>
       <c r="W958" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X958" s="4" t="s">
         <v>46</v>
@@ -85482,7 +85482,7 @@
         <v>45</v>
       </c>
       <c r="W959" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X959" s="4" t="s">
         <v>46</v>
@@ -85550,7 +85550,7 @@
       <c r="U960" s="4"/>
       <c r="V960" s="4"/>
       <c r="W960" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X960" s="4" t="s">
         <v>322</v>
@@ -85628,7 +85628,7 @@
         <v>66</v>
       </c>
       <c r="W961" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X961" s="4" t="s">
         <v>46</v>
@@ -85706,7 +85706,7 @@
         <v>66</v>
       </c>
       <c r="W962" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X962" s="4" t="s">
         <v>46</v>
@@ -85784,7 +85784,7 @@
         <v>66</v>
       </c>
       <c r="W963" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X963" s="4" t="s">
         <v>46</v>
@@ -85858,7 +85858,7 @@
       <c r="U964" s="4"/>
       <c r="V964" s="4"/>
       <c r="W964" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X964" s="4" t="s">
         <v>322</v>
@@ -85934,7 +85934,7 @@
       <c r="U965" s="4"/>
       <c r="V965" s="4"/>
       <c r="W965" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X965" s="4" t="s">
         <v>322</v>
@@ -86010,7 +86010,7 @@
       <c r="U966" s="4"/>
       <c r="V966" s="4"/>
       <c r="W966" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X966" s="4" t="s">
         <v>46</v>
@@ -86086,7 +86086,7 @@
       <c r="U967" s="4"/>
       <c r="V967" s="4"/>
       <c r="W967" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X967" s="4" t="s">
         <v>46</v>
@@ -86166,7 +86166,7 @@
         <v>74</v>
       </c>
       <c r="W968" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X968" s="4" t="s">
         <v>46</v>
@@ -86240,7 +86240,7 @@
       <c r="U969" s="4"/>
       <c r="V969" s="4"/>
       <c r="W969" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X969" s="4" t="s">
         <v>46</v>
@@ -86320,7 +86320,7 @@
         <v>321</v>
       </c>
       <c r="W970" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X970" s="4" t="s">
         <v>46</v>
@@ -86394,7 +86394,7 @@
       <c r="U971" s="4"/>
       <c r="V971" s="4"/>
       <c r="W971" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X971" s="4" t="s">
         <v>46</v>
@@ -86470,7 +86470,7 @@
         <v>340</v>
       </c>
       <c r="W972" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X972" s="4" t="s">
         <v>322</v>
@@ -86542,7 +86542,7 @@
         <v>321</v>
       </c>
       <c r="W973" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X973" s="4" t="s">
         <v>46</v>
@@ -86616,7 +86616,7 @@
       <c r="U974" s="4"/>
       <c r="V974" s="4"/>
       <c r="W974" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X974" s="4" t="s">
         <v>46</v>
@@ -86694,7 +86694,7 @@
         <v>340</v>
       </c>
       <c r="W975" s="4">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="X975" s="4" t="s">
         <v>46</v>
@@ -86772,7 +86772,7 @@
         <v>146</v>
       </c>
       <c r="W976" s="4">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X976" s="4" t="s">
         <v>46</v>
@@ -86848,7 +86848,7 @@
       <c r="U977" s="4"/>
       <c r="V977" s="4"/>
       <c r="W977" s="4">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X977" s="4" t="s">
         <v>46</v>
@@ -86924,7 +86924,7 @@
         <v>98</v>
       </c>
       <c r="W978" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="X978" s="4" t="s">
         <v>46</v>
@@ -87000,7 +87000,7 @@
       <c r="U979" s="4"/>
       <c r="V979" s="4"/>
       <c r="W979" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X979" s="4" t="s">
         <v>46</v>
@@ -87074,7 +87074,7 @@
       <c r="U980" s="4"/>
       <c r="V980" s="4"/>
       <c r="W980" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X980" s="4" t="s">
         <v>46</v>
@@ -87152,7 +87152,7 @@
         <v>224</v>
       </c>
       <c r="W981" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X981" s="4" t="s">
         <v>46</v>
@@ -87230,7 +87230,7 @@
         <v>721</v>
       </c>
       <c r="W982" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X982" s="4" t="s">
         <v>46</v>
@@ -87298,7 +87298,7 @@
       <c r="U983" s="4"/>
       <c r="V983" s="4"/>
       <c r="W983" s="4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X983" s="4" t="s">
         <v>46</v>
@@ -87370,7 +87370,7 @@
       <c r="U984" s="4"/>
       <c r="V984" s="4"/>
       <c r="W984" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X984" s="4" t="s">
         <v>46</v>
@@ -87448,7 +87448,7 @@
         <v>245</v>
       </c>
       <c r="W985" s="4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="X985" s="4" t="s">
         <v>46</v>
@@ -87524,7 +87524,7 @@
       <c r="U986" s="4"/>
       <c r="V986" s="4"/>
       <c r="W986" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X986" s="4" t="s">
         <v>46</v>
@@ -87598,7 +87598,7 @@
       <c r="U987" s="4"/>
       <c r="V987" s="4"/>
       <c r="W987" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X987" s="4" t="s">
         <v>46</v>
@@ -87672,7 +87672,7 @@
       <c r="U988" s="4"/>
       <c r="V988" s="4"/>
       <c r="W988" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X988" s="4" t="s">
         <v>46</v>
@@ -87748,7 +87748,7 @@
         <v>201</v>
       </c>
       <c r="W989" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="X989" s="4" t="s">
         <v>46</v>
@@ -87826,7 +87826,7 @@
         <v>1839</v>
       </c>
       <c r="W990" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="X990" s="4" t="s">
         <v>46</v>
@@ -87906,7 +87906,7 @@
         <v>602</v>
       </c>
       <c r="W991" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X991" s="4" t="s">
         <v>46</v>
@@ -87984,7 +87984,7 @@
         <v>45</v>
       </c>
       <c r="W992" s="4">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X992" s="4" t="s">
         <v>46</v>
@@ -88062,7 +88062,7 @@
         <v>45</v>
       </c>
       <c r="W993" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X993" s="4" t="s">
         <v>46</v>
@@ -88140,7 +88140,7 @@
         <v>321</v>
       </c>
       <c r="W994" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X994" s="4" t="s">
         <v>46</v>
@@ -88214,7 +88214,7 @@
       <c r="U995" s="4"/>
       <c r="V995" s="4"/>
       <c r="W995" s="4">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X995" s="4" t="s">
         <v>46</v>
@@ -88292,7 +88292,7 @@
         <v>245</v>
       </c>
       <c r="W996" s="4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X996" s="4" t="s">
         <v>46</v>
@@ -88372,7 +88372,7 @@
         <v>703</v>
       </c>
       <c r="W997" s="4">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X997" s="4" t="s">
         <v>46</v>
@@ -88448,7 +88448,7 @@
         <v>206</v>
       </c>
       <c r="W998" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="X998" s="4" t="s">
         <v>46</v>
@@ -88526,7 +88526,7 @@
         <v>340</v>
       </c>
       <c r="W999" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="X999" s="4" t="s">
         <v>46</v>
@@ -88602,7 +88602,7 @@
         <v>224</v>
       </c>
       <c r="W1000" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X1000" s="4" t="s">
         <v>46</v>
@@ -88680,7 +88680,7 @@
         <v>602</v>
       </c>
       <c r="W1001" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X1001" s="4" t="s">
         <v>46</v>
@@ -88758,7 +88758,7 @@
         <v>237</v>
       </c>
       <c r="W1002" s="4">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="X1002" s="4" t="s">
         <v>46</v>
@@ -88838,7 +88838,7 @@
         <v>123</v>
       </c>
       <c r="W1003" s="4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="X1003" s="4" t="s">
         <v>46</v>
@@ -88914,7 +88914,7 @@
       <c r="U1004" s="4"/>
       <c r="V1004" s="4"/>
       <c r="W1004" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X1004" s="4" t="s">
         <v>46</v>
@@ -88992,7 +88992,7 @@
         <v>756</v>
       </c>
       <c r="W1005" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X1005" s="4" t="s">
         <v>322</v>
@@ -89072,7 +89072,7 @@
         <v>141</v>
       </c>
       <c r="W1006" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X1006" s="4" t="s">
         <v>322</v>
@@ -89146,7 +89146,7 @@
       <c r="U1007" s="4"/>
       <c r="V1007" s="4"/>
       <c r="W1007" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X1007" s="4" t="s">
         <v>322</v>
@@ -89220,7 +89220,7 @@
       <c r="U1008" s="4"/>
       <c r="V1008" s="4"/>
       <c r="W1008" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X1008" s="4" t="s">
         <v>322</v>
@@ -89298,7 +89298,7 @@
         <v>340</v>
       </c>
       <c r="W1009" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X1009" s="4" t="s">
         <v>322</v>
@@ -89372,7 +89372,7 @@
       <c r="U1010" s="4"/>
       <c r="V1010" s="4"/>
       <c r="W1010" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X1010" s="4" t="s">
         <v>322</v>
@@ -89450,7 +89450,7 @@
         <v>340</v>
       </c>
       <c r="W1011" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X1011" s="4" t="s">
         <v>46</v>
@@ -89530,7 +89530,7 @@
         <v>340</v>
       </c>
       <c r="W1012" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X1012" s="4" t="s">
         <v>46</v>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>18/10/2026 a las 08:30:59</t>
+    <t>18/10/2026 a las 09:20:49</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>18/10/2026 a las 09:20:49</t>
+    <t>18/10/2026 a las 10:21:05</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>18/10/2026 a las 10:21:05</t>
+    <t>18/10/2026 a las 10:30:48</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>21/10/2026 a las 08:08:07</t>
+    <t>21/10/2026 a las 08:20:54</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -59854,7 +59854,7 @@
         <v>1</v>
       </c>
       <c r="X638" s="4" t="s">
-        <v>1847</v>
+        <v>244</v>
       </c>
       <c r="Y638" s="4"/>
       <c r="Z638" s="4" t="s">
@@ -69800,7 +69800,7 @@
         <v>1</v>
       </c>
       <c r="X768" s="4" t="s">
-        <v>1847</v>
+        <v>244</v>
       </c>
       <c r="Y768" s="4"/>
       <c r="Z768" s="4" t="s">
@@ -72890,7 +72890,7 @@
         <v>2</v>
       </c>
       <c r="X808" s="4" t="s">
-        <v>1847</v>
+        <v>244</v>
       </c>
       <c r="Y808" s="4"/>
       <c r="Z808" s="4" t="s">

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>22/10/2026 a las 21:20:54</t>
+    <t>22/10/2026 a las 21:30:50</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>22/10/2026 a las 21:30:50</t>
+    <t>22/10/2026 a las 22:21:06</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>22/10/2026 a las 22:21:06</t>
+    <t>22/10/2026 a las 22:30:53</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>24/10/2026 a las 07:31:34</t>
+    <t>24/10/2026 a las 07:47:09</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>27/10/2026 a las 08:31:13</t>
+    <t>27/10/2026 a las 08:32:25</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>27/10/2026 a las 11:31:11</t>
+    <t>27/10/2026 a las 11:32:26</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>27/10/2026 a las 14:31:12</t>
+    <t>27/10/2026 a las 14:32:29</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>28/10/2026 a las 10:31:00</t>
+    <t>28/10/2026 a las 10:33:03</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>28/10/2026 a las 21:30:54</t>
+    <t>28/10/2026 a las 21:32:15</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>28/10/2026 a las 21:32:15</t>
+    <t>28/10/2026 a las 21:32:58</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>29/10/2026 a las 07:31:08</t>
+    <t>29/10/2026 a las 07:33:17</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>29/10/2026 a las 09:30:55</t>
+    <t>29/10/2026 a las 09:33:06</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3464">
   <si>
     <t>DELTEC - GUAJIRA</t>
   </si>
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>29/10/2026 a las 10:31:07</t>
+    <t>29/10/2026 a las 10:32:25</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -9350,15 +9350,6 @@
     <t>CHAPINERO</t>
   </si>
   <si>
-    <t>CL 5 CR 14 - 25 DPL EG1702</t>
-  </si>
-  <si>
-    <t>LOPEZ  JOSE JAIME</t>
-  </si>
-  <si>
-    <t>Revision Suministromedidor MD PQR SUSPENSION DE BORNERA. Juan Jose Quinones 3052760224 Rev gral medidor pruebas giro en vacio ver lectura digitos censo verficado conexiones ver todo</t>
-  </si>
-  <si>
     <t>CR 15 CL 3 - 38 DPL EG1594</t>
   </si>
   <si>
@@ -9500,12 +9491,6 @@
     <t>Inspeccion PQR Peticion SUSPENSION DE BORNERA. Andres Alfonso Ramirez Lopez TEL 3142961771 Soporte de reclamo, ver lectura actual, alto estimado, estado del medidor, corregir anomalias, Conexiones normalizar si es necesario.</t>
   </si>
   <si>
-    <t>CL 2 # CR 6 - 109 DPL EG2490</t>
-  </si>
-  <si>
-    <t>Reclamacion por Tarifa SUSPENSION MINICANASTA Usuaria ZENITH MARIA CARRILLO GONZALES manifiesta inconformidad con el consumo facturado del predio, solicita cambio de estrato junto a otras pretensiones, se asocia mes de oct 2026.</t>
-  </si>
-  <si>
     <t>CL 3 # CR 3 - 39 DPL EG2662</t>
   </si>
   <si>
@@ -9623,27 +9608,6 @@
     <t>Revision Suministromedidor MD PQR SUSPENSION EN TENDIDO. cliente Jose Elieser Vega Daza Cel 3115472024 USUARIO RECLAMA POR ALTO CONSUMO, TOMAR LECTURA ACTUAL estado del medidor y predio.</t>
   </si>
   <si>
-    <t>CL 7 CR 3 - 51 PISO 1 APTO 101 EG5126</t>
-  </si>
-  <si>
-    <t>GAMEZ  ANGELA</t>
-  </si>
-  <si>
-    <t>Revision Suministromedidor MD PQR SUSPENSION EN TENDIDO. Soporte de reclamo Comunicarse con El Sr. Javier Cuello Gamez Familiar CC 5163829 Cel 3153575488 Correo cuello_javierhotmail.com, solicita revison predio dsocupado y registra consumo.</t>
-  </si>
-  <si>
-    <t>CL 7 CR 3 - 51 PISO 1 CS 1 EG5127</t>
-  </si>
-  <si>
-    <t>CUELLO SF  ORLANDO</t>
-  </si>
-  <si>
-    <t>3953194-MC079</t>
-  </si>
-  <si>
-    <t>Revision Suministromedidor MD PQR SUSPENSION DE BORNERA. Soporte de reclamo, comunicarse con El Sr. Javier Cuello Gamez  Familiar CC 5163829 Cel 3153575488 Correo cuello_javierhotmail.com, desviacion significativa de consumo.</t>
-  </si>
-  <si>
     <t>CL 8 # CR 5 - 70 APTO 1 EG5228</t>
   </si>
   <si>
@@ -9720,18 +9684,6 @@
   </si>
   <si>
     <t>Revision Suministromedidor MD PQR SUSPENSION EN TENDIDO. Verificar doble facturacion con el nic 8323048 a nombre de HELEN MORA, verificar estado del predio y medidor, lectura</t>
-  </si>
-  <si>
-    <t>CL 14SUR CR 5A - 36 DPL EG5776</t>
-  </si>
-  <si>
-    <t>MANOTAS  VERA JUDITH</t>
-  </si>
-  <si>
-    <t>5500146-MC953</t>
-  </si>
-  <si>
-    <t>Revision Suministromedidor MD PQR SUSPENSION DE BORNERA. Vera Judith Manotas cel. 3026637790  manifiesta que el predio estaba suspendido, se mudo a finales de septiembre. ver todo</t>
   </si>
   <si>
     <t>LAGUNITA</t>
@@ -10848,7 +10800,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB884"/>
+  <dimension ref="A1:AB879"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -71017,13 +70969,13 @@
         <v>33</v>
       </c>
       <c r="C788" s="4">
-        <v>169963438</v>
+        <v>170213528</v>
       </c>
       <c r="D788" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E788" s="4">
-        <v>5610656</v>
+        <v>5602151</v>
       </c>
       <c r="F788" s="4" t="s">
         <v>140</v>
@@ -71042,13 +70994,13 @@
       </c>
       <c r="K788" s="4"/>
       <c r="L788" s="4" t="s">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="M788" s="4" t="s">
-        <v>177</v>
+        <v>592</v>
       </c>
       <c r="N788" s="4">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="O788" s="4" t="s">
         <v>3111</v>
@@ -71061,15 +71013,15 @@
         <v>56</v>
       </c>
       <c r="S788" s="4">
-        <v>88505.95</v>
+        <v>0</v>
       </c>
       <c r="T788" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U788" s="4"/>
       <c r="V788" s="4"/>
       <c r="W788" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X788" s="4" t="s">
         <v>46</v>
@@ -71078,9 +71030,7 @@
       <c r="Z788" s="4" t="s">
         <v>3113</v>
       </c>
-      <c r="AA788" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="AA788" s="4"/>
       <c r="AB788" s="4" t="s">
         <v>61</v>
       </c>
@@ -71093,13 +71043,13 @@
         <v>33</v>
       </c>
       <c r="C789" s="4">
-        <v>170213528</v>
+        <v>170405825</v>
       </c>
       <c r="D789" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E789" s="4">
-        <v>5602151</v>
+        <v>8388237</v>
       </c>
       <c r="F789" s="4" t="s">
         <v>140</v>
@@ -71114,27 +71064,27 @@
         <v>3094</v>
       </c>
       <c r="J789" s="4" t="s">
-        <v>3110</v>
+        <v>3114</v>
       </c>
       <c r="K789" s="4"/>
       <c r="L789" s="4" t="s">
-        <v>194</v>
+        <v>3115</v>
       </c>
       <c r="M789" s="4" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="N789" s="4">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="O789" s="4" t="s">
-        <v>3114</v>
+        <v>3116</v>
       </c>
       <c r="P789" s="5"/>
       <c r="Q789" s="4" t="s">
-        <v>3115</v>
+        <v>3117</v>
       </c>
       <c r="R789" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S789" s="4">
         <v>0</v>
@@ -71145,16 +71095,18 @@
       <c r="U789" s="4"/>
       <c r="V789" s="4"/>
       <c r="W789" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X789" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y789" s="4"/>
       <c r="Z789" s="4" t="s">
-        <v>3116</v>
-      </c>
-      <c r="AA789" s="4"/>
+        <v>3118</v>
+      </c>
+      <c r="AA789" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB789" s="4" t="s">
         <v>61</v>
       </c>
@@ -71167,13 +71119,13 @@
         <v>33</v>
       </c>
       <c r="C790" s="4">
-        <v>170405825</v>
+        <v>166534144</v>
       </c>
       <c r="D790" s="4" t="s">
-        <v>50</v>
+        <v>364</v>
       </c>
       <c r="E790" s="4">
-        <v>8388237</v>
+        <v>8387630</v>
       </c>
       <c r="F790" s="4" t="s">
         <v>140</v>
@@ -71188,27 +71140,27 @@
         <v>3094</v>
       </c>
       <c r="J790" s="4" t="s">
-        <v>3117</v>
+        <v>3114</v>
       </c>
       <c r="K790" s="4"/>
       <c r="L790" s="4" t="s">
-        <v>3118</v>
+        <v>3119</v>
       </c>
       <c r="M790" s="4" t="s">
-        <v>578</v>
+        <v>613</v>
       </c>
       <c r="N790" s="4">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="O790" s="4" t="s">
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="P790" s="5"/>
       <c r="Q790" s="4" t="s">
-        <v>3120</v>
+        <v>3121</v>
       </c>
       <c r="R790" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S790" s="4">
         <v>0</v>
@@ -71219,18 +71171,16 @@
       <c r="U790" s="4"/>
       <c r="V790" s="4"/>
       <c r="W790" s="4">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="X790" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y790" s="4"/>
       <c r="Z790" s="4" t="s">
-        <v>3121</v>
-      </c>
-      <c r="AA790" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>3122</v>
+      </c>
+      <c r="AA790" s="4"/>
       <c r="AB790" s="4" t="s">
         <v>61</v>
       </c>
@@ -71243,13 +71193,13 @@
         <v>33</v>
       </c>
       <c r="C791" s="4">
-        <v>166534144</v>
+        <v>170315958</v>
       </c>
       <c r="D791" s="4" t="s">
-        <v>364</v>
+        <v>50</v>
       </c>
       <c r="E791" s="4">
-        <v>8387630</v>
+        <v>8294226</v>
       </c>
       <c r="F791" s="4" t="s">
         <v>140</v>
@@ -71264,17 +71214,17 @@
         <v>3094</v>
       </c>
       <c r="J791" s="4" t="s">
-        <v>3117</v>
+        <v>3114</v>
       </c>
       <c r="K791" s="4"/>
       <c r="L791" s="4" t="s">
-        <v>3122</v>
+        <v>613</v>
       </c>
       <c r="M791" s="4" t="s">
         <v>613</v>
       </c>
       <c r="N791" s="4">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="O791" s="4" t="s">
         <v>3123</v>
@@ -71284,18 +71234,18 @@
         <v>3124</v>
       </c>
       <c r="R791" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S791" s="4">
-        <v>0</v>
+        <v>232715.16</v>
       </c>
       <c r="T791" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U791" s="4"/>
       <c r="V791" s="4"/>
       <c r="W791" s="4">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="X791" s="4" t="s">
         <v>46</v>
@@ -71304,7 +71254,9 @@
       <c r="Z791" s="4" t="s">
         <v>3125</v>
       </c>
-      <c r="AA791" s="4"/>
+      <c r="AA791" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB791" s="4" t="s">
         <v>61</v>
       </c>
@@ -71317,13 +71269,13 @@
         <v>33</v>
       </c>
       <c r="C792" s="4">
-        <v>170315958</v>
+        <v>167798304</v>
       </c>
       <c r="D792" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E792" s="4">
-        <v>8294226</v>
+        <v>5606690</v>
       </c>
       <c r="F792" s="4" t="s">
         <v>140</v>
@@ -71335,48 +71287,48 @@
         <v>3094</v>
       </c>
       <c r="I792" s="4" t="s">
-        <v>3094</v>
+        <v>3126</v>
       </c>
       <c r="J792" s="4" t="s">
-        <v>3117</v>
+        <v>3126</v>
       </c>
       <c r="K792" s="4"/>
       <c r="L792" s="4" t="s">
-        <v>613</v>
+        <v>256</v>
       </c>
       <c r="M792" s="4" t="s">
-        <v>613</v>
+        <v>40</v>
       </c>
       <c r="N792" s="4">
-        <v>15</v>
+        <v>90182</v>
       </c>
       <c r="O792" s="4" t="s">
-        <v>3126</v>
+        <v>3127</v>
       </c>
       <c r="P792" s="5"/>
       <c r="Q792" s="4" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="R792" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S792" s="4">
-        <v>232715.16</v>
+        <v>0</v>
       </c>
       <c r="T792" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U792" s="4"/>
       <c r="V792" s="4"/>
       <c r="W792" s="4">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="X792" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y792" s="4"/>
       <c r="Z792" s="4" t="s">
-        <v>3128</v>
+        <v>3129</v>
       </c>
       <c r="AA792" s="4" t="s">
         <v>79</v>
@@ -71393,13 +71345,13 @@
         <v>33</v>
       </c>
       <c r="C793" s="4">
-        <v>167798304</v>
+        <v>167218990</v>
       </c>
       <c r="D793" s="4" t="s">
-        <v>34</v>
+        <v>286</v>
       </c>
       <c r="E793" s="4">
-        <v>5606690</v>
+        <v>7607643</v>
       </c>
       <c r="F793" s="4" t="s">
         <v>140</v>
@@ -71411,27 +71363,27 @@
         <v>3094</v>
       </c>
       <c r="I793" s="4" t="s">
-        <v>3129</v>
+        <v>3094</v>
       </c>
       <c r="J793" s="4" t="s">
-        <v>3129</v>
+        <v>3130</v>
       </c>
       <c r="K793" s="4"/>
       <c r="L793" s="4" t="s">
-        <v>256</v>
+        <v>68</v>
       </c>
       <c r="M793" s="4" t="s">
-        <v>40</v>
+        <v>3131</v>
       </c>
       <c r="N793" s="4">
-        <v>90182</v>
+        <v>4</v>
       </c>
       <c r="O793" s="4" t="s">
-        <v>3130</v>
+        <v>3132</v>
       </c>
       <c r="P793" s="5"/>
       <c r="Q793" s="4" t="s">
-        <v>3131</v>
+        <v>3133</v>
       </c>
       <c r="R793" s="4" t="s">
         <v>56</v>
@@ -71442,21 +71394,23 @@
       <c r="T793" s="4">
         <v>0</v>
       </c>
-      <c r="U793" s="4"/>
-      <c r="V793" s="4"/>
+      <c r="U793" s="4" t="s">
+        <v>3134</v>
+      </c>
+      <c r="V793" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="W793" s="4">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="X793" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y793" s="4"/>
       <c r="Z793" s="4" t="s">
-        <v>3132</v>
-      </c>
-      <c r="AA793" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>3135</v>
+      </c>
+      <c r="AA793" s="4"/>
       <c r="AB793" s="4" t="s">
         <v>61</v>
       </c>
@@ -71469,13 +71423,13 @@
         <v>33</v>
       </c>
       <c r="C794" s="4">
-        <v>167218990</v>
+        <v>166536002</v>
       </c>
       <c r="D794" s="4" t="s">
-        <v>286</v>
+        <v>364</v>
       </c>
       <c r="E794" s="4">
-        <v>7607643</v>
+        <v>8333328</v>
       </c>
       <c r="F794" s="4" t="s">
         <v>140</v>
@@ -71490,42 +71444,38 @@
         <v>3094</v>
       </c>
       <c r="J794" s="4" t="s">
-        <v>3133</v>
+        <v>3130</v>
       </c>
       <c r="K794" s="4"/>
       <c r="L794" s="4" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="M794" s="4" t="s">
-        <v>3134</v>
+        <v>2094</v>
       </c>
       <c r="N794" s="4">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="O794" s="4" t="s">
-        <v>3135</v>
+        <v>3136</v>
       </c>
       <c r="P794" s="5"/>
       <c r="Q794" s="4" t="s">
-        <v>3136</v>
+        <v>3137</v>
       </c>
       <c r="R794" s="4" t="s">
         <v>56</v>
       </c>
       <c r="S794" s="4">
-        <v>0</v>
+        <v>909249.99</v>
       </c>
       <c r="T794" s="4">
-        <v>0</v>
-      </c>
-      <c r="U794" s="4" t="s">
-        <v>3137</v>
-      </c>
-      <c r="V794" s="4" t="s">
-        <v>86</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="U794" s="4"/>
+      <c r="V794" s="4"/>
       <c r="W794" s="4">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="X794" s="4" t="s">
         <v>46</v>
@@ -71547,13 +71497,13 @@
         <v>33</v>
       </c>
       <c r="C795" s="4">
-        <v>166536002</v>
+        <v>170416739</v>
       </c>
       <c r="D795" s="4" t="s">
-        <v>364</v>
+        <v>50</v>
       </c>
       <c r="E795" s="4">
-        <v>8333328</v>
+        <v>5607920</v>
       </c>
       <c r="F795" s="4" t="s">
         <v>140</v>
@@ -71568,17 +71518,17 @@
         <v>3094</v>
       </c>
       <c r="J795" s="4" t="s">
-        <v>3133</v>
+        <v>3130</v>
       </c>
       <c r="K795" s="4"/>
       <c r="L795" s="4" t="s">
         <v>98</v>
       </c>
       <c r="M795" s="4" t="s">
-        <v>2094</v>
+        <v>3115</v>
       </c>
       <c r="N795" s="4">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="O795" s="4" t="s">
         <v>3139</v>
@@ -71591,15 +71541,15 @@
         <v>56</v>
       </c>
       <c r="S795" s="4">
-        <v>909249.99</v>
+        <v>193192.28</v>
       </c>
       <c r="T795" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U795" s="4"/>
       <c r="V795" s="4"/>
       <c r="W795" s="4">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="X795" s="4" t="s">
         <v>46</v>
@@ -71608,7 +71558,9 @@
       <c r="Z795" s="4" t="s">
         <v>3141</v>
       </c>
-      <c r="AA795" s="4"/>
+      <c r="AA795" s="4" t="s">
+        <v>445</v>
+      </c>
       <c r="AB795" s="4" t="s">
         <v>61</v>
       </c>
@@ -71621,13 +71573,13 @@
         <v>33</v>
       </c>
       <c r="C796" s="4">
-        <v>170416739</v>
+        <v>170358528</v>
       </c>
       <c r="D796" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E796" s="4">
-        <v>5607920</v>
+        <v>7551609</v>
       </c>
       <c r="F796" s="4" t="s">
         <v>140</v>
@@ -71642,49 +71594,51 @@
         <v>3094</v>
       </c>
       <c r="J796" s="4" t="s">
-        <v>3133</v>
+        <v>740</v>
       </c>
       <c r="K796" s="4"/>
       <c r="L796" s="4" t="s">
-        <v>98</v>
+        <v>3142</v>
       </c>
       <c r="M796" s="4" t="s">
-        <v>3118</v>
+        <v>177</v>
       </c>
       <c r="N796" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O796" s="4" t="s">
-        <v>3142</v>
+        <v>3143</v>
       </c>
       <c r="P796" s="5"/>
       <c r="Q796" s="4" t="s">
-        <v>3143</v>
+        <v>3144</v>
       </c>
       <c r="R796" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S796" s="4">
-        <v>193192.28</v>
+        <v>46350.86</v>
       </c>
       <c r="T796" s="4">
         <v>1</v>
       </c>
-      <c r="U796" s="4"/>
-      <c r="V796" s="4"/>
+      <c r="U796" s="4" t="s">
+        <v>3145</v>
+      </c>
+      <c r="V796" s="4" t="s">
+        <v>510</v>
+      </c>
       <c r="W796" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X796" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y796" s="4"/>
       <c r="Z796" s="4" t="s">
-        <v>3144</v>
-      </c>
-      <c r="AA796" s="4" t="s">
-        <v>445</v>
-      </c>
+        <v>3146</v>
+      </c>
+      <c r="AA796" s="4"/>
       <c r="AB796" s="4" t="s">
         <v>61</v>
       </c>
@@ -71694,16 +71648,16 @@
         <v>1000</v>
       </c>
       <c r="B797" s="4" t="s">
-        <v>33</v>
+        <v>590</v>
       </c>
       <c r="C797" s="4">
-        <v>170358528</v>
+        <v>170407967</v>
       </c>
       <c r="D797" s="4" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="E797" s="4">
-        <v>7551609</v>
+        <v>5602586</v>
       </c>
       <c r="F797" s="4" t="s">
         <v>140</v>
@@ -71722,47 +71676,49 @@
       </c>
       <c r="K797" s="4"/>
       <c r="L797" s="4" t="s">
-        <v>3145</v>
+        <v>104</v>
       </c>
       <c r="M797" s="4" t="s">
-        <v>177</v>
+        <v>710</v>
       </c>
       <c r="N797" s="4">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="O797" s="4" t="s">
-        <v>3146</v>
+        <v>3147</v>
       </c>
       <c r="P797" s="5"/>
       <c r="Q797" s="4" t="s">
-        <v>3147</v>
+        <v>3148</v>
       </c>
       <c r="R797" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S797" s="4">
-        <v>46350.86</v>
+        <v>0</v>
       </c>
       <c r="T797" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U797" s="4" t="s">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="V797" s="4" t="s">
-        <v>510</v>
+        <v>137</v>
       </c>
       <c r="W797" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X797" s="4" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="Y797" s="4"/>
       <c r="Z797" s="4" t="s">
-        <v>3149</v>
-      </c>
-      <c r="AA797" s="4"/>
+        <v>3150</v>
+      </c>
+      <c r="AA797" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="AB797" s="4" t="s">
         <v>61</v>
       </c>
@@ -71772,16 +71728,16 @@
         <v>1000</v>
       </c>
       <c r="B798" s="4" t="s">
-        <v>590</v>
+        <v>33</v>
       </c>
       <c r="C798" s="4">
-        <v>170407967</v>
+        <v>170161574</v>
       </c>
       <c r="D798" s="4" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="E798" s="4">
-        <v>5602586</v>
+        <v>5608946</v>
       </c>
       <c r="F798" s="4" t="s">
         <v>140</v>
@@ -71800,41 +71756,35 @@
       </c>
       <c r="K798" s="4"/>
       <c r="L798" s="4" t="s">
-        <v>104</v>
+        <v>219</v>
       </c>
       <c r="M798" s="4" t="s">
-        <v>710</v>
-      </c>
-      <c r="N798" s="4">
-        <v>60</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="N798" s="4"/>
       <c r="O798" s="4" t="s">
-        <v>3150</v>
+        <v>3151</v>
       </c>
       <c r="P798" s="5"/>
       <c r="Q798" s="4" t="s">
-        <v>3151</v>
+        <v>3152</v>
       </c>
       <c r="R798" s="4" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="S798" s="4">
-        <v>0</v>
+        <v>174754.68</v>
       </c>
       <c r="T798" s="4">
-        <v>0</v>
-      </c>
-      <c r="U798" s="4" t="s">
-        <v>3152</v>
-      </c>
-      <c r="V798" s="4" t="s">
-        <v>137</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U798" s="4"/>
+      <c r="V798" s="4"/>
       <c r="W798" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X798" s="4" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="Y798" s="4"/>
       <c r="Z798" s="4" t="s">
@@ -71855,13 +71805,13 @@
         <v>33</v>
       </c>
       <c r="C799" s="4">
-        <v>170161574</v>
+        <v>170357542</v>
       </c>
       <c r="D799" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E799" s="4">
-        <v>5608946</v>
+        <v>5611793</v>
       </c>
       <c r="F799" s="4" t="s">
         <v>140</v>
@@ -71876,14 +71826,14 @@
         <v>3094</v>
       </c>
       <c r="J799" s="4" t="s">
-        <v>740</v>
+        <v>184</v>
       </c>
       <c r="K799" s="4"/>
       <c r="L799" s="4" t="s">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="M799" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="N799" s="4"/>
       <c r="O799" s="4" t="s">
@@ -71897,22 +71847,26 @@
         <v>160</v>
       </c>
       <c r="S799" s="4">
-        <v>174754.68</v>
+        <v>149586.29</v>
       </c>
       <c r="T799" s="4">
         <v>1</v>
       </c>
-      <c r="U799" s="4"/>
-      <c r="V799" s="4"/>
+      <c r="U799" s="4" t="s">
+        <v>3156</v>
+      </c>
+      <c r="V799" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="W799" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="X799" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y799" s="4"/>
       <c r="Z799" s="4" t="s">
-        <v>3156</v>
+        <v>3157</v>
       </c>
       <c r="AA799" s="4" t="s">
         <v>60</v>
@@ -71929,13 +71883,13 @@
         <v>33</v>
       </c>
       <c r="C800" s="4">
-        <v>170357542</v>
+        <v>167735211</v>
       </c>
       <c r="D800" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E800" s="4">
-        <v>5611793</v>
+        <v>5601803</v>
       </c>
       <c r="F800" s="4" t="s">
         <v>140</v>
@@ -71954,36 +71908,32 @@
       </c>
       <c r="K800" s="4"/>
       <c r="L800" s="4" t="s">
-        <v>82</v>
+        <v>592</v>
       </c>
       <c r="M800" s="4" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="N800" s="4"/>
       <c r="O800" s="4" t="s">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="P800" s="5"/>
       <c r="Q800" s="4" t="s">
-        <v>3158</v>
+        <v>3159</v>
       </c>
       <c r="R800" s="4" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="S800" s="4">
-        <v>149586.29</v>
+        <v>0</v>
       </c>
       <c r="T800" s="4">
-        <v>1</v>
-      </c>
-      <c r="U800" s="4" t="s">
-        <v>3159</v>
-      </c>
-      <c r="V800" s="4" t="s">
-        <v>153</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U800" s="4"/>
+      <c r="V800" s="4"/>
       <c r="W800" s="4">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="X800" s="4" t="s">
         <v>46</v>
@@ -72007,13 +71957,13 @@
         <v>33</v>
       </c>
       <c r="C801" s="4">
-        <v>169614022</v>
+        <v>170347021</v>
       </c>
       <c r="D801" s="4" t="s">
-        <v>470</v>
+        <v>34</v>
       </c>
       <c r="E801" s="4">
-        <v>5601178</v>
+        <v>6519374</v>
       </c>
       <c r="F801" s="4" t="s">
         <v>140</v>
@@ -72032,10 +71982,10 @@
       </c>
       <c r="K801" s="4"/>
       <c r="L801" s="4" t="s">
-        <v>313</v>
+        <v>453</v>
       </c>
       <c r="M801" s="4" t="s">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="N801" s="4"/>
       <c r="O801" s="4" t="s">
@@ -72043,34 +71993,32 @@
       </c>
       <c r="P801" s="5"/>
       <c r="Q801" s="4" t="s">
-        <v>3143</v>
+        <v>3162</v>
       </c>
       <c r="R801" s="4" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="S801" s="4">
-        <v>14679525.87</v>
+        <v>0</v>
       </c>
       <c r="T801" s="4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U801" s="4"/>
       <c r="V801" s="4"/>
       <c r="W801" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X801" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y801" s="4"/>
       <c r="Z801" s="4" t="s">
-        <v>3162</v>
-      </c>
-      <c r="AA801" s="4" t="s">
-        <v>114</v>
-      </c>
+        <v>3163</v>
+      </c>
+      <c r="AA801" s="4"/>
       <c r="AB801" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="802" spans="1:28">
@@ -72081,13 +72029,13 @@
         <v>33</v>
       </c>
       <c r="C802" s="4">
-        <v>167735211</v>
+        <v>168524461</v>
       </c>
       <c r="D802" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E802" s="4">
-        <v>5601803</v>
+        <v>7736620</v>
       </c>
       <c r="F802" s="4" t="s">
         <v>140</v>
@@ -72106,18 +72054,20 @@
       </c>
       <c r="K802" s="4"/>
       <c r="L802" s="4" t="s">
-        <v>592</v>
+        <v>453</v>
       </c>
       <c r="M802" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="N802" s="4"/>
+        <v>157</v>
+      </c>
+      <c r="N802" s="4">
+        <v>32</v>
+      </c>
       <c r="O802" s="4" t="s">
-        <v>3163</v>
+        <v>3164</v>
       </c>
       <c r="P802" s="5"/>
       <c r="Q802" s="4" t="s">
-        <v>3164</v>
+        <v>3165</v>
       </c>
       <c r="R802" s="4" t="s">
         <v>56</v>
@@ -72131,14 +72081,14 @@
       <c r="U802" s="4"/>
       <c r="V802" s="4"/>
       <c r="W802" s="4">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="X802" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y802" s="4"/>
       <c r="Z802" s="4" t="s">
-        <v>3165</v>
+        <v>3166</v>
       </c>
       <c r="AA802" s="4" t="s">
         <v>60</v>
@@ -72155,13 +72105,13 @@
         <v>33</v>
       </c>
       <c r="C803" s="4">
-        <v>170347021</v>
+        <v>170208734</v>
       </c>
       <c r="D803" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E803" s="4">
-        <v>6519374</v>
+        <v>5604952</v>
       </c>
       <c r="F803" s="4" t="s">
         <v>140</v>
@@ -72180,21 +72130,21 @@
       </c>
       <c r="K803" s="4"/>
       <c r="L803" s="4" t="s">
-        <v>453</v>
+        <v>320</v>
       </c>
       <c r="M803" s="4" t="s">
-        <v>126</v>
+        <v>199</v>
       </c>
       <c r="N803" s="4"/>
       <c r="O803" s="4" t="s">
-        <v>3166</v>
+        <v>3167</v>
       </c>
       <c r="P803" s="5"/>
       <c r="Q803" s="4" t="s">
-        <v>3167</v>
+        <v>3168</v>
       </c>
       <c r="R803" s="4" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="S803" s="4">
         <v>0</v>
@@ -72205,14 +72155,14 @@
       <c r="U803" s="4"/>
       <c r="V803" s="4"/>
       <c r="W803" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X803" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y803" s="4"/>
       <c r="Z803" s="4" t="s">
-        <v>3168</v>
+        <v>3169</v>
       </c>
       <c r="AA803" s="4"/>
       <c r="AB803" s="4" t="s">
@@ -72227,13 +72177,13 @@
         <v>33</v>
       </c>
       <c r="C804" s="4">
-        <v>168524461</v>
+        <v>167797352</v>
       </c>
       <c r="D804" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E804" s="4">
-        <v>7736620</v>
+        <v>5601086</v>
       </c>
       <c r="F804" s="4" t="s">
         <v>140</v>
@@ -72252,20 +72202,18 @@
       </c>
       <c r="K804" s="4"/>
       <c r="L804" s="4" t="s">
-        <v>453</v>
+        <v>53</v>
       </c>
       <c r="M804" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="N804" s="4">
-        <v>32</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="N804" s="4"/>
       <c r="O804" s="4" t="s">
-        <v>3169</v>
+        <v>3170</v>
       </c>
       <c r="P804" s="5"/>
       <c r="Q804" s="4" t="s">
-        <v>3170</v>
+        <v>3171</v>
       </c>
       <c r="R804" s="4" t="s">
         <v>56</v>
@@ -72279,14 +72227,14 @@
       <c r="U804" s="4"/>
       <c r="V804" s="4"/>
       <c r="W804" s="4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="X804" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y804" s="4"/>
       <c r="Z804" s="4" t="s">
-        <v>3171</v>
+        <v>3172</v>
       </c>
       <c r="AA804" s="4" t="s">
         <v>60</v>
@@ -72303,13 +72251,13 @@
         <v>33</v>
       </c>
       <c r="C805" s="4">
-        <v>170208734</v>
+        <v>170153328</v>
       </c>
       <c r="D805" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E805" s="4">
-        <v>5604952</v>
+        <v>7895012</v>
       </c>
       <c r="F805" s="4" t="s">
         <v>140</v>
@@ -72328,41 +72276,43 @@
       </c>
       <c r="K805" s="4"/>
       <c r="L805" s="4" t="s">
-        <v>320</v>
+        <v>68</v>
       </c>
       <c r="M805" s="4" t="s">
-        <v>199</v>
+        <v>453</v>
       </c>
       <c r="N805" s="4"/>
       <c r="O805" s="4" t="s">
-        <v>3172</v>
+        <v>3173</v>
       </c>
       <c r="P805" s="5"/>
       <c r="Q805" s="4" t="s">
-        <v>3173</v>
+        <v>3174</v>
       </c>
       <c r="R805" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="S805" s="4">
-        <v>0</v>
+        <v>394848.18</v>
       </c>
       <c r="T805" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U805" s="4"/>
       <c r="V805" s="4"/>
       <c r="W805" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X805" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y805" s="4"/>
       <c r="Z805" s="4" t="s">
-        <v>3174</v>
-      </c>
-      <c r="AA805" s="4"/>
+        <v>3175</v>
+      </c>
+      <c r="AA805" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="AB805" s="4" t="s">
         <v>61</v>
       </c>
@@ -72375,13 +72325,13 @@
         <v>33</v>
       </c>
       <c r="C806" s="4">
-        <v>167797352</v>
+        <v>167340150</v>
       </c>
       <c r="D806" s="4" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="E806" s="4">
-        <v>5601086</v>
+        <v>6830468</v>
       </c>
       <c r="F806" s="4" t="s">
         <v>140</v>
@@ -72393,52 +72343,48 @@
         <v>3094</v>
       </c>
       <c r="I806" s="4" t="s">
-        <v>3094</v>
+        <v>3176</v>
       </c>
       <c r="J806" s="4" t="s">
-        <v>184</v>
+        <v>3176</v>
       </c>
       <c r="K806" s="4"/>
-      <c r="L806" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="M806" s="4" t="s">
-        <v>82</v>
-      </c>
+      <c r="L806" s="4"/>
+      <c r="M806" s="4"/>
       <c r="N806" s="4"/>
       <c r="O806" s="4" t="s">
-        <v>3175</v>
+        <v>3177</v>
       </c>
       <c r="P806" s="5"/>
       <c r="Q806" s="4" t="s">
-        <v>3176</v>
+        <v>3178</v>
       </c>
       <c r="R806" s="4" t="s">
         <v>56</v>
       </c>
       <c r="S806" s="4">
-        <v>0</v>
+        <v>3915397.51</v>
       </c>
       <c r="T806" s="4">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="U806" s="4"/>
       <c r="V806" s="4"/>
       <c r="W806" s="4">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="X806" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y806" s="4"/>
       <c r="Z806" s="4" t="s">
-        <v>3177</v>
+        <v>174</v>
       </c>
       <c r="AA806" s="4" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="AB806" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="807" spans="1:28">
@@ -72449,13 +72395,13 @@
         <v>33</v>
       </c>
       <c r="C807" s="4">
-        <v>170153328</v>
+        <v>167913191</v>
       </c>
       <c r="D807" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E807" s="4">
-        <v>7895012</v>
+        <v>5607309</v>
       </c>
       <c r="F807" s="4" t="s">
         <v>140</v>
@@ -72467,50 +72413,48 @@
         <v>3094</v>
       </c>
       <c r="I807" s="4" t="s">
-        <v>3094</v>
+        <v>3176</v>
       </c>
       <c r="J807" s="4" t="s">
-        <v>184</v>
+        <v>3176</v>
       </c>
       <c r="K807" s="4"/>
-      <c r="L807" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="M807" s="4" t="s">
-        <v>453</v>
-      </c>
+      <c r="L807" s="4"/>
+      <c r="M807" s="4"/>
       <c r="N807" s="4"/>
       <c r="O807" s="4" t="s">
-        <v>3178</v>
+        <v>3179</v>
       </c>
       <c r="P807" s="5"/>
       <c r="Q807" s="4" t="s">
-        <v>3179</v>
+        <v>3180</v>
       </c>
       <c r="R807" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="S807" s="4">
-        <v>394848.18</v>
+        <v>3760336.56</v>
       </c>
       <c r="T807" s="4">
-        <v>1</v>
-      </c>
-      <c r="U807" s="4"/>
-      <c r="V807" s="4"/>
+        <v>41</v>
+      </c>
+      <c r="U807" s="4" t="s">
+        <v>3181</v>
+      </c>
+      <c r="V807" s="4" t="s">
+        <v>173</v>
+      </c>
       <c r="W807" s="4">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="X807" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y807" s="4"/>
       <c r="Z807" s="4" t="s">
-        <v>3180</v>
-      </c>
-      <c r="AA807" s="4" t="s">
-        <v>60</v>
-      </c>
+        <v>3182</v>
+      </c>
+      <c r="AA807" s="4"/>
       <c r="AB807" s="4" t="s">
         <v>61</v>
       </c>
@@ -72523,13 +72467,13 @@
         <v>33</v>
       </c>
       <c r="C808" s="4">
-        <v>167340150</v>
+        <v>169525453</v>
       </c>
       <c r="D808" s="4" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="E808" s="4">
-        <v>6830468</v>
+        <v>5609399</v>
       </c>
       <c r="F808" s="4" t="s">
         <v>140</v>
@@ -72541,48 +72485,58 @@
         <v>3094</v>
       </c>
       <c r="I808" s="4" t="s">
-        <v>3181</v>
+        <v>3094</v>
       </c>
       <c r="J808" s="4" t="s">
-        <v>3181</v>
+        <v>3183</v>
       </c>
       <c r="K808" s="4"/>
-      <c r="L808" s="4"/>
-      <c r="M808" s="4"/>
-      <c r="N808" s="4"/>
+      <c r="L808" s="4" t="s">
+        <v>3184</v>
+      </c>
+      <c r="M808" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="N808" s="4">
+        <v>80</v>
+      </c>
       <c r="O808" s="4" t="s">
-        <v>3182</v>
+        <v>3185</v>
       </c>
       <c r="P808" s="5"/>
       <c r="Q808" s="4" t="s">
-        <v>3183</v>
+        <v>3186</v>
       </c>
       <c r="R808" s="4" t="s">
         <v>56</v>
       </c>
       <c r="S808" s="4">
-        <v>3915397.51</v>
+        <v>0</v>
       </c>
       <c r="T808" s="4">
-        <v>72</v>
-      </c>
-      <c r="U808" s="4"/>
-      <c r="V808" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U808" s="4" t="s">
+        <v>3187</v>
+      </c>
+      <c r="V808" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="W808" s="4">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="X808" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y808" s="4"/>
       <c r="Z808" s="4" t="s">
-        <v>174</v>
+        <v>3188</v>
       </c>
       <c r="AA808" s="4" t="s">
         <v>79</v>
       </c>
       <c r="AB808" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="809" spans="1:28">
@@ -72593,13 +72547,13 @@
         <v>33</v>
       </c>
       <c r="C809" s="4">
-        <v>167913191</v>
+        <v>170060002</v>
       </c>
       <c r="D809" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E809" s="4">
-        <v>5607309</v>
+        <v>5608557</v>
       </c>
       <c r="F809" s="4" t="s">
         <v>140</v>
@@ -72611,48 +72565,52 @@
         <v>3094</v>
       </c>
       <c r="I809" s="4" t="s">
-        <v>3181</v>
+        <v>3094</v>
       </c>
       <c r="J809" s="4" t="s">
-        <v>3181</v>
+        <v>3189</v>
       </c>
       <c r="K809" s="4"/>
-      <c r="L809" s="4"/>
-      <c r="M809" s="4"/>
-      <c r="N809" s="4"/>
+      <c r="L809" s="4" t="s">
+        <v>2089</v>
+      </c>
+      <c r="M809" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="N809" s="4">
+        <v>7</v>
+      </c>
       <c r="O809" s="4" t="s">
-        <v>3184</v>
+        <v>3190</v>
       </c>
       <c r="P809" s="5"/>
       <c r="Q809" s="4" t="s">
-        <v>3185</v>
+        <v>3191</v>
       </c>
       <c r="R809" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S809" s="4">
-        <v>3760336.56</v>
+        <v>344528.72</v>
       </c>
       <c r="T809" s="4">
-        <v>41</v>
-      </c>
-      <c r="U809" s="4" t="s">
-        <v>3186</v>
-      </c>
-      <c r="V809" s="4" t="s">
-        <v>173</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U809" s="4"/>
+      <c r="V809" s="4"/>
       <c r="W809" s="4">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="X809" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y809" s="4"/>
       <c r="Z809" s="4" t="s">
-        <v>3187</v>
-      </c>
-      <c r="AA809" s="4"/>
+        <v>3192</v>
+      </c>
+      <c r="AA809" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB809" s="4" t="s">
         <v>61</v>
       </c>
@@ -72665,13 +72623,13 @@
         <v>33</v>
       </c>
       <c r="C810" s="4">
-        <v>169525453</v>
+        <v>170213202</v>
       </c>
       <c r="D810" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E810" s="4">
-        <v>5609399</v>
+        <v>5605891</v>
       </c>
       <c r="F810" s="4" t="s">
         <v>140</v>
@@ -72686,49 +72644,45 @@
         <v>3094</v>
       </c>
       <c r="J810" s="4" t="s">
-        <v>3188</v>
+        <v>3193</v>
       </c>
       <c r="K810" s="4"/>
       <c r="L810" s="4" t="s">
-        <v>3189</v>
+        <v>110</v>
       </c>
       <c r="M810" s="4" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="N810" s="4">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="O810" s="4" t="s">
-        <v>3190</v>
+        <v>3194</v>
       </c>
       <c r="P810" s="5"/>
       <c r="Q810" s="4" t="s">
-        <v>3191</v>
+        <v>3195</v>
       </c>
       <c r="R810" s="4" t="s">
         <v>56</v>
       </c>
       <c r="S810" s="4">
-        <v>0</v>
+        <v>104784.93</v>
       </c>
       <c r="T810" s="4">
-        <v>0</v>
-      </c>
-      <c r="U810" s="4" t="s">
-        <v>3192</v>
-      </c>
-      <c r="V810" s="4" t="s">
-        <v>137</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U810" s="4"/>
+      <c r="V810" s="4"/>
       <c r="W810" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="X810" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y810" s="4"/>
       <c r="Z810" s="4" t="s">
-        <v>3193</v>
+        <v>3196</v>
       </c>
       <c r="AA810" s="4" t="s">
         <v>79</v>
@@ -72745,13 +72699,13 @@
         <v>33</v>
       </c>
       <c r="C811" s="4">
-        <v>170060002</v>
+        <v>169511808</v>
       </c>
       <c r="D811" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E811" s="4">
-        <v>5608557</v>
+        <v>1100825</v>
       </c>
       <c r="F811" s="4" t="s">
         <v>140</v>
@@ -72766,30 +72720,28 @@
         <v>3094</v>
       </c>
       <c r="J811" s="4" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="K811" s="4"/>
       <c r="L811" s="4" t="s">
-        <v>2089</v>
+        <v>116</v>
       </c>
       <c r="M811" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="N811" s="4">
-        <v>7</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N811" s="4"/>
       <c r="O811" s="4" t="s">
-        <v>3195</v>
+        <v>3197</v>
       </c>
       <c r="P811" s="5"/>
       <c r="Q811" s="4" t="s">
-        <v>3196</v>
+        <v>3198</v>
       </c>
       <c r="R811" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S811" s="4">
-        <v>344528.72</v>
+        <v>32081.95</v>
       </c>
       <c r="T811" s="4">
         <v>1</v>
@@ -72797,20 +72749,20 @@
       <c r="U811" s="4"/>
       <c r="V811" s="4"/>
       <c r="W811" s="4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="X811" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y811" s="4"/>
       <c r="Z811" s="4" t="s">
-        <v>3197</v>
+        <v>3199</v>
       </c>
       <c r="AA811" s="4" t="s">
         <v>79</v>
       </c>
       <c r="AB811" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="812" spans="1:28">
@@ -72821,13 +72773,13 @@
         <v>33</v>
       </c>
       <c r="C812" s="4">
-        <v>170213202</v>
+        <v>170178674</v>
       </c>
       <c r="D812" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E812" s="4">
-        <v>5605891</v>
+        <v>5608824</v>
       </c>
       <c r="F812" s="4" t="s">
         <v>140</v>
@@ -72842,30 +72794,30 @@
         <v>3094</v>
       </c>
       <c r="J812" s="4" t="s">
-        <v>3198</v>
+        <v>3200</v>
       </c>
       <c r="K812" s="4"/>
       <c r="L812" s="4" t="s">
-        <v>110</v>
+        <v>3115</v>
       </c>
       <c r="M812" s="4" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="N812" s="4">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="O812" s="4" t="s">
-        <v>3199</v>
+        <v>3201</v>
       </c>
       <c r="P812" s="5"/>
       <c r="Q812" s="4" t="s">
-        <v>3200</v>
+        <v>3202</v>
       </c>
       <c r="R812" s="4" t="s">
         <v>56</v>
       </c>
       <c r="S812" s="4">
-        <v>104784.93</v>
+        <v>13217.57</v>
       </c>
       <c r="T812" s="4">
         <v>1</v>
@@ -72873,14 +72825,14 @@
       <c r="U812" s="4"/>
       <c r="V812" s="4"/>
       <c r="W812" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X812" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y812" s="4"/>
       <c r="Z812" s="4" t="s">
-        <v>3201</v>
+        <v>3203</v>
       </c>
       <c r="AA812" s="4" t="s">
         <v>79</v>
@@ -72897,13 +72849,13 @@
         <v>33</v>
       </c>
       <c r="C813" s="4">
-        <v>169468959</v>
+        <v>170486377</v>
       </c>
       <c r="D813" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E813" s="4">
-        <v>5610977</v>
+        <v>6649715</v>
       </c>
       <c r="F813" s="4" t="s">
         <v>140</v>
@@ -72918,51 +72870,55 @@
         <v>3094</v>
       </c>
       <c r="J813" s="4" t="s">
-        <v>3198</v>
+        <v>3204</v>
       </c>
       <c r="K813" s="4"/>
       <c r="L813" s="4" t="s">
-        <v>320</v>
+        <v>3205</v>
       </c>
       <c r="M813" s="4" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="N813" s="4">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="O813" s="4" t="s">
-        <v>3202</v>
+        <v>3206</v>
       </c>
       <c r="P813" s="5"/>
       <c r="Q813" s="4" t="s">
-        <v>3203</v>
+        <v>3207</v>
       </c>
       <c r="R813" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S813" s="4">
-        <v>0</v>
+        <v>10238169.01</v>
       </c>
       <c r="T813" s="4">
-        <v>0</v>
-      </c>
-      <c r="U813" s="4"/>
-      <c r="V813" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="U813" s="4" t="s">
+        <v>3208</v>
+      </c>
+      <c r="V813" s="4" t="s">
+        <v>1043</v>
+      </c>
       <c r="W813" s="4">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="X813" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y813" s="4"/>
       <c r="Z813" s="4" t="s">
-        <v>3204</v>
+        <v>3209</v>
       </c>
       <c r="AA813" s="4" t="s">
         <v>79</v>
       </c>
       <c r="AB813" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="814" spans="1:28">
@@ -72970,16 +72926,16 @@
         <v>1000</v>
       </c>
       <c r="B814" s="4" t="s">
-        <v>33</v>
+        <v>590</v>
       </c>
       <c r="C814" s="4">
-        <v>169469893</v>
+        <v>170404515</v>
       </c>
       <c r="D814" s="4" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="E814" s="4">
-        <v>5605073</v>
+        <v>5601124</v>
       </c>
       <c r="F814" s="4" t="s">
         <v>140</v>
@@ -72994,24 +72950,22 @@
         <v>3094</v>
       </c>
       <c r="J814" s="4" t="s">
-        <v>3198</v>
+        <v>915</v>
       </c>
       <c r="K814" s="4"/>
       <c r="L814" s="4" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="M814" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="N814" s="4">
-        <v>51</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="N814" s="4"/>
       <c r="O814" s="4" t="s">
-        <v>3205</v>
+        <v>3210</v>
       </c>
       <c r="P814" s="5"/>
       <c r="Q814" s="4" t="s">
-        <v>3206</v>
+        <v>3211</v>
       </c>
       <c r="R814" s="4" t="s">
         <v>56</v>
@@ -73022,21 +72976,17 @@
       <c r="T814" s="4">
         <v>0</v>
       </c>
-      <c r="U814" s="4" t="s">
-        <v>3207</v>
-      </c>
-      <c r="V814" s="4" t="s">
-        <v>570</v>
-      </c>
+      <c r="U814" s="4"/>
+      <c r="V814" s="4"/>
       <c r="W814" s="4">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="X814" s="4" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="Y814" s="4"/>
       <c r="Z814" s="4" t="s">
-        <v>3208</v>
+        <v>3212</v>
       </c>
       <c r="AA814" s="4" t="s">
         <v>60</v>
@@ -73053,13 +73003,13 @@
         <v>33</v>
       </c>
       <c r="C815" s="4">
-        <v>169511808</v>
+        <v>170212869</v>
       </c>
       <c r="D815" s="4" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="E815" s="4">
-        <v>1100825</v>
+        <v>5608430</v>
       </c>
       <c r="F815" s="4" t="s">
         <v>140</v>
@@ -73071,52 +73021,54 @@
         <v>3094</v>
       </c>
       <c r="I815" s="4" t="s">
-        <v>3094</v>
+        <v>3213</v>
       </c>
       <c r="J815" s="4" t="s">
-        <v>3198</v>
+        <v>3213</v>
       </c>
       <c r="K815" s="4"/>
       <c r="L815" s="4" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="M815" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="N815" s="4"/>
+        <v>81</v>
+      </c>
+      <c r="N815" s="4">
+        <v>63</v>
+      </c>
       <c r="O815" s="4" t="s">
-        <v>3209</v>
+        <v>3214</v>
       </c>
       <c r="P815" s="5"/>
       <c r="Q815" s="4" t="s">
-        <v>3210</v>
+        <v>3215</v>
       </c>
       <c r="R815" s="4" t="s">
         <v>56</v>
       </c>
       <c r="S815" s="4">
-        <v>32081.95</v>
+        <v>2367256.82</v>
       </c>
       <c r="T815" s="4">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="U815" s="4"/>
       <c r="V815" s="4"/>
       <c r="W815" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="X815" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y815" s="4"/>
       <c r="Z815" s="4" t="s">
-        <v>3211</v>
+        <v>174</v>
       </c>
       <c r="AA815" s="4" t="s">
         <v>79</v>
       </c>
       <c r="AB815" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="816" spans="1:28">
@@ -73127,13 +73079,13 @@
         <v>33</v>
       </c>
       <c r="C816" s="4">
-        <v>170178674</v>
+        <v>170489233</v>
       </c>
       <c r="D816" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E816" s="4">
-        <v>5608824</v>
+        <v>8323048</v>
       </c>
       <c r="F816" s="4" t="s">
         <v>140</v>
@@ -73148,51 +73100,51 @@
         <v>3094</v>
       </c>
       <c r="J816" s="4" t="s">
-        <v>3212</v>
+        <v>1647</v>
       </c>
       <c r="K816" s="4"/>
       <c r="L816" s="4" t="s">
-        <v>3118</v>
+        <v>3216</v>
       </c>
       <c r="M816" s="4" t="s">
-        <v>194</v>
+        <v>2320</v>
       </c>
       <c r="N816" s="4">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="O816" s="4" t="s">
-        <v>3213</v>
+        <v>3217</v>
       </c>
       <c r="P816" s="5"/>
       <c r="Q816" s="4" t="s">
-        <v>3214</v>
+        <v>3218</v>
       </c>
       <c r="R816" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S816" s="4">
-        <v>13217.57</v>
+        <v>2286132.14</v>
       </c>
       <c r="T816" s="4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U816" s="4"/>
       <c r="V816" s="4"/>
       <c r="W816" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X816" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y816" s="4"/>
       <c r="Z816" s="4" t="s">
-        <v>3215</v>
+        <v>3219</v>
       </c>
       <c r="AA816" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="AB816" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="817" spans="1:28">
@@ -73203,13 +73155,13 @@
         <v>33</v>
       </c>
       <c r="C817" s="4">
-        <v>170486377</v>
+        <v>170489591</v>
       </c>
       <c r="D817" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E817" s="4">
-        <v>6649715</v>
+        <v>8239823</v>
       </c>
       <c r="F817" s="4" t="s">
         <v>140</v>
@@ -73224,40 +73176,36 @@
         <v>3094</v>
       </c>
       <c r="J817" s="4" t="s">
-        <v>3216</v>
+        <v>1647</v>
       </c>
       <c r="K817" s="4"/>
       <c r="L817" s="4" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="M817" s="4" t="s">
-        <v>126</v>
+        <v>2320</v>
       </c>
       <c r="N817" s="4">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="O817" s="4" t="s">
-        <v>3218</v>
+        <v>3220</v>
       </c>
       <c r="P817" s="5"/>
       <c r="Q817" s="4" t="s">
-        <v>3219</v>
+        <v>3221</v>
       </c>
       <c r="R817" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S817" s="4">
-        <v>10238169.01</v>
+        <v>66636.88</v>
       </c>
       <c r="T817" s="4">
-        <v>75</v>
-      </c>
-      <c r="U817" s="4" t="s">
-        <v>3220</v>
-      </c>
-      <c r="V817" s="4" t="s">
-        <v>1043</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U817" s="4"/>
+      <c r="V817" s="4"/>
       <c r="W817" s="4">
         <v>1</v>
       </c>
@@ -73266,13 +73214,13 @@
       </c>
       <c r="Y817" s="4"/>
       <c r="Z817" s="4" t="s">
-        <v>3221</v>
+        <v>3222</v>
       </c>
       <c r="AA817" s="4" t="s">
         <v>79</v>
       </c>
       <c r="AB817" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="818" spans="1:28">
@@ -73280,16 +73228,16 @@
         <v>1000</v>
       </c>
       <c r="B818" s="4" t="s">
-        <v>590</v>
+        <v>33</v>
       </c>
       <c r="C818" s="4">
-        <v>170404515</v>
+        <v>170328348</v>
       </c>
       <c r="D818" s="4" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="E818" s="4">
-        <v>5601124</v>
+        <v>5608058</v>
       </c>
       <c r="F818" s="4" t="s">
         <v>140</v>
@@ -73301,25 +73249,27 @@
         <v>3094</v>
       </c>
       <c r="I818" s="4" t="s">
-        <v>3094</v>
+        <v>3223</v>
       </c>
       <c r="J818" s="4" t="s">
-        <v>915</v>
+        <v>3223</v>
       </c>
       <c r="K818" s="4"/>
       <c r="L818" s="4" t="s">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="M818" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="N818" s="4"/>
+        <v>105</v>
+      </c>
+      <c r="N818" s="4">
+        <v>33</v>
+      </c>
       <c r="O818" s="4" t="s">
-        <v>3222</v>
+        <v>3224</v>
       </c>
       <c r="P818" s="5"/>
       <c r="Q818" s="4" t="s">
-        <v>3223</v>
+        <v>3225</v>
       </c>
       <c r="R818" s="4" t="s">
         <v>56</v>
@@ -73330,21 +73280,23 @@
       <c r="T818" s="4">
         <v>0</v>
       </c>
-      <c r="U818" s="4"/>
-      <c r="V818" s="4"/>
+      <c r="U818" s="4" t="s">
+        <v>3226</v>
+      </c>
+      <c r="V818" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="W818" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X818" s="4" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="Y818" s="4"/>
       <c r="Z818" s="4" t="s">
-        <v>3224</v>
-      </c>
-      <c r="AA818" s="4" t="s">
-        <v>60</v>
-      </c>
+        <v>3227</v>
+      </c>
+      <c r="AA818" s="4"/>
       <c r="AB818" s="4" t="s">
         <v>61</v>
       </c>
@@ -73357,13 +73309,13 @@
         <v>33</v>
       </c>
       <c r="C819" s="4">
-        <v>170212869</v>
+        <v>170346662</v>
       </c>
       <c r="D819" s="4" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="E819" s="4">
-        <v>5608430</v>
+        <v>7558292</v>
       </c>
       <c r="F819" s="4" t="s">
         <v>140</v>
@@ -73375,51 +73327,51 @@
         <v>3094</v>
       </c>
       <c r="I819" s="4" t="s">
-        <v>3225</v>
+        <v>3094</v>
       </c>
       <c r="J819" s="4" t="s">
-        <v>3225</v>
+        <v>928</v>
       </c>
       <c r="K819" s="4"/>
       <c r="L819" s="4" t="s">
         <v>82</v>
       </c>
       <c r="M819" s="4" t="s">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="N819" s="4">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="O819" s="4" t="s">
-        <v>3226</v>
+        <v>3228</v>
       </c>
       <c r="P819" s="5"/>
       <c r="Q819" s="4" t="s">
-        <v>3227</v>
+        <v>3229</v>
       </c>
       <c r="R819" s="4" t="s">
         <v>56</v>
       </c>
       <c r="S819" s="4">
-        <v>2367256.82</v>
+        <v>350358.3</v>
       </c>
       <c r="T819" s="4">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="U819" s="4"/>
       <c r="V819" s="4"/>
       <c r="W819" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X819" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y819" s="4"/>
       <c r="Z819" s="4" t="s">
-        <v>174</v>
+        <v>273</v>
       </c>
       <c r="AA819" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="AB819" s="4" t="s">
         <v>61</v>
@@ -73433,13 +73385,13 @@
         <v>33</v>
       </c>
       <c r="C820" s="4">
-        <v>170489233</v>
+        <v>170152547</v>
       </c>
       <c r="D820" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E820" s="4">
-        <v>8323048</v>
+        <v>5602892</v>
       </c>
       <c r="F820" s="4" t="s">
         <v>140</v>
@@ -73454,51 +73406,51 @@
         <v>3094</v>
       </c>
       <c r="J820" s="4" t="s">
-        <v>1647</v>
+        <v>928</v>
       </c>
       <c r="K820" s="4"/>
       <c r="L820" s="4" t="s">
-        <v>3228</v>
+        <v>335</v>
       </c>
       <c r="M820" s="4" t="s">
-        <v>2320</v>
+        <v>592</v>
       </c>
       <c r="N820" s="4">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="O820" s="4" t="s">
-        <v>3229</v>
+        <v>3230</v>
       </c>
       <c r="P820" s="5"/>
       <c r="Q820" s="4" t="s">
-        <v>3230</v>
+        <v>3231</v>
       </c>
       <c r="R820" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S820" s="4">
-        <v>2286132.14</v>
+        <v>0</v>
       </c>
       <c r="T820" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="U820" s="4"/>
       <c r="V820" s="4"/>
       <c r="W820" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X820" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y820" s="4"/>
       <c r="Z820" s="4" t="s">
-        <v>3231</v>
+        <v>3232</v>
       </c>
       <c r="AA820" s="4" t="s">
         <v>60</v>
       </c>
       <c r="AB820" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="821" spans="1:28">
@@ -73509,13 +73461,13 @@
         <v>33</v>
       </c>
       <c r="C821" s="4">
-        <v>170489591</v>
+        <v>170162745</v>
       </c>
       <c r="D821" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E821" s="4">
-        <v>8239823</v>
+        <v>6264608</v>
       </c>
       <c r="F821" s="4" t="s">
         <v>140</v>
@@ -73530,45 +73482,47 @@
         <v>3094</v>
       </c>
       <c r="J821" s="4" t="s">
-        <v>1647</v>
+        <v>3233</v>
       </c>
       <c r="K821" s="4"/>
       <c r="L821" s="4" t="s">
-        <v>3228</v>
+        <v>2094</v>
       </c>
       <c r="M821" s="4" t="s">
-        <v>2320</v>
-      </c>
-      <c r="N821" s="4">
-        <v>19</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="N821" s="4"/>
       <c r="O821" s="4" t="s">
-        <v>3232</v>
+        <v>3234</v>
       </c>
       <c r="P821" s="5"/>
       <c r="Q821" s="4" t="s">
-        <v>3233</v>
+        <v>3235</v>
       </c>
       <c r="R821" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S821" s="4">
-        <v>66636.88</v>
+        <v>0</v>
       </c>
       <c r="T821" s="4">
-        <v>2</v>
-      </c>
-      <c r="U821" s="4"/>
-      <c r="V821" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U821" s="4" t="s">
+        <v>3236</v>
+      </c>
+      <c r="V821" s="4" t="s">
+        <v>217</v>
+      </c>
       <c r="W821" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X821" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y821" s="4"/>
       <c r="Z821" s="4" t="s">
-        <v>3234</v>
+        <v>3237</v>
       </c>
       <c r="AA821" s="4" t="s">
         <v>79</v>
@@ -73585,13 +73539,13 @@
         <v>33</v>
       </c>
       <c r="C822" s="4">
-        <v>169714757</v>
+        <v>170416897</v>
       </c>
       <c r="D822" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E822" s="4">
-        <v>7508965</v>
+        <v>6500832</v>
       </c>
       <c r="F822" s="4" t="s">
         <v>140</v>
@@ -73606,53 +73560,47 @@
         <v>3094</v>
       </c>
       <c r="J822" s="4" t="s">
-        <v>1647</v>
+        <v>3238</v>
       </c>
       <c r="K822" s="4"/>
       <c r="L822" s="4" t="s">
-        <v>3228</v>
+        <v>884</v>
       </c>
       <c r="M822" s="4" t="s">
-        <v>2320</v>
+        <v>3119</v>
       </c>
       <c r="N822" s="4">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="O822" s="4" t="s">
-        <v>3235</v>
+        <v>3239</v>
       </c>
       <c r="P822" s="5"/>
       <c r="Q822" s="4" t="s">
-        <v>3236</v>
+        <v>3240</v>
       </c>
       <c r="R822" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S822" s="4">
-        <v>110830.1</v>
+        <v>25584</v>
       </c>
       <c r="T822" s="4">
         <v>1</v>
       </c>
-      <c r="U822" s="4" t="s">
-        <v>3237</v>
-      </c>
-      <c r="V822" s="4" t="s">
-        <v>510</v>
-      </c>
+      <c r="U822" s="4"/>
+      <c r="V822" s="4"/>
       <c r="W822" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="X822" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y822" s="4"/>
       <c r="Z822" s="4" t="s">
-        <v>3238</v>
-      </c>
-      <c r="AA822" s="4" t="s">
-        <v>60</v>
-      </c>
+        <v>3241</v>
+      </c>
+      <c r="AA822" s="4"/>
       <c r="AB822" s="4" t="s">
         <v>61</v>
       </c>
@@ -73665,13 +73613,13 @@
         <v>33</v>
       </c>
       <c r="C823" s="4">
-        <v>170328348</v>
+        <v>168730365</v>
       </c>
       <c r="D823" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E823" s="4">
-        <v>5608058</v>
+        <v>7618038</v>
       </c>
       <c r="F823" s="4" t="s">
         <v>140</v>
@@ -73683,27 +73631,27 @@
         <v>3094</v>
       </c>
       <c r="I823" s="4" t="s">
-        <v>3239</v>
+        <v>3094</v>
       </c>
       <c r="J823" s="4" t="s">
-        <v>3239</v>
+        <v>3242</v>
       </c>
       <c r="K823" s="4"/>
       <c r="L823" s="4" t="s">
-        <v>82</v>
+        <v>2089</v>
       </c>
       <c r="M823" s="4" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="N823" s="4">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="O823" s="4" t="s">
-        <v>3240</v>
+        <v>3243</v>
       </c>
       <c r="P823" s="5"/>
       <c r="Q823" s="4" t="s">
-        <v>3241</v>
+        <v>3244</v>
       </c>
       <c r="R823" s="4" t="s">
         <v>56</v>
@@ -73714,23 +73662,21 @@
       <c r="T823" s="4">
         <v>0</v>
       </c>
-      <c r="U823" s="4" t="s">
-        <v>3242</v>
-      </c>
-      <c r="V823" s="4" t="s">
-        <v>86</v>
-      </c>
+      <c r="U823" s="4"/>
+      <c r="V823" s="4"/>
       <c r="W823" s="4">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="X823" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y823" s="4"/>
       <c r="Z823" s="4" t="s">
-        <v>3243</v>
-      </c>
-      <c r="AA823" s="4"/>
+        <v>3245</v>
+      </c>
+      <c r="AA823" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB823" s="4" t="s">
         <v>61</v>
       </c>
@@ -73743,13 +73689,13 @@
         <v>33</v>
       </c>
       <c r="C824" s="4">
-        <v>170346662</v>
+        <v>169473857</v>
       </c>
       <c r="D824" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E824" s="4">
-        <v>7558292</v>
+        <v>6854484</v>
       </c>
       <c r="F824" s="4" t="s">
         <v>140</v>
@@ -73764,49 +73710,51 @@
         <v>3094</v>
       </c>
       <c r="J824" s="4" t="s">
-        <v>928</v>
+        <v>3242</v>
       </c>
       <c r="K824" s="4"/>
       <c r="L824" s="4" t="s">
-        <v>82</v>
+        <v>3246</v>
       </c>
       <c r="M824" s="4" t="s">
-        <v>335</v>
+        <v>2089</v>
       </c>
       <c r="N824" s="4">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="O824" s="4" t="s">
-        <v>3244</v>
+        <v>3247</v>
       </c>
       <c r="P824" s="5"/>
       <c r="Q824" s="4" t="s">
-        <v>3245</v>
+        <v>3248</v>
       </c>
       <c r="R824" s="4" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="S824" s="4">
-        <v>350358.3</v>
+        <v>2007564.26</v>
       </c>
       <c r="T824" s="4">
-        <v>1</v>
-      </c>
-      <c r="U824" s="4"/>
-      <c r="V824" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="U824" s="4" t="s">
+        <v>3249</v>
+      </c>
+      <c r="V824" s="4" t="s">
+        <v>217</v>
+      </c>
       <c r="W824" s="4">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="X824" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y824" s="4"/>
       <c r="Z824" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="AA824" s="4" t="s">
-        <v>60</v>
-      </c>
+        <v>3250</v>
+      </c>
+      <c r="AA824" s="4"/>
       <c r="AB824" s="4" t="s">
         <v>61</v>
       </c>
@@ -73819,13 +73767,13 @@
         <v>33</v>
       </c>
       <c r="C825" s="4">
-        <v>170152547</v>
+        <v>169514729</v>
       </c>
       <c r="D825" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E825" s="4">
-        <v>5602892</v>
+        <v>8086715</v>
       </c>
       <c r="F825" s="4" t="s">
         <v>140</v>
@@ -73840,48 +73788,42 @@
         <v>3094</v>
       </c>
       <c r="J825" s="4" t="s">
-        <v>928</v>
+        <v>1165</v>
       </c>
       <c r="K825" s="4"/>
-      <c r="L825" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="M825" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="N825" s="4">
-        <v>73</v>
-      </c>
+      <c r="L825" s="4"/>
+      <c r="M825" s="4"/>
+      <c r="N825" s="4"/>
       <c r="O825" s="4" t="s">
-        <v>3246</v>
+        <v>3251</v>
       </c>
       <c r="P825" s="5"/>
       <c r="Q825" s="4" t="s">
-        <v>3247</v>
+        <v>3252</v>
       </c>
       <c r="R825" s="4" t="s">
         <v>56</v>
       </c>
       <c r="S825" s="4">
-        <v>0</v>
+        <v>187735.5</v>
       </c>
       <c r="T825" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U825" s="4"/>
       <c r="V825" s="4"/>
       <c r="W825" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="X825" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y825" s="4"/>
       <c r="Z825" s="4" t="s">
-        <v>3248</v>
+        <v>3253</v>
       </c>
       <c r="AA825" s="4" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="AB825" s="4" t="s">
         <v>61</v>
@@ -73892,16 +73834,16 @@
         <v>1000</v>
       </c>
       <c r="B826" s="4" t="s">
-        <v>33</v>
+        <v>590</v>
       </c>
       <c r="C826" s="4">
-        <v>170162745</v>
+        <v>170411056</v>
       </c>
       <c r="D826" s="4" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="E826" s="4">
-        <v>6264608</v>
+        <v>7762399</v>
       </c>
       <c r="F826" s="4" t="s">
         <v>140</v>
@@ -73916,25 +73858,27 @@
         <v>3094</v>
       </c>
       <c r="J826" s="4" t="s">
-        <v>3249</v>
+        <v>992</v>
       </c>
       <c r="K826" s="4"/>
       <c r="L826" s="4" t="s">
-        <v>2094</v>
+        <v>320</v>
       </c>
       <c r="M826" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="N826" s="4"/>
+      <c r="N826" s="4">
+        <v>56</v>
+      </c>
       <c r="O826" s="4" t="s">
-        <v>3250</v>
+        <v>3254</v>
       </c>
       <c r="P826" s="5"/>
       <c r="Q826" s="4" t="s">
-        <v>3251</v>
+        <v>3255</v>
       </c>
       <c r="R826" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S826" s="4">
         <v>0</v>
@@ -73942,21 +73886,17 @@
       <c r="T826" s="4">
         <v>0</v>
       </c>
-      <c r="U826" s="4" t="s">
-        <v>3252</v>
-      </c>
-      <c r="V826" s="4" t="s">
-        <v>217</v>
-      </c>
+      <c r="U826" s="4"/>
+      <c r="V826" s="4"/>
       <c r="W826" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X826" s="4" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="Y826" s="4"/>
       <c r="Z826" s="4" t="s">
-        <v>3253</v>
+        <v>3256</v>
       </c>
       <c r="AA826" s="4" t="s">
         <v>79</v>
@@ -73973,13 +73913,13 @@
         <v>33</v>
       </c>
       <c r="C827" s="4">
-        <v>170416897</v>
+        <v>170314612</v>
       </c>
       <c r="D827" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E827" s="4">
-        <v>6500832</v>
+        <v>5609410</v>
       </c>
       <c r="F827" s="4" t="s">
         <v>140</v>
@@ -73994,30 +73934,30 @@
         <v>3094</v>
       </c>
       <c r="J827" s="4" t="s">
-        <v>3254</v>
+        <v>992</v>
       </c>
       <c r="K827" s="4"/>
       <c r="L827" s="4" t="s">
-        <v>884</v>
+        <v>3257</v>
       </c>
       <c r="M827" s="4" t="s">
-        <v>3122</v>
+        <v>573</v>
       </c>
       <c r="N827" s="4">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="O827" s="4" t="s">
-        <v>3255</v>
+        <v>3258</v>
       </c>
       <c r="P827" s="5"/>
       <c r="Q827" s="4" t="s">
-        <v>3256</v>
+        <v>3259</v>
       </c>
       <c r="R827" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S827" s="4">
-        <v>25584</v>
+        <v>93755.75</v>
       </c>
       <c r="T827" s="4">
         <v>1</v>
@@ -74025,16 +73965,18 @@
       <c r="U827" s="4"/>
       <c r="V827" s="4"/>
       <c r="W827" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X827" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y827" s="4"/>
       <c r="Z827" s="4" t="s">
-        <v>3257</v>
-      </c>
-      <c r="AA827" s="4"/>
+        <v>3260</v>
+      </c>
+      <c r="AA827" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="AB827" s="4" t="s">
         <v>61</v>
       </c>
@@ -74047,13 +73989,13 @@
         <v>33</v>
       </c>
       <c r="C828" s="4">
-        <v>168730365</v>
+        <v>168721422</v>
       </c>
       <c r="D828" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E828" s="4">
-        <v>7618038</v>
+        <v>7519730</v>
       </c>
       <c r="F828" s="4" t="s">
         <v>140</v>
@@ -74065,30 +74007,24 @@
         <v>3094</v>
       </c>
       <c r="I828" s="4" t="s">
-        <v>3094</v>
+        <v>3261</v>
       </c>
       <c r="J828" s="4" t="s">
-        <v>3258</v>
+        <v>3261</v>
       </c>
       <c r="K828" s="4"/>
-      <c r="L828" s="4" t="s">
-        <v>2089</v>
-      </c>
-      <c r="M828" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="N828" s="4">
-        <v>56</v>
-      </c>
+      <c r="L828" s="4"/>
+      <c r="M828" s="4"/>
+      <c r="N828" s="4"/>
       <c r="O828" s="4" t="s">
-        <v>3259</v>
+        <v>3262</v>
       </c>
       <c r="P828" s="5"/>
       <c r="Q828" s="4" t="s">
-        <v>3260</v>
+        <v>3263</v>
       </c>
       <c r="R828" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S828" s="4">
         <v>0</v>
@@ -74096,21 +74032,23 @@
       <c r="T828" s="4">
         <v>0</v>
       </c>
-      <c r="U828" s="4"/>
-      <c r="V828" s="4"/>
+      <c r="U828" s="4" t="s">
+        <v>3264</v>
+      </c>
+      <c r="V828" s="4" t="s">
+        <v>173</v>
+      </c>
       <c r="W828" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X828" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y828" s="4"/>
       <c r="Z828" s="4" t="s">
-        <v>3261</v>
-      </c>
-      <c r="AA828" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>3265</v>
+      </c>
+      <c r="AA828" s="4"/>
       <c r="AB828" s="4" t="s">
         <v>61</v>
       </c>
@@ -74123,13 +74061,13 @@
         <v>33</v>
       </c>
       <c r="C829" s="4">
-        <v>169473857</v>
+        <v>170058508</v>
       </c>
       <c r="D829" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E829" s="4">
-        <v>6854484</v>
+        <v>7338893</v>
       </c>
       <c r="F829" s="4" t="s">
         <v>140</v>
@@ -74141,56 +74079,52 @@
         <v>3094</v>
       </c>
       <c r="I829" s="4" t="s">
-        <v>3094</v>
+        <v>3261</v>
       </c>
       <c r="J829" s="4" t="s">
-        <v>3258</v>
+        <v>3261</v>
       </c>
       <c r="K829" s="4"/>
-      <c r="L829" s="4" t="s">
-        <v>3262</v>
-      </c>
-      <c r="M829" s="4" t="s">
-        <v>2089</v>
-      </c>
-      <c r="N829" s="4">
-        <v>13</v>
-      </c>
+      <c r="L829" s="4"/>
+      <c r="M829" s="4"/>
+      <c r="N829" s="4"/>
       <c r="O829" s="4" t="s">
-        <v>3263</v>
+        <v>3266</v>
       </c>
       <c r="P829" s="5"/>
       <c r="Q829" s="4" t="s">
-        <v>3264</v>
+        <v>3267</v>
       </c>
       <c r="R829" s="4" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="S829" s="4">
-        <v>2007564.26</v>
+        <v>65750.37</v>
       </c>
       <c r="T829" s="4">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U829" s="4" t="s">
-        <v>3265</v>
+        <v>3268</v>
       </c>
       <c r="V829" s="4" t="s">
         <v>217</v>
       </c>
       <c r="W829" s="4">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="X829" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y829" s="4"/>
       <c r="Z829" s="4" t="s">
-        <v>3266</v>
-      </c>
-      <c r="AA829" s="4"/>
+        <v>3269</v>
+      </c>
+      <c r="AA829" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB829" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="830" spans="1:28">
@@ -74201,13 +74135,13 @@
         <v>33</v>
       </c>
       <c r="C830" s="4">
-        <v>169514729</v>
+        <v>168326338</v>
       </c>
       <c r="D830" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E830" s="4">
-        <v>8086715</v>
+        <v>6596018</v>
       </c>
       <c r="F830" s="4" t="s">
         <v>140</v>
@@ -74219,48 +74153,58 @@
         <v>3094</v>
       </c>
       <c r="I830" s="4" t="s">
-        <v>3094</v>
+        <v>3261</v>
       </c>
       <c r="J830" s="4" t="s">
-        <v>1165</v>
+        <v>3261</v>
       </c>
       <c r="K830" s="4"/>
-      <c r="L830" s="4"/>
-      <c r="M830" s="4"/>
-      <c r="N830" s="4"/>
+      <c r="L830" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="M830" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N830" s="4">
+        <v>1</v>
+      </c>
       <c r="O830" s="4" t="s">
-        <v>3267</v>
+        <v>3270</v>
       </c>
       <c r="P830" s="5"/>
       <c r="Q830" s="4" t="s">
-        <v>3268</v>
+        <v>3271</v>
       </c>
       <c r="R830" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="S830" s="4">
-        <v>187735.5</v>
+        <v>199464933.62</v>
       </c>
       <c r="T830" s="4">
-        <v>1</v>
-      </c>
-      <c r="U830" s="4"/>
-      <c r="V830" s="4"/>
+        <v>116</v>
+      </c>
+      <c r="U830" s="4" t="s">
+        <v>3272</v>
+      </c>
+      <c r="V830" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="W830" s="4">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="X830" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y830" s="4"/>
       <c r="Z830" s="4" t="s">
-        <v>3269</v>
+        <v>3273</v>
       </c>
       <c r="AA830" s="4" t="s">
-        <v>79</v>
+        <v>445</v>
       </c>
       <c r="AB830" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="831" spans="1:28">
@@ -74268,16 +74212,16 @@
         <v>1000</v>
       </c>
       <c r="B831" s="4" t="s">
-        <v>590</v>
+        <v>33</v>
       </c>
       <c r="C831" s="4">
-        <v>170411056</v>
+        <v>167328500</v>
       </c>
       <c r="D831" s="4" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E831" s="4">
-        <v>7762399</v>
+        <v>5607367</v>
       </c>
       <c r="F831" s="4" t="s">
         <v>140</v>
@@ -74292,48 +74236,50 @@
         <v>3094</v>
       </c>
       <c r="J831" s="4" t="s">
-        <v>992</v>
+        <v>3274</v>
       </c>
       <c r="K831" s="4"/>
       <c r="L831" s="4" t="s">
-        <v>320</v>
+        <v>53</v>
       </c>
       <c r="M831" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="N831" s="4">
-        <v>56</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N831" s="4"/>
       <c r="O831" s="4" t="s">
-        <v>3270</v>
+        <v>3275</v>
       </c>
       <c r="P831" s="5"/>
       <c r="Q831" s="4" t="s">
-        <v>3271</v>
+        <v>3276</v>
       </c>
       <c r="R831" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S831" s="4">
-        <v>0</v>
+        <v>4181984.72</v>
       </c>
       <c r="T831" s="4">
-        <v>0</v>
-      </c>
-      <c r="U831" s="4"/>
-      <c r="V831" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="U831" s="4" t="s">
+        <v>3277</v>
+      </c>
+      <c r="V831" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="W831" s="4">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="X831" s="4" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="Y831" s="4"/>
       <c r="Z831" s="4" t="s">
-        <v>3272</v>
+        <v>324</v>
       </c>
       <c r="AA831" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="AB831" s="4" t="s">
         <v>61</v>
@@ -74347,13 +74293,13 @@
         <v>33</v>
       </c>
       <c r="C832" s="4">
-        <v>170314612</v>
+        <v>170426392</v>
       </c>
       <c r="D832" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E832" s="4">
-        <v>5609410</v>
+        <v>8336955</v>
       </c>
       <c r="F832" s="4" t="s">
         <v>140</v>
@@ -74368,48 +74314,48 @@
         <v>3094</v>
       </c>
       <c r="J832" s="4" t="s">
-        <v>992</v>
+        <v>3278</v>
       </c>
       <c r="K832" s="4"/>
       <c r="L832" s="4" t="s">
-        <v>3273</v>
+        <v>82</v>
       </c>
       <c r="M832" s="4" t="s">
-        <v>573</v>
+        <v>53</v>
       </c>
       <c r="N832" s="4">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="O832" s="4" t="s">
-        <v>3274</v>
+        <v>3279</v>
       </c>
       <c r="P832" s="5"/>
       <c r="Q832" s="4" t="s">
-        <v>3275</v>
+        <v>3280</v>
       </c>
       <c r="R832" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S832" s="4">
-        <v>93755.75</v>
+        <v>222025.44</v>
       </c>
       <c r="T832" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U832" s="4"/>
       <c r="V832" s="4"/>
       <c r="W832" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X832" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y832" s="4"/>
       <c r="Z832" s="4" t="s">
-        <v>3276</v>
+        <v>3281</v>
       </c>
       <c r="AA832" s="4" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="AB832" s="4" t="s">
         <v>61</v>
@@ -74423,13 +74369,13 @@
         <v>33</v>
       </c>
       <c r="C833" s="4">
-        <v>168721422</v>
+        <v>169476942</v>
       </c>
       <c r="D833" s="4" t="s">
-        <v>50</v>
+        <v>417</v>
       </c>
       <c r="E833" s="4">
-        <v>7519730</v>
+        <v>8398608</v>
       </c>
       <c r="F833" s="4" t="s">
         <v>140</v>
@@ -74441,24 +74387,24 @@
         <v>3094</v>
       </c>
       <c r="I833" s="4" t="s">
-        <v>3277</v>
+        <v>3094</v>
       </c>
       <c r="J833" s="4" t="s">
-        <v>3277</v>
+        <v>3282</v>
       </c>
       <c r="K833" s="4"/>
       <c r="L833" s="4"/>
       <c r="M833" s="4"/>
       <c r="N833" s="4"/>
       <c r="O833" s="4" t="s">
-        <v>3278</v>
+        <v>3283</v>
       </c>
       <c r="P833" s="5"/>
       <c r="Q833" s="4" t="s">
-        <v>3279</v>
+        <v>3284</v>
       </c>
       <c r="R833" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S833" s="4">
         <v>0</v>
@@ -74466,25 +74412,21 @@
       <c r="T833" s="4">
         <v>0</v>
       </c>
-      <c r="U833" s="4" t="s">
-        <v>3280</v>
-      </c>
-      <c r="V833" s="4" t="s">
-        <v>173</v>
-      </c>
+      <c r="U833" s="4"/>
+      <c r="V833" s="4"/>
       <c r="W833" s="4">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="X833" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y833" s="4"/>
       <c r="Z833" s="4" t="s">
-        <v>3281</v>
+        <v>3285</v>
       </c>
       <c r="AA833" s="4"/>
       <c r="AB833" s="4" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
     </row>
     <row r="834" spans="1:28">
@@ -74495,13 +74437,13 @@
         <v>33</v>
       </c>
       <c r="C834" s="4">
-        <v>170058508</v>
+        <v>169530986</v>
       </c>
       <c r="D834" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E834" s="4">
-        <v>7338893</v>
+        <v>5611094</v>
       </c>
       <c r="F834" s="4" t="s">
         <v>140</v>
@@ -74513,52 +74455,54 @@
         <v>3094</v>
       </c>
       <c r="I834" s="4" t="s">
-        <v>3277</v>
+        <v>3094</v>
       </c>
       <c r="J834" s="4" t="s">
-        <v>3277</v>
+        <v>3282</v>
       </c>
       <c r="K834" s="4"/>
-      <c r="L834" s="4"/>
-      <c r="M834" s="4"/>
+      <c r="L834" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M834" s="4" t="s">
+        <v>116</v>
+      </c>
       <c r="N834" s="4"/>
       <c r="O834" s="4" t="s">
-        <v>3282</v>
+        <v>3286</v>
       </c>
       <c r="P834" s="5"/>
       <c r="Q834" s="4" t="s">
-        <v>3283</v>
+        <v>3287</v>
       </c>
       <c r="R834" s="4" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="S834" s="4">
-        <v>65750.37</v>
+        <v>68767.63</v>
       </c>
       <c r="T834" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U834" s="4" t="s">
-        <v>3284</v>
+        <v>3288</v>
       </c>
       <c r="V834" s="4" t="s">
-        <v>217</v>
+        <v>45</v>
       </c>
       <c r="W834" s="4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="X834" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y834" s="4"/>
       <c r="Z834" s="4" t="s">
-        <v>3285</v>
-      </c>
-      <c r="AA834" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>3289</v>
+      </c>
+      <c r="AA834" s="4"/>
       <c r="AB834" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="835" spans="1:28">
@@ -74569,13 +74513,13 @@
         <v>33</v>
       </c>
       <c r="C835" s="4">
-        <v>168326338</v>
+        <v>170167418</v>
       </c>
       <c r="D835" s="4" t="s">
-        <v>34</v>
+        <v>1072</v>
       </c>
       <c r="E835" s="4">
-        <v>6596018</v>
+        <v>5605922</v>
       </c>
       <c r="F835" s="4" t="s">
         <v>140</v>
@@ -74587,58 +74531,54 @@
         <v>3094</v>
       </c>
       <c r="I835" s="4" t="s">
-        <v>3277</v>
+        <v>3094</v>
       </c>
       <c r="J835" s="4" t="s">
-        <v>3277</v>
+        <v>3282</v>
       </c>
       <c r="K835" s="4"/>
       <c r="L835" s="4" t="s">
-        <v>665</v>
+        <v>157</v>
       </c>
       <c r="M835" s="4" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="N835" s="4">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="O835" s="4" t="s">
-        <v>3286</v>
+        <v>3290</v>
       </c>
       <c r="P835" s="5"/>
       <c r="Q835" s="4" t="s">
-        <v>3287</v>
+        <v>3291</v>
       </c>
       <c r="R835" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="S835" s="4">
-        <v>199464933.62</v>
+        <v>0</v>
       </c>
       <c r="T835" s="4">
-        <v>116</v>
-      </c>
-      <c r="U835" s="4" t="s">
-        <v>3288</v>
-      </c>
-      <c r="V835" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U835" s="4"/>
+      <c r="V835" s="4"/>
       <c r="W835" s="4">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="X835" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y835" s="4"/>
       <c r="Z835" s="4" t="s">
-        <v>3289</v>
+        <v>3292</v>
       </c>
       <c r="AA835" s="4" t="s">
-        <v>445</v>
+        <v>60</v>
       </c>
       <c r="AB835" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="836" spans="1:28">
@@ -74649,13 +74589,13 @@
         <v>33</v>
       </c>
       <c r="C836" s="4">
-        <v>167328500</v>
+        <v>168713864</v>
       </c>
       <c r="D836" s="4" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="E836" s="4">
-        <v>5607367</v>
+        <v>7270609</v>
       </c>
       <c r="F836" s="4" t="s">
         <v>140</v>
@@ -74670,53 +74610,53 @@
         <v>3094</v>
       </c>
       <c r="J836" s="4" t="s">
-        <v>3290</v>
+        <v>3293</v>
       </c>
       <c r="K836" s="4"/>
       <c r="L836" s="4" t="s">
-        <v>53</v>
+        <v>3216</v>
       </c>
       <c r="M836" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="N836" s="4"/>
+        <v>710</v>
+      </c>
+      <c r="N836" s="4">
+        <v>16</v>
+      </c>
       <c r="O836" s="4" t="s">
-        <v>3291</v>
+        <v>3294</v>
       </c>
       <c r="P836" s="5"/>
       <c r="Q836" s="4" t="s">
-        <v>3292</v>
+        <v>3295</v>
       </c>
       <c r="R836" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S836" s="4">
-        <v>4181984.72</v>
+        <v>123782.36</v>
       </c>
       <c r="T836" s="4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="U836" s="4" t="s">
-        <v>3293</v>
+        <v>3296</v>
       </c>
       <c r="V836" s="4" t="s">
-        <v>153</v>
+        <v>3297</v>
       </c>
       <c r="W836" s="4">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="X836" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y836" s="4"/>
       <c r="Z836" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="AA836" s="4" t="s">
-        <v>60</v>
-      </c>
+        <v>3298</v>
+      </c>
+      <c r="AA836" s="4"/>
       <c r="AB836" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="837" spans="1:28">
@@ -74727,13 +74667,13 @@
         <v>33</v>
       </c>
       <c r="C837" s="4">
-        <v>170426392</v>
+        <v>168714166</v>
       </c>
       <c r="D837" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E837" s="4">
-        <v>8336955</v>
+        <v>7270892</v>
       </c>
       <c r="F837" s="4" t="s">
         <v>140</v>
@@ -74748,51 +74688,53 @@
         <v>3094</v>
       </c>
       <c r="J837" s="4" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="K837" s="4"/>
       <c r="L837" s="4" t="s">
-        <v>82</v>
+        <v>3216</v>
       </c>
       <c r="M837" s="4" t="s">
-        <v>53</v>
+        <v>710</v>
       </c>
       <c r="N837" s="4">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="O837" s="4" t="s">
-        <v>3295</v>
+        <v>3299</v>
       </c>
       <c r="P837" s="5"/>
       <c r="Q837" s="4" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="R837" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S837" s="4">
-        <v>222025.44</v>
+        <v>9647336.49</v>
       </c>
       <c r="T837" s="4">
-        <v>3</v>
-      </c>
-      <c r="U837" s="4"/>
-      <c r="V837" s="4"/>
+        <v>74</v>
+      </c>
+      <c r="U837" s="4" t="s">
+        <v>3300</v>
+      </c>
+      <c r="V837" s="4" t="s">
+        <v>3297</v>
+      </c>
       <c r="W837" s="4">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="X837" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y837" s="4"/>
       <c r="Z837" s="4" t="s">
-        <v>3297</v>
-      </c>
-      <c r="AA837" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>3301</v>
+      </c>
+      <c r="AA837" s="4"/>
       <c r="AB837" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="838" spans="1:28">
@@ -74803,13 +74745,13 @@
         <v>33</v>
       </c>
       <c r="C838" s="4">
-        <v>169476942</v>
+        <v>168714537</v>
       </c>
       <c r="D838" s="4" t="s">
-        <v>417</v>
+        <v>50</v>
       </c>
       <c r="E838" s="4">
-        <v>8398608</v>
+        <v>7270608</v>
       </c>
       <c r="F838" s="4" t="s">
         <v>140</v>
@@ -74824,43 +74766,53 @@
         <v>3094</v>
       </c>
       <c r="J838" s="4" t="s">
-        <v>3298</v>
+        <v>3293</v>
       </c>
       <c r="K838" s="4"/>
-      <c r="L838" s="4"/>
-      <c r="M838" s="4"/>
-      <c r="N838" s="4"/>
+      <c r="L838" s="4" t="s">
+        <v>3216</v>
+      </c>
+      <c r="M838" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="N838" s="4">
+        <v>16</v>
+      </c>
       <c r="O838" s="4" t="s">
-        <v>3299</v>
+        <v>3302</v>
       </c>
       <c r="P838" s="5"/>
       <c r="Q838" s="4" t="s">
-        <v>3300</v>
+        <v>3295</v>
       </c>
       <c r="R838" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S838" s="4">
-        <v>0</v>
+        <v>9580947.66</v>
       </c>
       <c r="T838" s="4">
-        <v>0</v>
-      </c>
-      <c r="U838" s="4"/>
-      <c r="V838" s="4"/>
+        <v>74</v>
+      </c>
+      <c r="U838" s="4" t="s">
+        <v>3303</v>
+      </c>
+      <c r="V838" s="4" t="s">
+        <v>3297</v>
+      </c>
       <c r="W838" s="4">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="X838" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y838" s="4"/>
       <c r="Z838" s="4" t="s">
-        <v>3301</v>
+        <v>3304</v>
       </c>
       <c r="AA838" s="4"/>
       <c r="AB838" s="4" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
     </row>
     <row r="839" spans="1:28">
@@ -74871,13 +74823,13 @@
         <v>33</v>
       </c>
       <c r="C839" s="4">
-        <v>169530986</v>
+        <v>167629550</v>
       </c>
       <c r="D839" s="4" t="s">
-        <v>50</v>
+        <v>286</v>
       </c>
       <c r="E839" s="4">
-        <v>5611094</v>
+        <v>8236065</v>
       </c>
       <c r="F839" s="4" t="s">
         <v>140</v>
@@ -74892,51 +74844,51 @@
         <v>3094</v>
       </c>
       <c r="J839" s="4" t="s">
-        <v>3298</v>
+        <v>3293</v>
       </c>
       <c r="K839" s="4"/>
       <c r="L839" s="4" t="s">
-        <v>68</v>
+        <v>177</v>
       </c>
       <c r="M839" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="N839" s="4"/>
+        <v>3305</v>
+      </c>
+      <c r="N839" s="4">
+        <v>5</v>
+      </c>
       <c r="O839" s="4" t="s">
-        <v>3302</v>
+        <v>3306</v>
       </c>
       <c r="P839" s="5"/>
       <c r="Q839" s="4" t="s">
-        <v>3303</v>
+        <v>3307</v>
       </c>
       <c r="R839" s="4" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="S839" s="4">
-        <v>68767.63</v>
+        <v>0</v>
       </c>
       <c r="T839" s="4">
-        <v>1</v>
-      </c>
-      <c r="U839" s="4" t="s">
-        <v>3304</v>
-      </c>
-      <c r="V839" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U839" s="4"/>
+      <c r="V839" s="4"/>
       <c r="W839" s="4">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="X839" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y839" s="4"/>
       <c r="Z839" s="4" t="s">
-        <v>3305</v>
-      </c>
-      <c r="AA839" s="4"/>
+        <v>3308</v>
+      </c>
+      <c r="AA839" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB839" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="840" spans="1:28">
@@ -74947,13 +74899,13 @@
         <v>33</v>
       </c>
       <c r="C840" s="4">
-        <v>170167418</v>
+        <v>167632954</v>
       </c>
       <c r="D840" s="4" t="s">
-        <v>1072</v>
+        <v>364</v>
       </c>
       <c r="E840" s="4">
-        <v>5605922</v>
+        <v>1102693</v>
       </c>
       <c r="F840" s="4" t="s">
         <v>140</v>
@@ -74968,48 +74920,48 @@
         <v>3094</v>
       </c>
       <c r="J840" s="4" t="s">
-        <v>3298</v>
+        <v>3309</v>
       </c>
       <c r="K840" s="4"/>
       <c r="L840" s="4" t="s">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="M840" s="4" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="N840" s="4">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="O840" s="4" t="s">
-        <v>3306</v>
+        <v>3310</v>
       </c>
       <c r="P840" s="5"/>
       <c r="Q840" s="4" t="s">
-        <v>3307</v>
+        <v>3311</v>
       </c>
       <c r="R840" s="4" t="s">
         <v>56</v>
       </c>
       <c r="S840" s="4">
-        <v>0</v>
+        <v>148356284.84</v>
       </c>
       <c r="T840" s="4">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="U840" s="4"/>
       <c r="V840" s="4"/>
       <c r="W840" s="4">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="X840" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y840" s="4"/>
       <c r="Z840" s="4" t="s">
-        <v>3308</v>
+        <v>3312</v>
       </c>
       <c r="AA840" s="4" t="s">
-        <v>60</v>
+        <v>3313</v>
       </c>
       <c r="AB840" s="4" t="s">
         <v>61</v>
@@ -75023,13 +74975,13 @@
         <v>33</v>
       </c>
       <c r="C841" s="4">
-        <v>168713864</v>
+        <v>168367155</v>
       </c>
       <c r="D841" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E841" s="4">
-        <v>7270609</v>
+        <v>5606412</v>
       </c>
       <c r="F841" s="4" t="s">
         <v>140</v>
@@ -75044,53 +74996,51 @@
         <v>3094</v>
       </c>
       <c r="J841" s="4" t="s">
-        <v>3309</v>
+        <v>3314</v>
       </c>
       <c r="K841" s="4"/>
       <c r="L841" s="4" t="s">
-        <v>3228</v>
+        <v>3142</v>
       </c>
       <c r="M841" s="4" t="s">
-        <v>710</v>
+        <v>199</v>
       </c>
       <c r="N841" s="4">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O841" s="4" t="s">
-        <v>3310</v>
+        <v>3315</v>
       </c>
       <c r="P841" s="5"/>
       <c r="Q841" s="4" t="s">
-        <v>3311</v>
+        <v>3316</v>
       </c>
       <c r="R841" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S841" s="4">
-        <v>123782.36</v>
+        <v>29542.54</v>
       </c>
       <c r="T841" s="4">
-        <v>3</v>
-      </c>
-      <c r="U841" s="4" t="s">
-        <v>3312</v>
-      </c>
-      <c r="V841" s="4" t="s">
-        <v>3313</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U841" s="4"/>
+      <c r="V841" s="4"/>
       <c r="W841" s="4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="X841" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y841" s="4"/>
       <c r="Z841" s="4" t="s">
-        <v>3314</v>
-      </c>
-      <c r="AA841" s="4"/>
+        <v>3317</v>
+      </c>
+      <c r="AA841" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="AB841" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="842" spans="1:28">
@@ -75101,13 +75051,13 @@
         <v>33</v>
       </c>
       <c r="C842" s="4">
-        <v>168714166</v>
+        <v>170207562</v>
       </c>
       <c r="D842" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E842" s="4">
-        <v>7270892</v>
+        <v>8383283</v>
       </c>
       <c r="F842" s="4" t="s">
         <v>140</v>
@@ -75122,53 +75072,49 @@
         <v>3094</v>
       </c>
       <c r="J842" s="4" t="s">
-        <v>3309</v>
+        <v>3318</v>
       </c>
       <c r="K842" s="4"/>
       <c r="L842" s="4" t="s">
-        <v>3228</v>
+        <v>3319</v>
       </c>
       <c r="M842" s="4" t="s">
-        <v>710</v>
+        <v>224</v>
       </c>
       <c r="N842" s="4">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="O842" s="4" t="s">
-        <v>3315</v>
+        <v>3320</v>
       </c>
       <c r="P842" s="5"/>
       <c r="Q842" s="4" t="s">
-        <v>3311</v>
+        <v>3321</v>
       </c>
       <c r="R842" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S842" s="4">
-        <v>9647336.49</v>
+        <v>26518.12</v>
       </c>
       <c r="T842" s="4">
-        <v>74</v>
-      </c>
-      <c r="U842" s="4" t="s">
-        <v>3316</v>
-      </c>
-      <c r="V842" s="4" t="s">
-        <v>3313</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U842" s="4"/>
+      <c r="V842" s="4"/>
       <c r="W842" s="4">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="X842" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y842" s="4"/>
       <c r="Z842" s="4" t="s">
-        <v>3317</v>
+        <v>3322</v>
       </c>
       <c r="AA842" s="4"/>
       <c r="AB842" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="843" spans="1:28">
@@ -75179,13 +75125,13 @@
         <v>33</v>
       </c>
       <c r="C843" s="4">
-        <v>168714537</v>
+        <v>168898285</v>
       </c>
       <c r="D843" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E843" s="4">
-        <v>7270608</v>
+        <v>7722000</v>
       </c>
       <c r="F843" s="4" t="s">
         <v>140</v>
@@ -75200,53 +75146,51 @@
         <v>3094</v>
       </c>
       <c r="J843" s="4" t="s">
-        <v>3309</v>
+        <v>3318</v>
       </c>
       <c r="K843" s="4"/>
       <c r="L843" s="4" t="s">
-        <v>3228</v>
+        <v>3323</v>
       </c>
       <c r="M843" s="4" t="s">
-        <v>710</v>
+        <v>224</v>
       </c>
       <c r="N843" s="4">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="O843" s="4" t="s">
-        <v>3318</v>
+        <v>3324</v>
       </c>
       <c r="P843" s="5"/>
       <c r="Q843" s="4" t="s">
-        <v>3311</v>
+        <v>3325</v>
       </c>
       <c r="R843" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S843" s="4">
-        <v>9580947.66</v>
+        <v>1429440.27</v>
       </c>
       <c r="T843" s="4">
-        <v>74</v>
-      </c>
-      <c r="U843" s="4" t="s">
-        <v>3319</v>
-      </c>
-      <c r="V843" s="4" t="s">
-        <v>3313</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U843" s="4"/>
+      <c r="V843" s="4"/>
       <c r="W843" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="X843" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y843" s="4"/>
       <c r="Z843" s="4" t="s">
-        <v>3320</v>
-      </c>
-      <c r="AA843" s="4"/>
+        <v>3326</v>
+      </c>
+      <c r="AA843" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB843" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="844" spans="1:28">
@@ -75257,13 +75201,13 @@
         <v>33</v>
       </c>
       <c r="C844" s="4">
-        <v>167629550</v>
+        <v>170522038</v>
       </c>
       <c r="D844" s="4" t="s">
-        <v>286</v>
+        <v>115</v>
       </c>
       <c r="E844" s="4">
-        <v>8236065</v>
+        <v>7720345</v>
       </c>
       <c r="F844" s="4" t="s">
         <v>140</v>
@@ -75278,24 +75222,24 @@
         <v>3094</v>
       </c>
       <c r="J844" s="4" t="s">
-        <v>3309</v>
+        <v>3318</v>
       </c>
       <c r="K844" s="4"/>
       <c r="L844" s="4" t="s">
-        <v>177</v>
+        <v>3327</v>
       </c>
       <c r="M844" s="4" t="s">
-        <v>3321</v>
+        <v>224</v>
       </c>
       <c r="N844" s="4">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="O844" s="4" t="s">
-        <v>3322</v>
+        <v>3328</v>
       </c>
       <c r="P844" s="5"/>
       <c r="Q844" s="4" t="s">
-        <v>3323</v>
+        <v>3329</v>
       </c>
       <c r="R844" s="4" t="s">
         <v>72</v>
@@ -75309,20 +75253,20 @@
       <c r="U844" s="4"/>
       <c r="V844" s="4"/>
       <c r="W844" s="4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X844" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y844" s="4"/>
       <c r="Z844" s="4" t="s">
-        <v>3324</v>
+        <v>3330</v>
       </c>
       <c r="AA844" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="AB844" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="845" spans="1:28">
@@ -75333,13 +75277,13 @@
         <v>33</v>
       </c>
       <c r="C845" s="4">
-        <v>167632954</v>
+        <v>169842061</v>
       </c>
       <c r="D845" s="4" t="s">
-        <v>364</v>
+        <v>50</v>
       </c>
       <c r="E845" s="4">
-        <v>1102693</v>
+        <v>7722234</v>
       </c>
       <c r="F845" s="4" t="s">
         <v>140</v>
@@ -75354,48 +75298,52 @@
         <v>3094</v>
       </c>
       <c r="J845" s="4" t="s">
-        <v>3325</v>
+        <v>3318</v>
       </c>
       <c r="K845" s="4"/>
       <c r="L845" s="4" t="s">
-        <v>256</v>
+        <v>3331</v>
       </c>
       <c r="M845" s="4" t="s">
-        <v>40</v>
+        <v>224</v>
       </c>
       <c r="N845" s="4">
-        <v>600</v>
+        <v>45</v>
       </c>
       <c r="O845" s="4" t="s">
-        <v>3326</v>
+        <v>3332</v>
       </c>
       <c r="P845" s="5"/>
       <c r="Q845" s="4" t="s">
-        <v>3327</v>
+        <v>3325</v>
       </c>
       <c r="R845" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S845" s="4">
-        <v>148356284.84</v>
+        <v>399902.99</v>
       </c>
       <c r="T845" s="4">
-        <v>43</v>
-      </c>
-      <c r="U845" s="4"/>
-      <c r="V845" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U845" s="4" t="s">
+        <v>3333</v>
+      </c>
+      <c r="V845" s="4" t="s">
+        <v>243</v>
+      </c>
       <c r="W845" s="4">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="X845" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y845" s="4"/>
       <c r="Z845" s="4" t="s">
-        <v>3328</v>
+        <v>3334</v>
       </c>
       <c r="AA845" s="4" t="s">
-        <v>3329</v>
+        <v>79</v>
       </c>
       <c r="AB845" s="4" t="s">
         <v>61</v>
@@ -75409,13 +75357,13 @@
         <v>33</v>
       </c>
       <c r="C846" s="4">
-        <v>168367155</v>
+        <v>168725695</v>
       </c>
       <c r="D846" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E846" s="4">
-        <v>5606412</v>
+        <v>7798971</v>
       </c>
       <c r="F846" s="4" t="s">
         <v>140</v>
@@ -75430,45 +75378,49 @@
         <v>3094</v>
       </c>
       <c r="J846" s="4" t="s">
-        <v>3330</v>
+        <v>3318</v>
       </c>
       <c r="K846" s="4"/>
       <c r="L846" s="4" t="s">
-        <v>3145</v>
+        <v>3335</v>
       </c>
       <c r="M846" s="4" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="N846" s="4">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="O846" s="4" t="s">
-        <v>3331</v>
+        <v>3336</v>
       </c>
       <c r="P846" s="5"/>
       <c r="Q846" s="4" t="s">
-        <v>3332</v>
+        <v>3337</v>
       </c>
       <c r="R846" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S846" s="4">
-        <v>29542.54</v>
+        <v>307743.64</v>
       </c>
       <c r="T846" s="4">
-        <v>1</v>
-      </c>
-      <c r="U846" s="4"/>
-      <c r="V846" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="U846" s="4" t="s">
+        <v>3338</v>
+      </c>
+      <c r="V846" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="W846" s="4">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="X846" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y846" s="4"/>
       <c r="Z846" s="4" t="s">
-        <v>3333</v>
+        <v>3339</v>
       </c>
       <c r="AA846" s="4" t="s">
         <v>60</v>
@@ -75485,13 +75437,13 @@
         <v>33</v>
       </c>
       <c r="C847" s="4">
-        <v>170207562</v>
+        <v>169988404</v>
       </c>
       <c r="D847" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E847" s="4">
-        <v>8383283</v>
+        <v>7635384</v>
       </c>
       <c r="F847" s="4" t="s">
         <v>140</v>
@@ -75506,30 +75458,30 @@
         <v>3094</v>
       </c>
       <c r="J847" s="4" t="s">
-        <v>3334</v>
+        <v>1194</v>
       </c>
       <c r="K847" s="4"/>
       <c r="L847" s="4" t="s">
-        <v>3335</v>
+        <v>855</v>
       </c>
       <c r="M847" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="N847" s="4">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="O847" s="4" t="s">
-        <v>3336</v>
+        <v>3340</v>
       </c>
       <c r="P847" s="5"/>
       <c r="Q847" s="4" t="s">
-        <v>3337</v>
+        <v>3341</v>
       </c>
       <c r="R847" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S847" s="4">
-        <v>26518.12</v>
+        <v>47039.24</v>
       </c>
       <c r="T847" s="4">
         <v>1</v>
@@ -75537,16 +75489,18 @@
       <c r="U847" s="4"/>
       <c r="V847" s="4"/>
       <c r="W847" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X847" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y847" s="4"/>
       <c r="Z847" s="4" t="s">
-        <v>3338</v>
-      </c>
-      <c r="AA847" s="4"/>
+        <v>3342</v>
+      </c>
+      <c r="AA847" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB847" s="4" t="s">
         <v>61</v>
       </c>
@@ -75559,13 +75513,13 @@
         <v>33</v>
       </c>
       <c r="C848" s="4">
-        <v>168898285</v>
+        <v>169829909</v>
       </c>
       <c r="D848" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E848" s="4">
-        <v>7722000</v>
+        <v>6849464</v>
       </c>
       <c r="F848" s="4" t="s">
         <v>140</v>
@@ -75580,45 +75534,45 @@
         <v>3094</v>
       </c>
       <c r="J848" s="4" t="s">
-        <v>3334</v>
+        <v>1194</v>
       </c>
       <c r="K848" s="4"/>
       <c r="L848" s="4" t="s">
-        <v>3339</v>
+        <v>335</v>
       </c>
       <c r="M848" s="4" t="s">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="N848" s="4">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="O848" s="4" t="s">
-        <v>3340</v>
+        <v>3343</v>
       </c>
       <c r="P848" s="5"/>
       <c r="Q848" s="4" t="s">
-        <v>3341</v>
+        <v>3344</v>
       </c>
       <c r="R848" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S848" s="4">
-        <v>1429440.27</v>
+        <v>374101.81</v>
       </c>
       <c r="T848" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U848" s="4"/>
       <c r="V848" s="4"/>
       <c r="W848" s="4">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="X848" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y848" s="4"/>
       <c r="Z848" s="4" t="s">
-        <v>3342</v>
+        <v>3345</v>
       </c>
       <c r="AA848" s="4" t="s">
         <v>79</v>
@@ -75635,13 +75589,13 @@
         <v>33</v>
       </c>
       <c r="C849" s="4">
-        <v>170522038</v>
+        <v>169487687</v>
       </c>
       <c r="D849" s="4" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="E849" s="4">
-        <v>7720345</v>
+        <v>7293133</v>
       </c>
       <c r="F849" s="4" t="s">
         <v>140</v>
@@ -75656,24 +75610,22 @@
         <v>3094</v>
       </c>
       <c r="J849" s="4" t="s">
-        <v>3334</v>
+        <v>1194</v>
       </c>
       <c r="K849" s="4"/>
       <c r="L849" s="4" t="s">
-        <v>3343</v>
+        <v>705</v>
       </c>
       <c r="M849" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="N849" s="4">
-        <v>60</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N849" s="4"/>
       <c r="O849" s="4" t="s">
-        <v>3344</v>
+        <v>3346</v>
       </c>
       <c r="P849" s="5"/>
       <c r="Q849" s="4" t="s">
-        <v>3345</v>
+        <v>3347</v>
       </c>
       <c r="R849" s="4" t="s">
         <v>72</v>
@@ -75687,18 +75639,16 @@
       <c r="U849" s="4"/>
       <c r="V849" s="4"/>
       <c r="W849" s="4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="X849" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y849" s="4"/>
       <c r="Z849" s="4" t="s">
-        <v>3346</v>
-      </c>
-      <c r="AA849" s="4" t="s">
-        <v>60</v>
-      </c>
+        <v>3348</v>
+      </c>
+      <c r="AA849" s="4"/>
       <c r="AB849" s="4" t="s">
         <v>61</v>
       </c>
@@ -75711,13 +75661,13 @@
         <v>33</v>
       </c>
       <c r="C850" s="4">
-        <v>169842061</v>
+        <v>167347239</v>
       </c>
       <c r="D850" s="4" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="E850" s="4">
-        <v>7722234</v>
+        <v>7409197</v>
       </c>
       <c r="F850" s="4" t="s">
         <v>140</v>
@@ -75729,58 +75679,54 @@
         <v>3094</v>
       </c>
       <c r="I850" s="4" t="s">
-        <v>3094</v>
+        <v>3349</v>
       </c>
       <c r="J850" s="4" t="s">
-        <v>3334</v>
+        <v>3349</v>
       </c>
       <c r="K850" s="4"/>
       <c r="L850" s="4" t="s">
-        <v>3347</v>
-      </c>
-      <c r="M850" s="4" t="s">
-        <v>224</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="M850" s="4"/>
       <c r="N850" s="4">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="O850" s="4" t="s">
-        <v>3348</v>
+        <v>3350</v>
       </c>
       <c r="P850" s="5"/>
       <c r="Q850" s="4" t="s">
-        <v>3341</v>
+        <v>3351</v>
       </c>
       <c r="R850" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S850" s="4">
-        <v>399902.99</v>
+        <v>4869737.28</v>
       </c>
       <c r="T850" s="4">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="U850" s="4" t="s">
-        <v>3349</v>
+        <v>3352</v>
       </c>
       <c r="V850" s="4" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="W850" s="4">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="X850" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y850" s="4"/>
       <c r="Z850" s="4" t="s">
-        <v>3350</v>
-      </c>
-      <c r="AA850" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="AA850" s="4"/>
       <c r="AB850" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="851" spans="1:28">
@@ -75791,13 +75737,13 @@
         <v>33</v>
       </c>
       <c r="C851" s="4">
-        <v>168725695</v>
+        <v>167709123</v>
       </c>
       <c r="D851" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E851" s="4">
-        <v>7798971</v>
+        <v>5607771</v>
       </c>
       <c r="F851" s="4" t="s">
         <v>140</v>
@@ -75809,55 +75755,49 @@
         <v>3094</v>
       </c>
       <c r="I851" s="4" t="s">
-        <v>3094</v>
+        <v>3353</v>
       </c>
       <c r="J851" s="4" t="s">
-        <v>3334</v>
+        <v>3353</v>
       </c>
       <c r="K851" s="4"/>
-      <c r="L851" s="4" t="s">
-        <v>3351</v>
-      </c>
-      <c r="M851" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="N851" s="4">
-        <v>98</v>
-      </c>
+      <c r="L851" s="4"/>
+      <c r="M851" s="4"/>
+      <c r="N851" s="4"/>
       <c r="O851" s="4" t="s">
-        <v>3352</v>
+        <v>3354</v>
       </c>
       <c r="P851" s="5"/>
       <c r="Q851" s="4" t="s">
-        <v>3353</v>
+        <v>3355</v>
       </c>
       <c r="R851" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S851" s="4">
-        <v>307743.64</v>
+        <v>4274093.02</v>
       </c>
       <c r="T851" s="4">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="U851" s="4" t="s">
-        <v>3354</v>
+        <v>3356</v>
       </c>
       <c r="V851" s="4" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="W851" s="4">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="X851" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y851" s="4"/>
       <c r="Z851" s="4" t="s">
-        <v>3355</v>
+        <v>3357</v>
       </c>
       <c r="AA851" s="4" t="s">
-        <v>60</v>
+        <v>445</v>
       </c>
       <c r="AB851" s="4" t="s">
         <v>61</v>
@@ -75871,70 +75811,68 @@
         <v>33</v>
       </c>
       <c r="C852" s="4">
-        <v>169988404</v>
+        <v>166985500</v>
       </c>
       <c r="D852" s="4" t="s">
-        <v>50</v>
+        <v>364</v>
       </c>
       <c r="E852" s="4">
-        <v>7635384</v>
+        <v>8370701</v>
       </c>
       <c r="F852" s="4" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="G852" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H852" s="4" t="s">
-        <v>3094</v>
+        <v>3358</v>
       </c>
       <c r="I852" s="4" t="s">
-        <v>3094</v>
+        <v>3358</v>
       </c>
       <c r="J852" s="4" t="s">
-        <v>1194</v>
+        <v>3359</v>
       </c>
       <c r="K852" s="4"/>
       <c r="L852" s="4" t="s">
-        <v>855</v>
+        <v>224</v>
       </c>
       <c r="M852" s="4" t="s">
-        <v>219</v>
+        <v>3360</v>
       </c>
       <c r="N852" s="4">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="O852" s="4" t="s">
-        <v>3356</v>
+        <v>3361</v>
       </c>
       <c r="P852" s="5"/>
       <c r="Q852" s="4" t="s">
-        <v>3357</v>
+        <v>3362</v>
       </c>
       <c r="R852" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S852" s="4">
-        <v>47039.24</v>
+        <v>0</v>
       </c>
       <c r="T852" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U852" s="4"/>
       <c r="V852" s="4"/>
       <c r="W852" s="4">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="X852" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y852" s="4"/>
       <c r="Z852" s="4" t="s">
-        <v>3358</v>
-      </c>
-      <c r="AA852" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>3363</v>
+      </c>
+      <c r="AA852" s="4"/>
       <c r="AB852" s="4" t="s">
         <v>61</v>
       </c>
@@ -75947,51 +75885,51 @@
         <v>33</v>
       </c>
       <c r="C853" s="4">
-        <v>169829909</v>
+        <v>166986360</v>
       </c>
       <c r="D853" s="4" t="s">
-        <v>50</v>
+        <v>364</v>
       </c>
       <c r="E853" s="4">
-        <v>6849464</v>
+        <v>8370708</v>
       </c>
       <c r="F853" s="4" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="G853" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H853" s="4" t="s">
-        <v>3094</v>
+        <v>3358</v>
       </c>
       <c r="I853" s="4" t="s">
-        <v>3094</v>
+        <v>3358</v>
       </c>
       <c r="J853" s="4" t="s">
-        <v>1194</v>
+        <v>3359</v>
       </c>
       <c r="K853" s="4"/>
       <c r="L853" s="4" t="s">
-        <v>335</v>
+        <v>224</v>
       </c>
       <c r="M853" s="4" t="s">
-        <v>116</v>
+        <v>3360</v>
       </c>
       <c r="N853" s="4">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="O853" s="4" t="s">
-        <v>3359</v>
+        <v>3364</v>
       </c>
       <c r="P853" s="5"/>
       <c r="Q853" s="4" t="s">
-        <v>3360</v>
+        <v>3362</v>
       </c>
       <c r="R853" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="S853" s="4">
-        <v>374101.81</v>
+        <v>2277764.52</v>
       </c>
       <c r="T853" s="4">
         <v>3</v>
@@ -75999,18 +75937,16 @@
       <c r="U853" s="4"/>
       <c r="V853" s="4"/>
       <c r="W853" s="4">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="X853" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y853" s="4"/>
       <c r="Z853" s="4" t="s">
-        <v>3361</v>
-      </c>
-      <c r="AA853" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>3365</v>
+      </c>
+      <c r="AA853" s="4"/>
       <c r="AB853" s="4" t="s">
         <v>61</v>
       </c>
@@ -76023,64 +75959,66 @@
         <v>33</v>
       </c>
       <c r="C854" s="4">
-        <v>169487687</v>
+        <v>170400653</v>
       </c>
       <c r="D854" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E854" s="4">
-        <v>7293133</v>
+        <v>8370701</v>
       </c>
       <c r="F854" s="4" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="G854" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H854" s="4" t="s">
-        <v>3094</v>
+        <v>3358</v>
       </c>
       <c r="I854" s="4" t="s">
-        <v>3094</v>
+        <v>3358</v>
       </c>
       <c r="J854" s="4" t="s">
-        <v>1194</v>
+        <v>3359</v>
       </c>
       <c r="K854" s="4"/>
       <c r="L854" s="4" t="s">
-        <v>705</v>
+        <v>224</v>
       </c>
       <c r="M854" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="N854" s="4"/>
+        <v>3360</v>
+      </c>
+      <c r="N854" s="4">
+        <v>7</v>
+      </c>
       <c r="O854" s="4" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="P854" s="5"/>
       <c r="Q854" s="4" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="R854" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S854" s="4">
-        <v>0</v>
+        <v>241005</v>
       </c>
       <c r="T854" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U854" s="4"/>
       <c r="V854" s="4"/>
       <c r="W854" s="4">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="X854" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y854" s="4"/>
       <c r="Z854" s="4" t="s">
-        <v>3364</v>
+        <v>3366</v>
       </c>
       <c r="AA854" s="4"/>
       <c r="AB854" s="4" t="s">
@@ -76095,72 +76033,72 @@
         <v>33</v>
       </c>
       <c r="C855" s="4">
-        <v>167347239</v>
+        <v>165796789</v>
       </c>
       <c r="D855" s="4" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="E855" s="4">
-        <v>7409197</v>
+        <v>6265969</v>
       </c>
       <c r="F855" s="4" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="G855" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H855" s="4" t="s">
-        <v>3094</v>
+        <v>3358</v>
       </c>
       <c r="I855" s="4" t="s">
-        <v>3365</v>
+        <v>3358</v>
       </c>
       <c r="J855" s="4" t="s">
-        <v>3365</v>
+        <v>3359</v>
       </c>
       <c r="K855" s="4"/>
       <c r="L855" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="M855" s="4"/>
-      <c r="N855" s="4">
-        <v>42</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="M855" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="N855" s="4"/>
       <c r="O855" s="4" t="s">
-        <v>3366</v>
+        <v>3367</v>
       </c>
       <c r="P855" s="5"/>
       <c r="Q855" s="4" t="s">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="R855" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S855" s="4">
-        <v>4869737.28</v>
+        <v>5354617.7</v>
       </c>
       <c r="T855" s="4">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="U855" s="4" t="s">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="V855" s="4" t="s">
-        <v>217</v>
+        <v>515</v>
       </c>
       <c r="W855" s="4">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="X855" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y855" s="4"/>
       <c r="Z855" s="4" t="s">
-        <v>109</v>
+        <v>3370</v>
       </c>
       <c r="AA855" s="4"/>
       <c r="AB855" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="856" spans="1:28">
@@ -76171,57 +76109,57 @@
         <v>33</v>
       </c>
       <c r="C856" s="4">
-        <v>167709123</v>
+        <v>168888525</v>
       </c>
       <c r="D856" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E856" s="4">
-        <v>5607771</v>
+        <v>1336389</v>
       </c>
       <c r="F856" s="4" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="G856" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H856" s="4" t="s">
-        <v>3094</v>
+        <v>3358</v>
       </c>
       <c r="I856" s="4" t="s">
-        <v>3369</v>
+        <v>3358</v>
       </c>
       <c r="J856" s="4" t="s">
-        <v>3369</v>
+        <v>1588</v>
       </c>
       <c r="K856" s="4"/>
-      <c r="L856" s="4"/>
-      <c r="M856" s="4"/>
+      <c r="L856" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="M856" s="4" t="s">
+        <v>219</v>
+      </c>
       <c r="N856" s="4"/>
       <c r="O856" s="4" t="s">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="P856" s="5"/>
       <c r="Q856" s="4" t="s">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="R856" s="4" t="s">
         <v>56</v>
       </c>
       <c r="S856" s="4">
-        <v>4274093.02</v>
+        <v>0</v>
       </c>
       <c r="T856" s="4">
-        <v>26</v>
-      </c>
-      <c r="U856" s="4" t="s">
-        <v>3372</v>
-      </c>
-      <c r="V856" s="4" t="s">
-        <v>173</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U856" s="4"/>
+      <c r="V856" s="4"/>
       <c r="W856" s="4">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="X856" s="4" t="s">
         <v>46</v>
@@ -76230,9 +76168,7 @@
       <c r="Z856" s="4" t="s">
         <v>3373</v>
       </c>
-      <c r="AA856" s="4" t="s">
-        <v>445</v>
-      </c>
+      <c r="AA856" s="4"/>
       <c r="AB856" s="4" t="s">
         <v>61</v>
       </c>
@@ -76245,13 +76181,13 @@
         <v>33</v>
       </c>
       <c r="C857" s="4">
-        <v>166985500</v>
+        <v>169092476</v>
       </c>
       <c r="D857" s="4" t="s">
-        <v>364</v>
+        <v>50</v>
       </c>
       <c r="E857" s="4">
-        <v>8370701</v>
+        <v>5653487</v>
       </c>
       <c r="F857" s="4" t="s">
         <v>35</v>
@@ -76260,33 +76196,33 @@
         <v>36</v>
       </c>
       <c r="H857" s="4" t="s">
+        <v>3358</v>
+      </c>
+      <c r="I857" s="4" t="s">
+        <v>3358</v>
+      </c>
+      <c r="J857" s="4" t="s">
         <v>3374</v>
-      </c>
-      <c r="I857" s="4" t="s">
-        <v>3374</v>
-      </c>
-      <c r="J857" s="4" t="s">
-        <v>3375</v>
       </c>
       <c r="K857" s="4"/>
       <c r="L857" s="4" t="s">
+        <v>3065</v>
+      </c>
+      <c r="M857" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="M857" s="4" t="s">
-        <v>3376</v>
-      </c>
       <c r="N857" s="4">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="O857" s="4" t="s">
-        <v>3377</v>
+        <v>3375</v>
       </c>
       <c r="P857" s="5"/>
       <c r="Q857" s="4" t="s">
-        <v>3378</v>
+        <v>3376</v>
       </c>
       <c r="R857" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S857" s="4">
         <v>0</v>
@@ -76294,17 +76230,21 @@
       <c r="T857" s="4">
         <v>0</v>
       </c>
-      <c r="U857" s="4"/>
-      <c r="V857" s="4"/>
+      <c r="U857" s="4" t="s">
+        <v>3377</v>
+      </c>
+      <c r="V857" s="4" t="s">
+        <v>439</v>
+      </c>
       <c r="W857" s="4">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="X857" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y857" s="4"/>
       <c r="Z857" s="4" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="AA857" s="4"/>
       <c r="AB857" s="4" t="s">
@@ -76319,13 +76259,13 @@
         <v>33</v>
       </c>
       <c r="C858" s="4">
-        <v>166986360</v>
+        <v>169821857</v>
       </c>
       <c r="D858" s="4" t="s">
-        <v>364</v>
+        <v>34</v>
       </c>
       <c r="E858" s="4">
-        <v>8370708</v>
+        <v>7623292</v>
       </c>
       <c r="F858" s="4" t="s">
         <v>35</v>
@@ -76334,51 +76274,55 @@
         <v>36</v>
       </c>
       <c r="H858" s="4" t="s">
-        <v>3374</v>
+        <v>3358</v>
       </c>
       <c r="I858" s="4" t="s">
-        <v>3374</v>
+        <v>3358</v>
       </c>
       <c r="J858" s="4" t="s">
-        <v>3375</v>
+        <v>3379</v>
       </c>
       <c r="K858" s="4"/>
       <c r="L858" s="4" t="s">
-        <v>224</v>
+        <v>2485</v>
       </c>
       <c r="M858" s="4" t="s">
-        <v>3376</v>
+        <v>148</v>
       </c>
       <c r="N858" s="4">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="O858" s="4" t="s">
         <v>3380</v>
       </c>
       <c r="P858" s="5"/>
       <c r="Q858" s="4" t="s">
-        <v>3378</v>
+        <v>3381</v>
       </c>
       <c r="R858" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="S858" s="4">
-        <v>2277764.52</v>
+        <v>3920332.09</v>
       </c>
       <c r="T858" s="4">
-        <v>3</v>
-      </c>
-      <c r="U858" s="4"/>
-      <c r="V858" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="U858" s="4" t="s">
+        <v>3382</v>
+      </c>
+      <c r="V858" s="4" t="s">
+        <v>173</v>
+      </c>
       <c r="W858" s="4">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="X858" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y858" s="4"/>
       <c r="Z858" s="4" t="s">
-        <v>3381</v>
+        <v>3383</v>
       </c>
       <c r="AA858" s="4"/>
       <c r="AB858" s="4" t="s">
@@ -76393,13 +76337,13 @@
         <v>33</v>
       </c>
       <c r="C859" s="4">
-        <v>170400653</v>
+        <v>167328603</v>
       </c>
       <c r="D859" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E859" s="4">
-        <v>8370701</v>
+        <v>1117251</v>
       </c>
       <c r="F859" s="4" t="s">
         <v>35</v>
@@ -76408,53 +76352,57 @@
         <v>36</v>
       </c>
       <c r="H859" s="4" t="s">
-        <v>3374</v>
+        <v>3358</v>
       </c>
       <c r="I859" s="4" t="s">
-        <v>3374</v>
+        <v>3358</v>
       </c>
       <c r="J859" s="4" t="s">
-        <v>3375</v>
+        <v>3379</v>
       </c>
       <c r="K859" s="4"/>
       <c r="L859" s="4" t="s">
-        <v>224</v>
+        <v>148</v>
       </c>
       <c r="M859" s="4" t="s">
-        <v>3376</v>
-      </c>
-      <c r="N859" s="4">
-        <v>7</v>
-      </c>
+        <v>2467</v>
+      </c>
+      <c r="N859" s="4"/>
       <c r="O859" s="4" t="s">
-        <v>3377</v>
+        <v>3384</v>
       </c>
       <c r="P859" s="5"/>
       <c r="Q859" s="4" t="s">
-        <v>3378</v>
+        <v>3385</v>
       </c>
       <c r="R859" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S859" s="4">
-        <v>241005</v>
+        <v>0</v>
       </c>
       <c r="T859" s="4">
-        <v>2</v>
-      </c>
-      <c r="U859" s="4"/>
-      <c r="V859" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="U859" s="4" t="s">
+        <v>3386</v>
+      </c>
+      <c r="V859" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="W859" s="4">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="X859" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y859" s="4"/>
       <c r="Z859" s="4" t="s">
-        <v>3382</v>
-      </c>
-      <c r="AA859" s="4"/>
+        <v>3387</v>
+      </c>
+      <c r="AA859" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="AB859" s="4" t="s">
         <v>61</v>
       </c>
@@ -76467,13 +76415,13 @@
         <v>33</v>
       </c>
       <c r="C860" s="4">
-        <v>165796789</v>
+        <v>167009144</v>
       </c>
       <c r="D860" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E860" s="4">
-        <v>6265969</v>
+        <v>6747980</v>
       </c>
       <c r="F860" s="4" t="s">
         <v>35</v>
@@ -76482,53 +76430,53 @@
         <v>36</v>
       </c>
       <c r="H860" s="4" t="s">
-        <v>3374</v>
+        <v>3358</v>
       </c>
       <c r="I860" s="4" t="s">
-        <v>3374</v>
+        <v>3358</v>
       </c>
       <c r="J860" s="4" t="s">
-        <v>3375</v>
+        <v>3379</v>
       </c>
       <c r="K860" s="4"/>
       <c r="L860" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="M860" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="M860" s="4" t="s">
-        <v>199</v>
       </c>
       <c r="N860" s="4"/>
       <c r="O860" s="4" t="s">
-        <v>3383</v>
+        <v>3388</v>
       </c>
       <c r="P860" s="5"/>
       <c r="Q860" s="4" t="s">
-        <v>3384</v>
+        <v>3389</v>
       </c>
       <c r="R860" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S860" s="4">
-        <v>5354617.7</v>
+        <v>10011293.94</v>
       </c>
       <c r="T860" s="4">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="U860" s="4" t="s">
-        <v>3385</v>
+        <v>3390</v>
       </c>
       <c r="V860" s="4" t="s">
-        <v>515</v>
+        <v>173</v>
       </c>
       <c r="W860" s="4">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="X860" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y860" s="4"/>
       <c r="Z860" s="4" t="s">
-        <v>3386</v>
+        <v>3391</v>
       </c>
       <c r="AA860" s="4"/>
       <c r="AB860" s="4" t="s">
@@ -76543,13 +76491,13 @@
         <v>33</v>
       </c>
       <c r="C861" s="4">
-        <v>168888525</v>
+        <v>170423305</v>
       </c>
       <c r="D861" s="4" t="s">
-        <v>50</v>
+        <v>417</v>
       </c>
       <c r="E861" s="4">
-        <v>1336389</v>
+        <v>8400324</v>
       </c>
       <c r="F861" s="4" t="s">
         <v>35</v>
@@ -76558,28 +76506,24 @@
         <v>36</v>
       </c>
       <c r="H861" s="4" t="s">
-        <v>3374</v>
+        <v>3358</v>
       </c>
       <c r="I861" s="4" t="s">
-        <v>3374</v>
+        <v>3358</v>
       </c>
       <c r="J861" s="4" t="s">
-        <v>1588</v>
+        <v>1073</v>
       </c>
       <c r="K861" s="4"/>
-      <c r="L861" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="M861" s="4" t="s">
-        <v>219</v>
-      </c>
+      <c r="L861" s="4"/>
+      <c r="M861" s="4"/>
       <c r="N861" s="4"/>
       <c r="O861" s="4" t="s">
-        <v>3387</v>
+        <v>3392</v>
       </c>
       <c r="P861" s="5"/>
       <c r="Q861" s="4" t="s">
-        <v>3388</v>
+        <v>3393</v>
       </c>
       <c r="R861" s="4" t="s">
         <v>56</v>
@@ -76593,18 +76537,18 @@
       <c r="U861" s="4"/>
       <c r="V861" s="4"/>
       <c r="W861" s="4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="X861" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y861" s="4"/>
       <c r="Z861" s="4" t="s">
-        <v>3389</v>
+        <v>3394</v>
       </c>
       <c r="AA861" s="4"/>
       <c r="AB861" s="4" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
     </row>
     <row r="862" spans="1:28">
@@ -76615,13 +76559,13 @@
         <v>33</v>
       </c>
       <c r="C862" s="4">
-        <v>169092476</v>
+        <v>164808120</v>
       </c>
       <c r="D862" s="4" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="E862" s="4">
-        <v>5653487</v>
+        <v>6265736</v>
       </c>
       <c r="F862" s="4" t="s">
         <v>35</v>
@@ -76630,55 +76574,53 @@
         <v>36</v>
       </c>
       <c r="H862" s="4" t="s">
-        <v>3374</v>
+        <v>3358</v>
       </c>
       <c r="I862" s="4" t="s">
-        <v>3374</v>
+        <v>3358</v>
       </c>
       <c r="J862" s="4" t="s">
-        <v>3390</v>
+        <v>1073</v>
       </c>
       <c r="K862" s="4"/>
       <c r="L862" s="4" t="s">
-        <v>3065</v>
+        <v>453</v>
       </c>
       <c r="M862" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="N862" s="4">
-        <v>50</v>
-      </c>
+        <v>3395</v>
+      </c>
+      <c r="N862" s="4"/>
       <c r="O862" s="4" t="s">
-        <v>3391</v>
+        <v>3396</v>
       </c>
       <c r="P862" s="5"/>
       <c r="Q862" s="4" t="s">
-        <v>3392</v>
+        <v>3397</v>
       </c>
       <c r="R862" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S862" s="4">
-        <v>0</v>
+        <v>3817749.56</v>
       </c>
       <c r="T862" s="4">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="U862" s="4" t="s">
-        <v>3393</v>
+        <v>3398</v>
       </c>
       <c r="V862" s="4" t="s">
-        <v>439</v>
+        <v>217</v>
       </c>
       <c r="W862" s="4">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="X862" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y862" s="4"/>
       <c r="Z862" s="4" t="s">
-        <v>3394</v>
+        <v>109</v>
       </c>
       <c r="AA862" s="4"/>
       <c r="AB862" s="4" t="s">
@@ -76693,13 +76635,13 @@
         <v>33</v>
       </c>
       <c r="C863" s="4">
-        <v>169821857</v>
+        <v>167028650</v>
       </c>
       <c r="D863" s="4" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="E863" s="4">
-        <v>7623292</v>
+        <v>5664526</v>
       </c>
       <c r="F863" s="4" t="s">
         <v>35</v>
@@ -76708,55 +76650,53 @@
         <v>36</v>
       </c>
       <c r="H863" s="4" t="s">
-        <v>3374</v>
+        <v>3358</v>
       </c>
       <c r="I863" s="4" t="s">
-        <v>3374</v>
+        <v>3358</v>
       </c>
       <c r="J863" s="4" t="s">
-        <v>3395</v>
+        <v>1073</v>
       </c>
       <c r="K863" s="4"/>
       <c r="L863" s="4" t="s">
-        <v>2485</v>
+        <v>98</v>
       </c>
       <c r="M863" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="N863" s="4">
-        <v>25</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N863" s="4"/>
       <c r="O863" s="4" t="s">
-        <v>3396</v>
+        <v>3399</v>
       </c>
       <c r="P863" s="5"/>
       <c r="Q863" s="4" t="s">
-        <v>3397</v>
+        <v>3400</v>
       </c>
       <c r="R863" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="S863" s="4">
-        <v>3920332.09</v>
+        <v>7062.05</v>
       </c>
       <c r="T863" s="4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="U863" s="4" t="s">
-        <v>3398</v>
+        <v>3401</v>
       </c>
       <c r="V863" s="4" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="W863" s="4">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="X863" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y863" s="4"/>
       <c r="Z863" s="4" t="s">
-        <v>3399</v>
+        <v>109</v>
       </c>
       <c r="AA863" s="4"/>
       <c r="AB863" s="4" t="s">
@@ -76768,49 +76708,49 @@
         <v>1000</v>
       </c>
       <c r="B864" s="4" t="s">
-        <v>33</v>
+        <v>590</v>
       </c>
       <c r="C864" s="4">
-        <v>167328603</v>
+        <v>170209996</v>
       </c>
       <c r="D864" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E864" s="4">
-        <v>1117251</v>
+        <v>6262508</v>
       </c>
       <c r="F864" s="4" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="G864" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H864" s="4" t="s">
-        <v>3374</v>
+        <v>3402</v>
       </c>
       <c r="I864" s="4" t="s">
-        <v>3374</v>
+        <v>3402</v>
       </c>
       <c r="J864" s="4" t="s">
-        <v>3395</v>
+        <v>3403</v>
       </c>
       <c r="K864" s="4"/>
       <c r="L864" s="4" t="s">
-        <v>148</v>
+        <v>2467</v>
       </c>
       <c r="M864" s="4" t="s">
-        <v>2467</v>
+        <v>157</v>
       </c>
       <c r="N864" s="4"/>
       <c r="O864" s="4" t="s">
-        <v>3400</v>
+        <v>3404</v>
       </c>
       <c r="P864" s="5"/>
       <c r="Q864" s="4" t="s">
-        <v>3401</v>
+        <v>3405</v>
       </c>
       <c r="R864" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S864" s="4">
         <v>0</v>
@@ -76819,20 +76759,20 @@
         <v>0</v>
       </c>
       <c r="U864" s="4" t="s">
-        <v>3402</v>
+        <v>3406</v>
       </c>
       <c r="V864" s="4" t="s">
-        <v>45</v>
+        <v>217</v>
       </c>
       <c r="W864" s="4">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="X864" s="4" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="Y864" s="4"/>
       <c r="Z864" s="4" t="s">
-        <v>3403</v>
+        <v>3407</v>
       </c>
       <c r="AA864" s="4" t="s">
         <v>60</v>
@@ -76849,70 +76789,70 @@
         <v>33</v>
       </c>
       <c r="C865" s="4">
-        <v>167009144</v>
+        <v>170416264</v>
       </c>
       <c r="D865" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E865" s="4">
-        <v>6747980</v>
+        <v>5603011</v>
       </c>
       <c r="F865" s="4" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="G865" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H865" s="4" t="s">
-        <v>3374</v>
+        <v>3402</v>
       </c>
       <c r="I865" s="4" t="s">
-        <v>3374</v>
+        <v>3402</v>
       </c>
       <c r="J865" s="4" t="s">
-        <v>3395</v>
+        <v>906</v>
       </c>
       <c r="K865" s="4"/>
       <c r="L865" s="4" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="M865" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="N865" s="4"/>
+        <v>53</v>
+      </c>
+      <c r="N865" s="4">
+        <v>5</v>
+      </c>
       <c r="O865" s="4" t="s">
-        <v>3404</v>
+        <v>3408</v>
       </c>
       <c r="P865" s="5"/>
       <c r="Q865" s="4" t="s">
-        <v>3405</v>
+        <v>3409</v>
       </c>
       <c r="R865" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S865" s="4">
-        <v>10011293.94</v>
+        <v>1892491.87</v>
       </c>
       <c r="T865" s="4">
-        <v>52</v>
-      </c>
-      <c r="U865" s="4" t="s">
-        <v>3406</v>
-      </c>
-      <c r="V865" s="4" t="s">
-        <v>173</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U865" s="4"/>
+      <c r="V865" s="4"/>
       <c r="W865" s="4">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="X865" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y865" s="4"/>
       <c r="Z865" s="4" t="s">
-        <v>3407</v>
-      </c>
-      <c r="AA865" s="4"/>
+        <v>3410</v>
+      </c>
+      <c r="AA865" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB865" s="4" t="s">
         <v>61</v>
       </c>
@@ -76925,42 +76865,46 @@
         <v>33</v>
       </c>
       <c r="C866" s="4">
-        <v>170423305</v>
+        <v>170403907</v>
       </c>
       <c r="D866" s="4" t="s">
-        <v>417</v>
+        <v>286</v>
       </c>
       <c r="E866" s="4">
-        <v>8400324</v>
+        <v>5601040</v>
       </c>
       <c r="F866" s="4" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="G866" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H866" s="4" t="s">
-        <v>3374</v>
+        <v>3411</v>
       </c>
       <c r="I866" s="4" t="s">
-        <v>3374</v>
+        <v>3412</v>
       </c>
       <c r="J866" s="4" t="s">
-        <v>1073</v>
+        <v>3413</v>
       </c>
       <c r="K866" s="4"/>
-      <c r="L866" s="4"/>
-      <c r="M866" s="4"/>
+      <c r="L866" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M866" s="4" t="s">
+        <v>705</v>
+      </c>
       <c r="N866" s="4"/>
       <c r="O866" s="4" t="s">
-        <v>3408</v>
+        <v>3414</v>
       </c>
       <c r="P866" s="5"/>
       <c r="Q866" s="4" t="s">
-        <v>3409</v>
+        <v>3415</v>
       </c>
       <c r="R866" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S866" s="4">
         <v>0</v>
@@ -76978,11 +76922,13 @@
       </c>
       <c r="Y866" s="4"/>
       <c r="Z866" s="4" t="s">
-        <v>3410</v>
-      </c>
-      <c r="AA866" s="4"/>
+        <v>3416</v>
+      </c>
+      <c r="AA866" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB866" s="4" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
     </row>
     <row r="867" spans="1:28">
@@ -76993,70 +76939,70 @@
         <v>33</v>
       </c>
       <c r="C867" s="4">
-        <v>164808120</v>
+        <v>170323984</v>
       </c>
       <c r="D867" s="4" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="E867" s="4">
-        <v>6265736</v>
+        <v>8029205</v>
       </c>
       <c r="F867" s="4" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="G867" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H867" s="4" t="s">
-        <v>3374</v>
+        <v>3411</v>
       </c>
       <c r="I867" s="4" t="s">
-        <v>3374</v>
+        <v>3412</v>
       </c>
       <c r="J867" s="4" t="s">
-        <v>1073</v>
+        <v>3417</v>
       </c>
       <c r="K867" s="4"/>
       <c r="L867" s="4" t="s">
-        <v>453</v>
+        <v>281</v>
       </c>
       <c r="M867" s="4" t="s">
-        <v>3411</v>
-      </c>
-      <c r="N867" s="4"/>
+        <v>81</v>
+      </c>
+      <c r="N867" s="4">
+        <v>5</v>
+      </c>
       <c r="O867" s="4" t="s">
-        <v>3412</v>
+        <v>3418</v>
       </c>
       <c r="P867" s="5"/>
       <c r="Q867" s="4" t="s">
-        <v>3413</v>
+        <v>3419</v>
       </c>
       <c r="R867" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S867" s="4">
-        <v>3817749.56</v>
+        <v>180277.94</v>
       </c>
       <c r="T867" s="4">
-        <v>70</v>
-      </c>
-      <c r="U867" s="4" t="s">
-        <v>3414</v>
-      </c>
-      <c r="V867" s="4" t="s">
-        <v>217</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U867" s="4"/>
+      <c r="V867" s="4"/>
       <c r="W867" s="4">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="X867" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y867" s="4"/>
       <c r="Z867" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA867" s="4"/>
+        <v>3420</v>
+      </c>
+      <c r="AA867" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB867" s="4" t="s">
         <v>61</v>
       </c>
@@ -77069,61 +77015,59 @@
         <v>33</v>
       </c>
       <c r="C868" s="4">
-        <v>167028650</v>
+        <v>170415204</v>
       </c>
       <c r="D868" s="4" t="s">
         <v>103</v>
       </c>
       <c r="E868" s="4">
-        <v>5664526</v>
+        <v>8023961</v>
       </c>
       <c r="F868" s="4" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="G868" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H868" s="4" t="s">
-        <v>3374</v>
+        <v>3411</v>
       </c>
       <c r="I868" s="4" t="s">
-        <v>3374</v>
+        <v>3412</v>
       </c>
       <c r="J868" s="4" t="s">
-        <v>1073</v>
+        <v>3417</v>
       </c>
       <c r="K868" s="4"/>
       <c r="L868" s="4" t="s">
-        <v>98</v>
+        <v>704</v>
       </c>
       <c r="M868" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="N868" s="4"/>
+        <v>105</v>
+      </c>
+      <c r="N868" s="4">
+        <v>50</v>
+      </c>
       <c r="O868" s="4" t="s">
-        <v>3415</v>
+        <v>3421</v>
       </c>
       <c r="P868" s="5"/>
       <c r="Q868" s="4" t="s">
-        <v>3416</v>
+        <v>3422</v>
       </c>
       <c r="R868" s="4" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="S868" s="4">
-        <v>7062.05</v>
+        <v>0</v>
       </c>
       <c r="T868" s="4">
-        <v>1</v>
-      </c>
-      <c r="U868" s="4" t="s">
-        <v>3417</v>
-      </c>
-      <c r="V868" s="4" t="s">
-        <v>153</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U868" s="4"/>
+      <c r="V868" s="4"/>
       <c r="W868" s="4">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="X868" s="4" t="s">
         <v>46</v>
@@ -77145,13 +77089,13 @@
         <v>590</v>
       </c>
       <c r="C869" s="4">
-        <v>170209996</v>
+        <v>170486293</v>
       </c>
       <c r="D869" s="4" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="E869" s="4">
-        <v>6262508</v>
+        <v>5659891</v>
       </c>
       <c r="F869" s="4" t="s">
         <v>140</v>
@@ -77160,31 +77104,31 @@
         <v>36</v>
       </c>
       <c r="H869" s="4" t="s">
-        <v>3418</v>
+        <v>3411</v>
       </c>
       <c r="I869" s="4" t="s">
-        <v>3418</v>
+        <v>3412</v>
       </c>
       <c r="J869" s="4" t="s">
-        <v>3419</v>
+        <v>3423</v>
       </c>
       <c r="K869" s="4"/>
       <c r="L869" s="4" t="s">
-        <v>2467</v>
+        <v>566</v>
       </c>
       <c r="M869" s="4" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="N869" s="4"/>
       <c r="O869" s="4" t="s">
-        <v>3420</v>
+        <v>3424</v>
       </c>
       <c r="P869" s="5"/>
       <c r="Q869" s="4" t="s">
-        <v>3421</v>
+        <v>3425</v>
       </c>
       <c r="R869" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S869" s="4">
         <v>0</v>
@@ -77192,24 +77136,20 @@
       <c r="T869" s="4">
         <v>0</v>
       </c>
-      <c r="U869" s="4" t="s">
-        <v>3422</v>
-      </c>
-      <c r="V869" s="4" t="s">
-        <v>217</v>
-      </c>
+      <c r="U869" s="4"/>
+      <c r="V869" s="4"/>
       <c r="W869" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X869" s="4" t="s">
         <v>182</v>
       </c>
       <c r="Y869" s="4"/>
       <c r="Z869" s="4" t="s">
-        <v>3423</v>
+        <v>3426</v>
       </c>
       <c r="AA869" s="4" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="AB869" s="4" t="s">
         <v>61</v>
@@ -77223,13 +77163,13 @@
         <v>33</v>
       </c>
       <c r="C870" s="4">
-        <v>170416264</v>
+        <v>170494808</v>
       </c>
       <c r="D870" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E870" s="4">
-        <v>5603011</v>
+        <v>7705610</v>
       </c>
       <c r="F870" s="4" t="s">
         <v>140</v>
@@ -77238,54 +77178,56 @@
         <v>36</v>
       </c>
       <c r="H870" s="4" t="s">
-        <v>3418</v>
+        <v>3411</v>
       </c>
       <c r="I870" s="4" t="s">
-        <v>3418</v>
+        <v>3412</v>
       </c>
       <c r="J870" s="4" t="s">
-        <v>906</v>
+        <v>3423</v>
       </c>
       <c r="K870" s="4"/>
       <c r="L870" s="4" t="s">
-        <v>122</v>
+        <v>566</v>
       </c>
       <c r="M870" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="N870" s="4">
-        <v>5</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N870" s="4"/>
       <c r="O870" s="4" t="s">
-        <v>3424</v>
+        <v>3427</v>
       </c>
       <c r="P870" s="5"/>
       <c r="Q870" s="4" t="s">
-        <v>3425</v>
+        <v>3428</v>
       </c>
       <c r="R870" s="4" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="S870" s="4">
-        <v>1892491.87</v>
+        <v>0</v>
       </c>
       <c r="T870" s="4">
+        <v>0</v>
+      </c>
+      <c r="U870" s="4" t="s">
+        <v>3429</v>
+      </c>
+      <c r="V870" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="W870" s="4">
         <v>1</v>
-      </c>
-      <c r="U870" s="4"/>
-      <c r="V870" s="4"/>
-      <c r="W870" s="4">
-        <v>2</v>
       </c>
       <c r="X870" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y870" s="4"/>
       <c r="Z870" s="4" t="s">
-        <v>3426</v>
+        <v>3430</v>
       </c>
       <c r="AA870" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="AB870" s="4" t="s">
         <v>61</v>
@@ -77296,16 +77238,16 @@
         <v>1000</v>
       </c>
       <c r="B871" s="4" t="s">
-        <v>33</v>
+        <v>590</v>
       </c>
       <c r="C871" s="4">
-        <v>170403907</v>
+        <v>170177663</v>
       </c>
       <c r="D871" s="4" t="s">
-        <v>286</v>
+        <v>50</v>
       </c>
       <c r="E871" s="4">
-        <v>5601040</v>
+        <v>5613560</v>
       </c>
       <c r="F871" s="4" t="s">
         <v>140</v>
@@ -77314,52 +77256,56 @@
         <v>36</v>
       </c>
       <c r="H871" s="4" t="s">
-        <v>3427</v>
+        <v>3411</v>
       </c>
       <c r="I871" s="4" t="s">
-        <v>3428</v>
+        <v>3412</v>
       </c>
       <c r="J871" s="4" t="s">
-        <v>3429</v>
+        <v>928</v>
       </c>
       <c r="K871" s="4"/>
       <c r="L871" s="4" t="s">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="M871" s="4" t="s">
-        <v>705</v>
+        <v>335</v>
       </c>
       <c r="N871" s="4"/>
       <c r="O871" s="4" t="s">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="P871" s="5"/>
       <c r="Q871" s="4" t="s">
-        <v>3431</v>
+        <v>3432</v>
       </c>
       <c r="R871" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S871" s="4">
-        <v>0</v>
+        <v>61796.29</v>
       </c>
       <c r="T871" s="4">
-        <v>0</v>
-      </c>
-      <c r="U871" s="4"/>
-      <c r="V871" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="U871" s="4" t="s">
+        <v>3433</v>
+      </c>
+      <c r="V871" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="W871" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X871" s="4" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="Y871" s="4"/>
       <c r="Z871" s="4" t="s">
-        <v>3432</v>
+        <v>3434</v>
       </c>
       <c r="AA871" s="4" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="AB871" s="4" t="s">
         <v>61</v>
@@ -77373,13 +77319,13 @@
         <v>33</v>
       </c>
       <c r="C872" s="4">
-        <v>170323984</v>
+        <v>170399493</v>
       </c>
       <c r="D872" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E872" s="4">
-        <v>8029205</v>
+        <v>5613472</v>
       </c>
       <c r="F872" s="4" t="s">
         <v>140</v>
@@ -77388,57 +77334,59 @@
         <v>36</v>
       </c>
       <c r="H872" s="4" t="s">
-        <v>3427</v>
+        <v>3411</v>
       </c>
       <c r="I872" s="4" t="s">
-        <v>3428</v>
+        <v>3412</v>
       </c>
       <c r="J872" s="4" t="s">
-        <v>3433</v>
+        <v>928</v>
       </c>
       <c r="K872" s="4"/>
       <c r="L872" s="4" t="s">
-        <v>281</v>
+        <v>566</v>
       </c>
       <c r="M872" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="N872" s="4">
-        <v>5</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N872" s="4"/>
       <c r="O872" s="4" t="s">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="P872" s="5"/>
       <c r="Q872" s="4" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="R872" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S872" s="4">
-        <v>180277.94</v>
+        <v>250707.93</v>
       </c>
       <c r="T872" s="4">
-        <v>1</v>
-      </c>
-      <c r="U872" s="4"/>
-      <c r="V872" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="U872" s="4" t="s">
+        <v>3437</v>
+      </c>
+      <c r="V872" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="W872" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X872" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y872" s="4"/>
       <c r="Z872" s="4" t="s">
-        <v>3436</v>
+        <v>3438</v>
       </c>
       <c r="AA872" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="AB872" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="873" spans="1:28">
@@ -77446,16 +77394,16 @@
         <v>1000</v>
       </c>
       <c r="B873" s="4" t="s">
-        <v>33</v>
+        <v>590</v>
       </c>
       <c r="C873" s="4">
-        <v>170415204</v>
+        <v>170493990</v>
       </c>
       <c r="D873" s="4" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E873" s="4">
-        <v>8023961</v>
+        <v>5613065</v>
       </c>
       <c r="F873" s="4" t="s">
         <v>140</v>
@@ -77464,33 +77412,31 @@
         <v>36</v>
       </c>
       <c r="H873" s="4" t="s">
-        <v>3427</v>
+        <v>3411</v>
       </c>
       <c r="I873" s="4" t="s">
-        <v>3428</v>
+        <v>3412</v>
       </c>
       <c r="J873" s="4" t="s">
-        <v>3433</v>
+        <v>928</v>
       </c>
       <c r="K873" s="4"/>
       <c r="L873" s="4" t="s">
-        <v>704</v>
+        <v>219</v>
       </c>
       <c r="M873" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="N873" s="4">
-        <v>50</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="N873" s="4"/>
       <c r="O873" s="4" t="s">
-        <v>3437</v>
+        <v>3439</v>
       </c>
       <c r="P873" s="5"/>
       <c r="Q873" s="4" t="s">
-        <v>3438</v>
+        <v>3440</v>
       </c>
       <c r="R873" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S873" s="4">
         <v>0</v>
@@ -77501,16 +77447,18 @@
       <c r="U873" s="4"/>
       <c r="V873" s="4"/>
       <c r="W873" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X873" s="4" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="Y873" s="4"/>
       <c r="Z873" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA873" s="4"/>
+        <v>3441</v>
+      </c>
+      <c r="AA873" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="AB873" s="4" t="s">
         <v>61</v>
       </c>
@@ -77520,16 +77468,16 @@
         <v>1000</v>
       </c>
       <c r="B874" s="4" t="s">
-        <v>590</v>
+        <v>33</v>
       </c>
       <c r="C874" s="4">
-        <v>170486293</v>
+        <v>170355425</v>
       </c>
       <c r="D874" s="4" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E874" s="4">
-        <v>5659891</v>
+        <v>5613029</v>
       </c>
       <c r="F874" s="4" t="s">
         <v>140</v>
@@ -77538,28 +77486,28 @@
         <v>36</v>
       </c>
       <c r="H874" s="4" t="s">
-        <v>3427</v>
+        <v>3411</v>
       </c>
       <c r="I874" s="4" t="s">
-        <v>3428</v>
+        <v>3412</v>
       </c>
       <c r="J874" s="4" t="s">
-        <v>3439</v>
+        <v>928</v>
       </c>
       <c r="K874" s="4"/>
       <c r="L874" s="4" t="s">
-        <v>566</v>
+        <v>194</v>
       </c>
       <c r="M874" s="4" t="s">
-        <v>177</v>
+        <v>766</v>
       </c>
       <c r="N874" s="4"/>
       <c r="O874" s="4" t="s">
-        <v>3440</v>
+        <v>3442</v>
       </c>
       <c r="P874" s="5"/>
       <c r="Q874" s="4" t="s">
-        <v>3441</v>
+        <v>3443</v>
       </c>
       <c r="R874" s="4" t="s">
         <v>56</v>
@@ -77573,14 +77521,14 @@
       <c r="U874" s="4"/>
       <c r="V874" s="4"/>
       <c r="W874" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X874" s="4" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="Y874" s="4"/>
       <c r="Z874" s="4" t="s">
-        <v>3442</v>
+        <v>174</v>
       </c>
       <c r="AA874" s="4" t="s">
         <v>79</v>
@@ -77597,13 +77545,13 @@
         <v>33</v>
       </c>
       <c r="C875" s="4">
-        <v>170494808</v>
+        <v>170406503</v>
       </c>
       <c r="D875" s="4" t="s">
-        <v>50</v>
+        <v>286</v>
       </c>
       <c r="E875" s="4">
-        <v>7705610</v>
+        <v>5613329</v>
       </c>
       <c r="F875" s="4" t="s">
         <v>140</v>
@@ -77612,31 +77560,31 @@
         <v>36</v>
       </c>
       <c r="H875" s="4" t="s">
-        <v>3427</v>
+        <v>3411</v>
       </c>
       <c r="I875" s="4" t="s">
-        <v>3428</v>
+        <v>3412</v>
       </c>
       <c r="J875" s="4" t="s">
-        <v>3439</v>
+        <v>1165</v>
       </c>
       <c r="K875" s="4"/>
       <c r="L875" s="4" t="s">
-        <v>566</v>
+        <v>193</v>
       </c>
       <c r="M875" s="4" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="N875" s="4"/>
       <c r="O875" s="4" t="s">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="P875" s="5"/>
       <c r="Q875" s="4" t="s">
-        <v>3444</v>
+        <v>3445</v>
       </c>
       <c r="R875" s="4" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="S875" s="4">
         <v>0</v>
@@ -77644,14 +77592,10 @@
       <c r="T875" s="4">
         <v>0</v>
       </c>
-      <c r="U875" s="4" t="s">
-        <v>3445</v>
-      </c>
-      <c r="V875" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="U875" s="4"/>
+      <c r="V875" s="4"/>
       <c r="W875" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X875" s="4" t="s">
         <v>46</v>
@@ -77660,9 +77604,7 @@
       <c r="Z875" s="4" t="s">
         <v>3446</v>
       </c>
-      <c r="AA875" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="AA875" s="4"/>
       <c r="AB875" s="4" t="s">
         <v>61</v>
       </c>
@@ -77672,16 +77614,16 @@
         <v>1000</v>
       </c>
       <c r="B876" s="4" t="s">
-        <v>590</v>
+        <v>33</v>
       </c>
       <c r="C876" s="4">
-        <v>170177663</v>
+        <v>170505174</v>
       </c>
       <c r="D876" s="4" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="E876" s="4">
-        <v>5613560</v>
+        <v>1098787</v>
       </c>
       <c r="F876" s="4" t="s">
         <v>140</v>
@@ -77690,56 +77632,52 @@
         <v>36</v>
       </c>
       <c r="H876" s="4" t="s">
-        <v>3427</v>
+        <v>3411</v>
       </c>
       <c r="I876" s="4" t="s">
-        <v>3428</v>
+        <v>3412</v>
       </c>
       <c r="J876" s="4" t="s">
-        <v>928</v>
+        <v>3447</v>
       </c>
       <c r="K876" s="4"/>
       <c r="L876" s="4" t="s">
-        <v>224</v>
+        <v>617</v>
       </c>
       <c r="M876" s="4" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="N876" s="4"/>
       <c r="O876" s="4" t="s">
-        <v>3447</v>
+        <v>3448</v>
       </c>
       <c r="P876" s="5"/>
       <c r="Q876" s="4" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="R876" s="4" t="s">
         <v>56</v>
       </c>
       <c r="S876" s="4">
-        <v>61796.29</v>
+        <v>0</v>
       </c>
       <c r="T876" s="4">
-        <v>2</v>
-      </c>
-      <c r="U876" s="4" t="s">
-        <v>3449</v>
-      </c>
-      <c r="V876" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U876" s="4"/>
+      <c r="V876" s="4"/>
       <c r="W876" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X876" s="4" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="Y876" s="4"/>
       <c r="Z876" s="4" t="s">
         <v>3450</v>
       </c>
       <c r="AA876" s="4" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="AB876" s="4" t="s">
         <v>61</v>
@@ -77753,13 +77691,13 @@
         <v>33</v>
       </c>
       <c r="C877" s="4">
-        <v>170399493</v>
+        <v>170524918</v>
       </c>
       <c r="D877" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E877" s="4">
-        <v>5613472</v>
+        <v>5615101</v>
       </c>
       <c r="F877" s="4" t="s">
         <v>140</v>
@@ -77768,22 +77706,24 @@
         <v>36</v>
       </c>
       <c r="H877" s="4" t="s">
-        <v>3427</v>
+        <v>3411</v>
       </c>
       <c r="I877" s="4" t="s">
-        <v>3428</v>
+        <v>3412</v>
       </c>
       <c r="J877" s="4" t="s">
-        <v>928</v>
+        <v>3447</v>
       </c>
       <c r="K877" s="4"/>
       <c r="L877" s="4" t="s">
-        <v>566</v>
+        <v>617</v>
       </c>
       <c r="M877" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="N877" s="4"/>
+        <v>320</v>
+      </c>
+      <c r="N877" s="4">
+        <v>88</v>
+      </c>
       <c r="O877" s="4" t="s">
         <v>3451</v>
       </c>
@@ -77795,29 +77735,25 @@
         <v>56</v>
       </c>
       <c r="S877" s="4">
-        <v>250707.93</v>
+        <v>0</v>
       </c>
       <c r="T877" s="4">
-        <v>3</v>
-      </c>
-      <c r="U877" s="4" t="s">
-        <v>3453</v>
-      </c>
-      <c r="V877" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U877" s="4"/>
+      <c r="V877" s="4"/>
       <c r="W877" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X877" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y877" s="4"/>
       <c r="Z877" s="4" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="AA877" s="4" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="AB877" s="4" t="s">
         <v>49</v>
@@ -77828,49 +77764,51 @@
         <v>1000</v>
       </c>
       <c r="B878" s="4" t="s">
-        <v>590</v>
+        <v>33</v>
       </c>
       <c r="C878" s="4">
-        <v>170493990</v>
+        <v>167227156</v>
       </c>
       <c r="D878" s="4" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="E878" s="4">
-        <v>5613065</v>
+        <v>1130632</v>
       </c>
       <c r="F878" s="4" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="G878" s="4" t="s">
-        <v>36</v>
+        <v>3454</v>
       </c>
       <c r="H878" s="4" t="s">
-        <v>3427</v>
+        <v>3455</v>
       </c>
       <c r="I878" s="4" t="s">
-        <v>3428</v>
+        <v>3455</v>
       </c>
       <c r="J878" s="4" t="s">
-        <v>928</v>
+        <v>411</v>
       </c>
       <c r="K878" s="4"/>
       <c r="L878" s="4" t="s">
-        <v>219</v>
+        <v>352</v>
       </c>
       <c r="M878" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="N878" s="4"/>
+        <v>105</v>
+      </c>
+      <c r="N878" s="4">
+        <v>49</v>
+      </c>
       <c r="O878" s="4" t="s">
-        <v>3455</v>
+        <v>3456</v>
       </c>
       <c r="P878" s="5"/>
       <c r="Q878" s="4" t="s">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="R878" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S878" s="4">
         <v>0</v>
@@ -77878,17 +77816,21 @@
       <c r="T878" s="4">
         <v>0</v>
       </c>
-      <c r="U878" s="4"/>
-      <c r="V878" s="4"/>
+      <c r="U878" s="4" t="s">
+        <v>3458</v>
+      </c>
+      <c r="V878" s="4" t="s">
+        <v>217</v>
+      </c>
       <c r="W878" s="4">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="X878" s="4" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="Y878" s="4"/>
       <c r="Z878" s="4" t="s">
-        <v>3457</v>
+        <v>3459</v>
       </c>
       <c r="AA878" s="4" t="s">
         <v>60</v>
@@ -77905,451 +77847,75 @@
         <v>33</v>
       </c>
       <c r="C879" s="4">
-        <v>170355425</v>
+        <v>168526053</v>
       </c>
       <c r="D879" s="4" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="E879" s="4">
-        <v>5613029</v>
+        <v>1131068</v>
       </c>
       <c r="F879" s="4" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="G879" s="4" t="s">
-        <v>36</v>
+        <v>3454</v>
       </c>
       <c r="H879" s="4" t="s">
-        <v>3427</v>
+        <v>3455</v>
       </c>
       <c r="I879" s="4" t="s">
-        <v>3428</v>
+        <v>3455</v>
       </c>
       <c r="J879" s="4" t="s">
-        <v>928</v>
+        <v>411</v>
       </c>
       <c r="K879" s="4"/>
       <c r="L879" s="4" t="s">
-        <v>194</v>
+        <v>105</v>
       </c>
       <c r="M879" s="4" t="s">
-        <v>766</v>
-      </c>
-      <c r="N879" s="4"/>
+        <v>352</v>
+      </c>
+      <c r="N879" s="4">
+        <v>5</v>
+      </c>
       <c r="O879" s="4" t="s">
-        <v>3458</v>
+        <v>3460</v>
       </c>
       <c r="P879" s="5"/>
       <c r="Q879" s="4" t="s">
-        <v>3459</v>
+        <v>3461</v>
       </c>
       <c r="R879" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S879" s="4">
-        <v>0</v>
+        <v>40673.87</v>
       </c>
       <c r="T879" s="4">
-        <v>0</v>
-      </c>
-      <c r="U879" s="4"/>
-      <c r="V879" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U879" s="4" t="s">
+        <v>3462</v>
+      </c>
+      <c r="V879" s="4" t="s">
+        <v>217</v>
+      </c>
       <c r="W879" s="4">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="X879" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y879" s="4"/>
       <c r="Z879" s="4" t="s">
-        <v>174</v>
+        <v>3463</v>
       </c>
       <c r="AA879" s="4" t="s">
         <v>79</v>
       </c>
       <c r="AB879" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="880" spans="1:28">
-      <c r="A880" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B880" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C880" s="4">
-        <v>170406503</v>
-      </c>
-      <c r="D880" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="E880" s="4">
-        <v>5613329</v>
-      </c>
-      <c r="F880" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G880" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H880" s="4" t="s">
-        <v>3427</v>
-      </c>
-      <c r="I880" s="4" t="s">
-        <v>3428</v>
-      </c>
-      <c r="J880" s="4" t="s">
-        <v>1165</v>
-      </c>
-      <c r="K880" s="4"/>
-      <c r="L880" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="M880" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="N880" s="4"/>
-      <c r="O880" s="4" t="s">
-        <v>3460</v>
-      </c>
-      <c r="P880" s="5"/>
-      <c r="Q880" s="4" t="s">
-        <v>3461</v>
-      </c>
-      <c r="R880" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="S880" s="4">
-        <v>0</v>
-      </c>
-      <c r="T880" s="4">
-        <v>0</v>
-      </c>
-      <c r="U880" s="4"/>
-      <c r="V880" s="4"/>
-      <c r="W880" s="4">
-        <v>2</v>
-      </c>
-      <c r="X880" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y880" s="4"/>
-      <c r="Z880" s="4" t="s">
-        <v>3462</v>
-      </c>
-      <c r="AA880" s="4"/>
-      <c r="AB880" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="881" spans="1:28">
-      <c r="A881" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B881" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C881" s="4">
-        <v>170505174</v>
-      </c>
-      <c r="D881" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E881" s="4">
-        <v>1098787</v>
-      </c>
-      <c r="F881" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G881" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H881" s="4" t="s">
-        <v>3427</v>
-      </c>
-      <c r="I881" s="4" t="s">
-        <v>3428</v>
-      </c>
-      <c r="J881" s="4" t="s">
-        <v>3463</v>
-      </c>
-      <c r="K881" s="4"/>
-      <c r="L881" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="M881" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="N881" s="4"/>
-      <c r="O881" s="4" t="s">
-        <v>3464</v>
-      </c>
-      <c r="P881" s="5"/>
-      <c r="Q881" s="4" t="s">
-        <v>3465</v>
-      </c>
-      <c r="R881" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="S881" s="4">
-        <v>0</v>
-      </c>
-      <c r="T881" s="4">
-        <v>0</v>
-      </c>
-      <c r="U881" s="4"/>
-      <c r="V881" s="4"/>
-      <c r="W881" s="4">
-        <v>1</v>
-      </c>
-      <c r="X881" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y881" s="4"/>
-      <c r="Z881" s="4" t="s">
-        <v>3466</v>
-      </c>
-      <c r="AA881" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB881" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="882" spans="1:28">
-      <c r="A882" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B882" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C882" s="4">
-        <v>170524918</v>
-      </c>
-      <c r="D882" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E882" s="4">
-        <v>5615101</v>
-      </c>
-      <c r="F882" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G882" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H882" s="4" t="s">
-        <v>3427</v>
-      </c>
-      <c r="I882" s="4" t="s">
-        <v>3428</v>
-      </c>
-      <c r="J882" s="4" t="s">
-        <v>3463</v>
-      </c>
-      <c r="K882" s="4"/>
-      <c r="L882" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="M882" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="N882" s="4">
-        <v>88</v>
-      </c>
-      <c r="O882" s="4" t="s">
-        <v>3467</v>
-      </c>
-      <c r="P882" s="5"/>
-      <c r="Q882" s="4" t="s">
-        <v>3468</v>
-      </c>
-      <c r="R882" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="S882" s="4">
-        <v>0</v>
-      </c>
-      <c r="T882" s="4">
-        <v>0</v>
-      </c>
-      <c r="U882" s="4"/>
-      <c r="V882" s="4"/>
-      <c r="W882" s="4">
-        <v>0</v>
-      </c>
-      <c r="X882" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y882" s="4"/>
-      <c r="Z882" s="4" t="s">
-        <v>3469</v>
-      </c>
-      <c r="AA882" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB882" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="883" spans="1:28">
-      <c r="A883" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B883" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C883" s="4">
-        <v>167227156</v>
-      </c>
-      <c r="D883" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E883" s="4">
-        <v>1130632</v>
-      </c>
-      <c r="F883" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G883" s="4" t="s">
-        <v>3470</v>
-      </c>
-      <c r="H883" s="4" t="s">
-        <v>3471</v>
-      </c>
-      <c r="I883" s="4" t="s">
-        <v>3471</v>
-      </c>
-      <c r="J883" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="K883" s="4"/>
-      <c r="L883" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="M883" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="N883" s="4">
-        <v>49</v>
-      </c>
-      <c r="O883" s="4" t="s">
-        <v>3472</v>
-      </c>
-      <c r="P883" s="5"/>
-      <c r="Q883" s="4" t="s">
-        <v>3473</v>
-      </c>
-      <c r="R883" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="S883" s="4">
-        <v>0</v>
-      </c>
-      <c r="T883" s="4">
-        <v>0</v>
-      </c>
-      <c r="U883" s="4" t="s">
-        <v>3474</v>
-      </c>
-      <c r="V883" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="W883" s="4">
-        <v>38</v>
-      </c>
-      <c r="X883" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y883" s="4"/>
-      <c r="Z883" s="4" t="s">
-        <v>3475</v>
-      </c>
-      <c r="AA883" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB883" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="884" spans="1:28">
-      <c r="A884" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B884" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C884" s="4">
-        <v>168526053</v>
-      </c>
-      <c r="D884" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E884" s="4">
-        <v>1131068</v>
-      </c>
-      <c r="F884" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G884" s="4" t="s">
-        <v>3470</v>
-      </c>
-      <c r="H884" s="4" t="s">
-        <v>3471</v>
-      </c>
-      <c r="I884" s="4" t="s">
-        <v>3471</v>
-      </c>
-      <c r="J884" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="K884" s="4"/>
-      <c r="L884" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="M884" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="N884" s="4">
-        <v>5</v>
-      </c>
-      <c r="O884" s="4" t="s">
-        <v>3476</v>
-      </c>
-      <c r="P884" s="5"/>
-      <c r="Q884" s="4" t="s">
-        <v>3477</v>
-      </c>
-      <c r="R884" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="S884" s="4">
-        <v>40673.87</v>
-      </c>
-      <c r="T884" s="4">
-        <v>1</v>
-      </c>
-      <c r="U884" s="4" t="s">
-        <v>3478</v>
-      </c>
-      <c r="V884" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="W884" s="4">
-        <v>24</v>
-      </c>
-      <c r="X884" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y884" s="4"/>
-      <c r="Z884" s="4" t="s">
-        <v>3479</v>
-      </c>
-      <c r="AA884" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB884" s="4" t="s">
         <v>61</v>
       </c>
     </row>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="3457">
   <si>
     <t>DELTEC - GUAJIRA</t>
   </si>
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>29/10/2026 a las 10:32:25</t>
+    <t>29/10/2026 a las 10:33:09</t>
   </si>
   <si>
     <t>Num_Lote</t>
@@ -10010,18 +10010,6 @@
     <t>Investigar Dano medidor yo acometida SUSPENSION DE BORNERA. Reportado por IVR - Tel 3107449662</t>
   </si>
   <si>
-    <t>CR 4 OESTE</t>
-  </si>
-  <si>
-    <t>CR 4 OESTE CL 13 - 45 DPL Y1639</t>
-  </si>
-  <si>
-    <t>001213495-MC988</t>
-  </si>
-  <si>
-    <t>Revision Suministromedidor MD PQR SUSPENSION EN TENDIDO. Etilcio Aragon cc.1122397045 cel. 3170537360 solicita que se tome lectura verificar conexiones</t>
-  </si>
-  <si>
     <t>CR 5 OESTE</t>
   </si>
   <si>
@@ -10044,15 +10032,6 @@
   </si>
   <si>
     <t>Revision Suministromedidor MD PQR SUSPENSION EN TENDIDO. Elsa Yovana Meneses Moreno 3017946387 Rev gral medidor pruebas giro en vacio ver lectura digitos censo verficado conexiones ver todo</t>
-  </si>
-  <si>
-    <t>CR 11 CL 8 - 41 APTO 1 EG997</t>
-  </si>
-  <si>
-    <t>ONATE  JULIA</t>
-  </si>
-  <si>
-    <t>Revision Suministromedidor MD PQR SUSPENSION EN TENDIDO. Lida Rocio Penaranda Onate 3057861485 Rev gral medidor pruebas giro en vacio ver lectura digitos censo verficado conexiones ver todo</t>
   </si>
   <si>
     <t>CR 9 # CL 12 - 25 APTO 2 EG1508</t>
@@ -10800,7 +10779,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB879"/>
+  <dimension ref="A1:AB877"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -75277,13 +75256,13 @@
         <v>33</v>
       </c>
       <c r="C845" s="4">
-        <v>169842061</v>
+        <v>168725695</v>
       </c>
       <c r="D845" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E845" s="4">
-        <v>7722234</v>
+        <v>7798971</v>
       </c>
       <c r="F845" s="4" t="s">
         <v>140</v>
@@ -75308,42 +75287,42 @@
         <v>224</v>
       </c>
       <c r="N845" s="4">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="O845" s="4" t="s">
         <v>3332</v>
       </c>
       <c r="P845" s="5"/>
       <c r="Q845" s="4" t="s">
-        <v>3325</v>
+        <v>3333</v>
       </c>
       <c r="R845" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S845" s="4">
-        <v>399902.99</v>
+        <v>307743.64</v>
       </c>
       <c r="T845" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U845" s="4" t="s">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="V845" s="4" t="s">
-        <v>243</v>
+        <v>120</v>
       </c>
       <c r="W845" s="4">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="X845" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y845" s="4"/>
       <c r="Z845" s="4" t="s">
-        <v>3334</v>
+        <v>3335</v>
       </c>
       <c r="AA845" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="AB845" s="4" t="s">
         <v>61</v>
@@ -75357,13 +75336,13 @@
         <v>33</v>
       </c>
       <c r="C846" s="4">
-        <v>168725695</v>
+        <v>169988404</v>
       </c>
       <c r="D846" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E846" s="4">
-        <v>7798971</v>
+        <v>7635384</v>
       </c>
       <c r="F846" s="4" t="s">
         <v>140</v>
@@ -75378,17 +75357,17 @@
         <v>3094</v>
       </c>
       <c r="J846" s="4" t="s">
-        <v>3318</v>
+        <v>1194</v>
       </c>
       <c r="K846" s="4"/>
       <c r="L846" s="4" t="s">
-        <v>3335</v>
+        <v>855</v>
       </c>
       <c r="M846" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="N846" s="4">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="O846" s="4" t="s">
         <v>3336</v>
@@ -75398,32 +75377,28 @@
         <v>3337</v>
       </c>
       <c r="R846" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S846" s="4">
-        <v>307743.64</v>
+        <v>47039.24</v>
       </c>
       <c r="T846" s="4">
-        <v>3</v>
-      </c>
-      <c r="U846" s="4" t="s">
-        <v>3338</v>
-      </c>
-      <c r="V846" s="4" t="s">
-        <v>120</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U846" s="4"/>
+      <c r="V846" s="4"/>
       <c r="W846" s="4">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="X846" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y846" s="4"/>
       <c r="Z846" s="4" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="AA846" s="4" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="AB846" s="4" t="s">
         <v>61</v>
@@ -75437,13 +75412,13 @@
         <v>33</v>
       </c>
       <c r="C847" s="4">
-        <v>169988404</v>
+        <v>169487687</v>
       </c>
       <c r="D847" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E847" s="4">
-        <v>7635384</v>
+        <v>7293133</v>
       </c>
       <c r="F847" s="4" t="s">
         <v>140</v>
@@ -75462,45 +75437,41 @@
       </c>
       <c r="K847" s="4"/>
       <c r="L847" s="4" t="s">
-        <v>855</v>
+        <v>705</v>
       </c>
       <c r="M847" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="N847" s="4">
-        <v>24</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N847" s="4"/>
       <c r="O847" s="4" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="P847" s="5"/>
       <c r="Q847" s="4" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="R847" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S847" s="4">
-        <v>47039.24</v>
+        <v>0</v>
       </c>
       <c r="T847" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U847" s="4"/>
       <c r="V847" s="4"/>
       <c r="W847" s="4">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X847" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y847" s="4"/>
       <c r="Z847" s="4" t="s">
-        <v>3342</v>
-      </c>
-      <c r="AA847" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>3341</v>
+      </c>
+      <c r="AA847" s="4"/>
       <c r="AB847" s="4" t="s">
         <v>61</v>
       </c>
@@ -75513,13 +75484,13 @@
         <v>33</v>
       </c>
       <c r="C848" s="4">
-        <v>169829909</v>
+        <v>167347239</v>
       </c>
       <c r="D848" s="4" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="E848" s="4">
-        <v>6849464</v>
+        <v>7409197</v>
       </c>
       <c r="F848" s="4" t="s">
         <v>140</v>
@@ -75531,20 +75502,18 @@
         <v>3094</v>
       </c>
       <c r="I848" s="4" t="s">
-        <v>3094</v>
+        <v>3342</v>
       </c>
       <c r="J848" s="4" t="s">
-        <v>1194</v>
+        <v>3342</v>
       </c>
       <c r="K848" s="4"/>
       <c r="L848" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="M848" s="4" t="s">
-        <v>116</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="M848" s="4"/>
       <c r="N848" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O848" s="4" t="s">
         <v>3343</v>
@@ -75554,31 +75523,33 @@
         <v>3344</v>
       </c>
       <c r="R848" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S848" s="4">
-        <v>374101.81</v>
+        <v>4869737.28</v>
       </c>
       <c r="T848" s="4">
-        <v>3</v>
-      </c>
-      <c r="U848" s="4"/>
-      <c r="V848" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="U848" s="4" t="s">
+        <v>3345</v>
+      </c>
+      <c r="V848" s="4" t="s">
+        <v>217</v>
+      </c>
       <c r="W848" s="4">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="X848" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y848" s="4"/>
       <c r="Z848" s="4" t="s">
-        <v>3345</v>
-      </c>
-      <c r="AA848" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="AA848" s="4"/>
       <c r="AB848" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="849" spans="1:28">
@@ -75589,13 +75560,13 @@
         <v>33</v>
       </c>
       <c r="C849" s="4">
-        <v>169487687</v>
+        <v>167709123</v>
       </c>
       <c r="D849" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E849" s="4">
-        <v>7293133</v>
+        <v>5607771</v>
       </c>
       <c r="F849" s="4" t="s">
         <v>140</v>
@@ -75607,48 +75578,50 @@
         <v>3094</v>
       </c>
       <c r="I849" s="4" t="s">
-        <v>3094</v>
+        <v>3346</v>
       </c>
       <c r="J849" s="4" t="s">
-        <v>1194</v>
+        <v>3346</v>
       </c>
       <c r="K849" s="4"/>
-      <c r="L849" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="M849" s="4" t="s">
-        <v>206</v>
-      </c>
+      <c r="L849" s="4"/>
+      <c r="M849" s="4"/>
       <c r="N849" s="4"/>
       <c r="O849" s="4" t="s">
-        <v>3346</v>
+        <v>3347</v>
       </c>
       <c r="P849" s="5"/>
       <c r="Q849" s="4" t="s">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="R849" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S849" s="4">
-        <v>0</v>
+        <v>4274093.02</v>
       </c>
       <c r="T849" s="4">
-        <v>0</v>
-      </c>
-      <c r="U849" s="4"/>
-      <c r="V849" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="U849" s="4" t="s">
+        <v>3349</v>
+      </c>
+      <c r="V849" s="4" t="s">
+        <v>173</v>
+      </c>
       <c r="W849" s="4">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="X849" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y849" s="4"/>
       <c r="Z849" s="4" t="s">
-        <v>3348</v>
-      </c>
-      <c r="AA849" s="4"/>
+        <v>3350</v>
+      </c>
+      <c r="AA849" s="4" t="s">
+        <v>445</v>
+      </c>
       <c r="AB849" s="4" t="s">
         <v>61</v>
       </c>
@@ -75661,72 +75634,70 @@
         <v>33</v>
       </c>
       <c r="C850" s="4">
-        <v>167347239</v>
+        <v>166985500</v>
       </c>
       <c r="D850" s="4" t="s">
-        <v>103</v>
+        <v>364</v>
       </c>
       <c r="E850" s="4">
-        <v>7409197</v>
+        <v>8370701</v>
       </c>
       <c r="F850" s="4" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="G850" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H850" s="4" t="s">
-        <v>3094</v>
+        <v>3351</v>
       </c>
       <c r="I850" s="4" t="s">
-        <v>3349</v>
+        <v>3351</v>
       </c>
       <c r="J850" s="4" t="s">
-        <v>3349</v>
+        <v>3352</v>
       </c>
       <c r="K850" s="4"/>
       <c r="L850" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="M850" s="4"/>
+        <v>224</v>
+      </c>
+      <c r="M850" s="4" t="s">
+        <v>3353</v>
+      </c>
       <c r="N850" s="4">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="O850" s="4" t="s">
-        <v>3350</v>
+        <v>3354</v>
       </c>
       <c r="P850" s="5"/>
       <c r="Q850" s="4" t="s">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="R850" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S850" s="4">
-        <v>4869737.28</v>
+        <v>0</v>
       </c>
       <c r="T850" s="4">
-        <v>63</v>
-      </c>
-      <c r="U850" s="4" t="s">
-        <v>3352</v>
-      </c>
-      <c r="V850" s="4" t="s">
-        <v>217</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U850" s="4"/>
+      <c r="V850" s="4"/>
       <c r="W850" s="4">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="X850" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y850" s="4"/>
       <c r="Z850" s="4" t="s">
-        <v>109</v>
+        <v>3356</v>
       </c>
       <c r="AA850" s="4"/>
       <c r="AB850" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="851" spans="1:28">
@@ -75737,68 +75708,68 @@
         <v>33</v>
       </c>
       <c r="C851" s="4">
-        <v>167709123</v>
+        <v>166986360</v>
       </c>
       <c r="D851" s="4" t="s">
-        <v>50</v>
+        <v>364</v>
       </c>
       <c r="E851" s="4">
-        <v>5607771</v>
+        <v>8370708</v>
       </c>
       <c r="F851" s="4" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="G851" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H851" s="4" t="s">
-        <v>3094</v>
+        <v>3351</v>
       </c>
       <c r="I851" s="4" t="s">
+        <v>3351</v>
+      </c>
+      <c r="J851" s="4" t="s">
+        <v>3352</v>
+      </c>
+      <c r="K851" s="4"/>
+      <c r="L851" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="M851" s="4" t="s">
         <v>3353</v>
       </c>
-      <c r="J851" s="4" t="s">
-        <v>3353</v>
-      </c>
-      <c r="K851" s="4"/>
-      <c r="L851" s="4"/>
-      <c r="M851" s="4"/>
-      <c r="N851" s="4"/>
+      <c r="N851" s="4">
+        <v>7</v>
+      </c>
       <c r="O851" s="4" t="s">
-        <v>3354</v>
+        <v>3357</v>
       </c>
       <c r="P851" s="5"/>
       <c r="Q851" s="4" t="s">
         <v>3355</v>
       </c>
       <c r="R851" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="S851" s="4">
-        <v>4274093.02</v>
+        <v>2277764.52</v>
       </c>
       <c r="T851" s="4">
-        <v>26</v>
-      </c>
-      <c r="U851" s="4" t="s">
-        <v>3356</v>
-      </c>
-      <c r="V851" s="4" t="s">
-        <v>173</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="U851" s="4"/>
+      <c r="V851" s="4"/>
       <c r="W851" s="4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="X851" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y851" s="4"/>
       <c r="Z851" s="4" t="s">
-        <v>3357</v>
-      </c>
-      <c r="AA851" s="4" t="s">
-        <v>445</v>
-      </c>
+        <v>3358</v>
+      </c>
+      <c r="AA851" s="4"/>
       <c r="AB851" s="4" t="s">
         <v>61</v>
       </c>
@@ -75811,10 +75782,10 @@
         <v>33</v>
       </c>
       <c r="C852" s="4">
-        <v>166985500</v>
+        <v>170400653</v>
       </c>
       <c r="D852" s="4" t="s">
-        <v>364</v>
+        <v>34</v>
       </c>
       <c r="E852" s="4">
         <v>8370701</v>
@@ -75826,51 +75797,51 @@
         <v>36</v>
       </c>
       <c r="H852" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="I852" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="J852" s="4" t="s">
-        <v>3359</v>
+        <v>3352</v>
       </c>
       <c r="K852" s="4"/>
       <c r="L852" s="4" t="s">
         <v>224</v>
       </c>
       <c r="M852" s="4" t="s">
-        <v>3360</v>
+        <v>3353</v>
       </c>
       <c r="N852" s="4">
         <v>7</v>
       </c>
       <c r="O852" s="4" t="s">
-        <v>3361</v>
+        <v>3354</v>
       </c>
       <c r="P852" s="5"/>
       <c r="Q852" s="4" t="s">
-        <v>3362</v>
+        <v>3355</v>
       </c>
       <c r="R852" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S852" s="4">
-        <v>0</v>
+        <v>241005</v>
       </c>
       <c r="T852" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U852" s="4"/>
       <c r="V852" s="4"/>
       <c r="W852" s="4">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="X852" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y852" s="4"/>
       <c r="Z852" s="4" t="s">
-        <v>3363</v>
+        <v>3359</v>
       </c>
       <c r="AA852" s="4"/>
       <c r="AB852" s="4" t="s">
@@ -75885,13 +75856,13 @@
         <v>33</v>
       </c>
       <c r="C853" s="4">
-        <v>166986360</v>
+        <v>165796789</v>
       </c>
       <c r="D853" s="4" t="s">
-        <v>364</v>
+        <v>34</v>
       </c>
       <c r="E853" s="4">
-        <v>8370708</v>
+        <v>6265969</v>
       </c>
       <c r="F853" s="4" t="s">
         <v>35</v>
@@ -75900,51 +75871,53 @@
         <v>36</v>
       </c>
       <c r="H853" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="I853" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="J853" s="4" t="s">
-        <v>3359</v>
+        <v>3352</v>
       </c>
       <c r="K853" s="4"/>
       <c r="L853" s="4" t="s">
-        <v>224</v>
+        <v>156</v>
       </c>
       <c r="M853" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="N853" s="4"/>
+      <c r="O853" s="4" t="s">
         <v>3360</v>
-      </c>
-      <c r="N853" s="4">
-        <v>7</v>
-      </c>
-      <c r="O853" s="4" t="s">
-        <v>3364</v>
       </c>
       <c r="P853" s="5"/>
       <c r="Q853" s="4" t="s">
+        <v>3361</v>
+      </c>
+      <c r="R853" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S853" s="4">
+        <v>5354617.7</v>
+      </c>
+      <c r="T853" s="4">
+        <v>48</v>
+      </c>
+      <c r="U853" s="4" t="s">
         <v>3362</v>
       </c>
-      <c r="R853" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="S853" s="4">
-        <v>2277764.52</v>
-      </c>
-      <c r="T853" s="4">
-        <v>3</v>
-      </c>
-      <c r="U853" s="4"/>
-      <c r="V853" s="4"/>
+      <c r="V853" s="4" t="s">
+        <v>515</v>
+      </c>
       <c r="W853" s="4">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="X853" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y853" s="4"/>
       <c r="Z853" s="4" t="s">
-        <v>3365</v>
+        <v>3363</v>
       </c>
       <c r="AA853" s="4"/>
       <c r="AB853" s="4" t="s">
@@ -75959,13 +75932,13 @@
         <v>33</v>
       </c>
       <c r="C854" s="4">
-        <v>170400653</v>
+        <v>168888525</v>
       </c>
       <c r="D854" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E854" s="4">
-        <v>8370701</v>
+        <v>1336389</v>
       </c>
       <c r="F854" s="4" t="s">
         <v>35</v>
@@ -75974,44 +75947,42 @@
         <v>36</v>
       </c>
       <c r="H854" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="I854" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="J854" s="4" t="s">
-        <v>3359</v>
+        <v>1588</v>
       </c>
       <c r="K854" s="4"/>
       <c r="L854" s="4" t="s">
-        <v>224</v>
+        <v>110</v>
       </c>
       <c r="M854" s="4" t="s">
-        <v>3360</v>
-      </c>
-      <c r="N854" s="4">
-        <v>7</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N854" s="4"/>
       <c r="O854" s="4" t="s">
-        <v>3361</v>
+        <v>3364</v>
       </c>
       <c r="P854" s="5"/>
       <c r="Q854" s="4" t="s">
-        <v>3362</v>
+        <v>3365</v>
       </c>
       <c r="R854" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S854" s="4">
-        <v>241005</v>
+        <v>0</v>
       </c>
       <c r="T854" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U854" s="4"/>
       <c r="V854" s="4"/>
       <c r="W854" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="X854" s="4" t="s">
         <v>46</v>
@@ -76033,13 +76004,13 @@
         <v>33</v>
       </c>
       <c r="C855" s="4">
-        <v>165796789</v>
+        <v>169092476</v>
       </c>
       <c r="D855" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E855" s="4">
-        <v>6265969</v>
+        <v>5653487</v>
       </c>
       <c r="F855" s="4" t="s">
         <v>35</v>
@@ -76048,53 +76019,55 @@
         <v>36</v>
       </c>
       <c r="H855" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="I855" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="J855" s="4" t="s">
-        <v>3359</v>
+        <v>3367</v>
       </c>
       <c r="K855" s="4"/>
       <c r="L855" s="4" t="s">
-        <v>156</v>
+        <v>3065</v>
       </c>
       <c r="M855" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="N855" s="4"/>
+        <v>224</v>
+      </c>
+      <c r="N855" s="4">
+        <v>50</v>
+      </c>
       <c r="O855" s="4" t="s">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="P855" s="5"/>
       <c r="Q855" s="4" t="s">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="R855" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S855" s="4">
-        <v>5354617.7</v>
+        <v>0</v>
       </c>
       <c r="T855" s="4">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="U855" s="4" t="s">
-        <v>3369</v>
+        <v>3370</v>
       </c>
       <c r="V855" s="4" t="s">
-        <v>515</v>
+        <v>439</v>
       </c>
       <c r="W855" s="4">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="X855" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y855" s="4"/>
       <c r="Z855" s="4" t="s">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="AA855" s="4"/>
       <c r="AB855" s="4" t="s">
@@ -76109,13 +76082,13 @@
         <v>33</v>
       </c>
       <c r="C856" s="4">
-        <v>168888525</v>
+        <v>169821857</v>
       </c>
       <c r="D856" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E856" s="4">
-        <v>1336389</v>
+        <v>7623292</v>
       </c>
       <c r="F856" s="4" t="s">
         <v>35</v>
@@ -76124,49 +76097,55 @@
         <v>36</v>
       </c>
       <c r="H856" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="I856" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="J856" s="4" t="s">
-        <v>1588</v>
+        <v>3372</v>
       </c>
       <c r="K856" s="4"/>
       <c r="L856" s="4" t="s">
-        <v>110</v>
+        <v>2485</v>
       </c>
       <c r="M856" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="N856" s="4"/>
+        <v>148</v>
+      </c>
+      <c r="N856" s="4">
+        <v>25</v>
+      </c>
       <c r="O856" s="4" t="s">
-        <v>3371</v>
+        <v>3373</v>
       </c>
       <c r="P856" s="5"/>
       <c r="Q856" s="4" t="s">
-        <v>3372</v>
+        <v>3374</v>
       </c>
       <c r="R856" s="4" t="s">
         <v>56</v>
       </c>
       <c r="S856" s="4">
-        <v>0</v>
+        <v>3920332.09</v>
       </c>
       <c r="T856" s="4">
-        <v>0</v>
-      </c>
-      <c r="U856" s="4"/>
-      <c r="V856" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="U856" s="4" t="s">
+        <v>3375</v>
+      </c>
+      <c r="V856" s="4" t="s">
+        <v>173</v>
+      </c>
       <c r="W856" s="4">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="X856" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y856" s="4"/>
       <c r="Z856" s="4" t="s">
-        <v>3373</v>
+        <v>3376</v>
       </c>
       <c r="AA856" s="4"/>
       <c r="AB856" s="4" t="s">
@@ -76181,13 +76160,13 @@
         <v>33</v>
       </c>
       <c r="C857" s="4">
-        <v>169092476</v>
+        <v>167328603</v>
       </c>
       <c r="D857" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E857" s="4">
-        <v>5653487</v>
+        <v>1117251</v>
       </c>
       <c r="F857" s="4" t="s">
         <v>35</v>
@@ -76196,30 +76175,28 @@
         <v>36</v>
       </c>
       <c r="H857" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="I857" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="J857" s="4" t="s">
-        <v>3374</v>
+        <v>3372</v>
       </c>
       <c r="K857" s="4"/>
       <c r="L857" s="4" t="s">
-        <v>3065</v>
+        <v>148</v>
       </c>
       <c r="M857" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="N857" s="4">
-        <v>50</v>
-      </c>
+        <v>2467</v>
+      </c>
+      <c r="N857" s="4"/>
       <c r="O857" s="4" t="s">
-        <v>3375</v>
+        <v>3377</v>
       </c>
       <c r="P857" s="5"/>
       <c r="Q857" s="4" t="s">
-        <v>3376</v>
+        <v>3378</v>
       </c>
       <c r="R857" s="4" t="s">
         <v>56</v>
@@ -76231,22 +76208,24 @@
         <v>0</v>
       </c>
       <c r="U857" s="4" t="s">
-        <v>3377</v>
+        <v>3379</v>
       </c>
       <c r="V857" s="4" t="s">
-        <v>439</v>
+        <v>45</v>
       </c>
       <c r="W857" s="4">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="X857" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y857" s="4"/>
       <c r="Z857" s="4" t="s">
-        <v>3378</v>
-      </c>
-      <c r="AA857" s="4"/>
+        <v>3380</v>
+      </c>
+      <c r="AA857" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="AB857" s="4" t="s">
         <v>61</v>
       </c>
@@ -76259,13 +76238,13 @@
         <v>33</v>
       </c>
       <c r="C858" s="4">
-        <v>169821857</v>
+        <v>167009144</v>
       </c>
       <c r="D858" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E858" s="4">
-        <v>7623292</v>
+        <v>6747980</v>
       </c>
       <c r="F858" s="4" t="s">
         <v>35</v>
@@ -76274,55 +76253,53 @@
         <v>36</v>
       </c>
       <c r="H858" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="I858" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="J858" s="4" t="s">
-        <v>3379</v>
+        <v>3372</v>
       </c>
       <c r="K858" s="4"/>
       <c r="L858" s="4" t="s">
-        <v>2485</v>
+        <v>148</v>
       </c>
       <c r="M858" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="N858" s="4">
-        <v>25</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N858" s="4"/>
       <c r="O858" s="4" t="s">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="P858" s="5"/>
       <c r="Q858" s="4" t="s">
-        <v>3381</v>
+        <v>3382</v>
       </c>
       <c r="R858" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S858" s="4">
-        <v>3920332.09</v>
+        <v>10011293.94</v>
       </c>
       <c r="T858" s="4">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="U858" s="4" t="s">
-        <v>3382</v>
+        <v>3383</v>
       </c>
       <c r="V858" s="4" t="s">
         <v>173</v>
       </c>
       <c r="W858" s="4">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="X858" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y858" s="4"/>
       <c r="Z858" s="4" t="s">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="AA858" s="4"/>
       <c r="AB858" s="4" t="s">
@@ -76337,13 +76314,13 @@
         <v>33</v>
       </c>
       <c r="C859" s="4">
-        <v>167328603</v>
+        <v>170423305</v>
       </c>
       <c r="D859" s="4" t="s">
-        <v>50</v>
+        <v>417</v>
       </c>
       <c r="E859" s="4">
-        <v>1117251</v>
+        <v>8400324</v>
       </c>
       <c r="F859" s="4" t="s">
         <v>35</v>
@@ -76352,28 +76329,24 @@
         <v>36</v>
       </c>
       <c r="H859" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="I859" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="J859" s="4" t="s">
-        <v>3379</v>
+        <v>1073</v>
       </c>
       <c r="K859" s="4"/>
-      <c r="L859" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="M859" s="4" t="s">
-        <v>2467</v>
-      </c>
+      <c r="L859" s="4"/>
+      <c r="M859" s="4"/>
       <c r="N859" s="4"/>
       <c r="O859" s="4" t="s">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="P859" s="5"/>
       <c r="Q859" s="4" t="s">
-        <v>3385</v>
+        <v>3386</v>
       </c>
       <c r="R859" s="4" t="s">
         <v>56</v>
@@ -76384,14 +76357,10 @@
       <c r="T859" s="4">
         <v>0</v>
       </c>
-      <c r="U859" s="4" t="s">
-        <v>3386</v>
-      </c>
-      <c r="V859" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="U859" s="4"/>
+      <c r="V859" s="4"/>
       <c r="W859" s="4">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="X859" s="4" t="s">
         <v>46</v>
@@ -76400,11 +76369,9 @@
       <c r="Z859" s="4" t="s">
         <v>3387</v>
       </c>
-      <c r="AA859" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="AA859" s="4"/>
       <c r="AB859" s="4" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
     </row>
     <row r="860" spans="1:28">
@@ -76415,13 +76382,13 @@
         <v>33</v>
       </c>
       <c r="C860" s="4">
-        <v>167009144</v>
+        <v>164808120</v>
       </c>
       <c r="D860" s="4" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="E860" s="4">
-        <v>6747980</v>
+        <v>6265736</v>
       </c>
       <c r="F860" s="4" t="s">
         <v>35</v>
@@ -76430,53 +76397,53 @@
         <v>36</v>
       </c>
       <c r="H860" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="I860" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="J860" s="4" t="s">
-        <v>3379</v>
+        <v>1073</v>
       </c>
       <c r="K860" s="4"/>
       <c r="L860" s="4" t="s">
-        <v>148</v>
+        <v>453</v>
       </c>
       <c r="M860" s="4" t="s">
-        <v>156</v>
+        <v>3388</v>
       </c>
       <c r="N860" s="4"/>
       <c r="O860" s="4" t="s">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="P860" s="5"/>
       <c r="Q860" s="4" t="s">
-        <v>3389</v>
+        <v>3390</v>
       </c>
       <c r="R860" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S860" s="4">
-        <v>10011293.94</v>
+        <v>3817749.56</v>
       </c>
       <c r="T860" s="4">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="U860" s="4" t="s">
-        <v>3390</v>
+        <v>3391</v>
       </c>
       <c r="V860" s="4" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="W860" s="4">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="X860" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y860" s="4"/>
       <c r="Z860" s="4" t="s">
-        <v>3391</v>
+        <v>109</v>
       </c>
       <c r="AA860" s="4"/>
       <c r="AB860" s="4" t="s">
@@ -76491,13 +76458,13 @@
         <v>33</v>
       </c>
       <c r="C861" s="4">
-        <v>170423305</v>
+        <v>167028650</v>
       </c>
       <c r="D861" s="4" t="s">
-        <v>417</v>
+        <v>103</v>
       </c>
       <c r="E861" s="4">
-        <v>8400324</v>
+        <v>5664526</v>
       </c>
       <c r="F861" s="4" t="s">
         <v>35</v>
@@ -76506,17 +76473,21 @@
         <v>36</v>
       </c>
       <c r="H861" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="I861" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="J861" s="4" t="s">
         <v>1073</v>
       </c>
       <c r="K861" s="4"/>
-      <c r="L861" s="4"/>
-      <c r="M861" s="4"/>
+      <c r="L861" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="M861" s="4" t="s">
+        <v>193</v>
+      </c>
       <c r="N861" s="4"/>
       <c r="O861" s="4" t="s">
         <v>3392</v>
@@ -76526,29 +76497,33 @@
         <v>3393</v>
       </c>
       <c r="R861" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="S861" s="4">
-        <v>0</v>
+        <v>7062.05</v>
       </c>
       <c r="T861" s="4">
-        <v>0</v>
-      </c>
-      <c r="U861" s="4"/>
-      <c r="V861" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U861" s="4" t="s">
+        <v>3394</v>
+      </c>
+      <c r="V861" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="W861" s="4">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="X861" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y861" s="4"/>
       <c r="Z861" s="4" t="s">
-        <v>3394</v>
+        <v>109</v>
       </c>
       <c r="AA861" s="4"/>
       <c r="AB861" s="4" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
     </row>
     <row r="862" spans="1:28">
@@ -76556,73 +76531,75 @@
         <v>1000</v>
       </c>
       <c r="B862" s="4" t="s">
-        <v>33</v>
+        <v>590</v>
       </c>
       <c r="C862" s="4">
-        <v>164808120</v>
+        <v>170209996</v>
       </c>
       <c r="D862" s="4" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="E862" s="4">
-        <v>6265736</v>
+        <v>6262508</v>
       </c>
       <c r="F862" s="4" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="G862" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H862" s="4" t="s">
-        <v>3358</v>
+        <v>3395</v>
       </c>
       <c r="I862" s="4" t="s">
-        <v>3358</v>
+        <v>3395</v>
       </c>
       <c r="J862" s="4" t="s">
-        <v>1073</v>
+        <v>3396</v>
       </c>
       <c r="K862" s="4"/>
       <c r="L862" s="4" t="s">
-        <v>453</v>
+        <v>2467</v>
       </c>
       <c r="M862" s="4" t="s">
-        <v>3395</v>
+        <v>157</v>
       </c>
       <c r="N862" s="4"/>
       <c r="O862" s="4" t="s">
-        <v>3396</v>
+        <v>3397</v>
       </c>
       <c r="P862" s="5"/>
       <c r="Q862" s="4" t="s">
-        <v>3397</v>
+        <v>3398</v>
       </c>
       <c r="R862" s="4" t="s">
         <v>72</v>
       </c>
       <c r="S862" s="4">
-        <v>3817749.56</v>
+        <v>0</v>
       </c>
       <c r="T862" s="4">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="U862" s="4" t="s">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="V862" s="4" t="s">
         <v>217</v>
       </c>
       <c r="W862" s="4">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="X862" s="4" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="Y862" s="4"/>
       <c r="Z862" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA862" s="4"/>
+        <v>3400</v>
+      </c>
+      <c r="AA862" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="AB862" s="4" t="s">
         <v>61</v>
       </c>
@@ -76635,70 +76612,70 @@
         <v>33</v>
       </c>
       <c r="C863" s="4">
-        <v>167028650</v>
+        <v>170416264</v>
       </c>
       <c r="D863" s="4" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="E863" s="4">
-        <v>5664526</v>
+        <v>5603011</v>
       </c>
       <c r="F863" s="4" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="G863" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H863" s="4" t="s">
-        <v>3358</v>
+        <v>3395</v>
       </c>
       <c r="I863" s="4" t="s">
-        <v>3358</v>
+        <v>3395</v>
       </c>
       <c r="J863" s="4" t="s">
-        <v>1073</v>
+        <v>906</v>
       </c>
       <c r="K863" s="4"/>
       <c r="L863" s="4" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="M863" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="N863" s="4"/>
+        <v>53</v>
+      </c>
+      <c r="N863" s="4">
+        <v>5</v>
+      </c>
       <c r="O863" s="4" t="s">
-        <v>3399</v>
+        <v>3401</v>
       </c>
       <c r="P863" s="5"/>
       <c r="Q863" s="4" t="s">
-        <v>3400</v>
+        <v>3402</v>
       </c>
       <c r="R863" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="S863" s="4">
-        <v>7062.05</v>
+        <v>1892491.87</v>
       </c>
       <c r="T863" s="4">
         <v>1</v>
       </c>
-      <c r="U863" s="4" t="s">
-        <v>3401</v>
-      </c>
-      <c r="V863" s="4" t="s">
-        <v>153</v>
-      </c>
+      <c r="U863" s="4"/>
+      <c r="V863" s="4"/>
       <c r="W863" s="4">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="X863" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y863" s="4"/>
       <c r="Z863" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA863" s="4"/>
+        <v>3403</v>
+      </c>
+      <c r="AA863" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB863" s="4" t="s">
         <v>61</v>
       </c>
@@ -76708,16 +76685,16 @@
         <v>1000</v>
       </c>
       <c r="B864" s="4" t="s">
-        <v>590</v>
+        <v>33</v>
       </c>
       <c r="C864" s="4">
-        <v>170209996</v>
+        <v>170403907</v>
       </c>
       <c r="D864" s="4" t="s">
-        <v>50</v>
+        <v>286</v>
       </c>
       <c r="E864" s="4">
-        <v>6262508</v>
+        <v>5601040</v>
       </c>
       <c r="F864" s="4" t="s">
         <v>140</v>
@@ -76726,28 +76703,28 @@
         <v>36</v>
       </c>
       <c r="H864" s="4" t="s">
-        <v>3402</v>
+        <v>3404</v>
       </c>
       <c r="I864" s="4" t="s">
-        <v>3402</v>
+        <v>3405</v>
       </c>
       <c r="J864" s="4" t="s">
-        <v>3403</v>
+        <v>3406</v>
       </c>
       <c r="K864" s="4"/>
       <c r="L864" s="4" t="s">
-        <v>2467</v>
+        <v>82</v>
       </c>
       <c r="M864" s="4" t="s">
-        <v>157</v>
+        <v>705</v>
       </c>
       <c r="N864" s="4"/>
       <c r="O864" s="4" t="s">
-        <v>3404</v>
+        <v>3407</v>
       </c>
       <c r="P864" s="5"/>
       <c r="Q864" s="4" t="s">
-        <v>3405</v>
+        <v>3408</v>
       </c>
       <c r="R864" s="4" t="s">
         <v>72</v>
@@ -76758,24 +76735,20 @@
       <c r="T864" s="4">
         <v>0</v>
       </c>
-      <c r="U864" s="4" t="s">
-        <v>3406</v>
-      </c>
-      <c r="V864" s="4" t="s">
-        <v>217</v>
-      </c>
+      <c r="U864" s="4"/>
+      <c r="V864" s="4"/>
       <c r="W864" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X864" s="4" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="Y864" s="4"/>
       <c r="Z864" s="4" t="s">
-        <v>3407</v>
+        <v>3409</v>
       </c>
       <c r="AA864" s="4" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="AB864" s="4" t="s">
         <v>61</v>
@@ -76789,13 +76762,13 @@
         <v>33</v>
       </c>
       <c r="C865" s="4">
-        <v>170416264</v>
+        <v>170323984</v>
       </c>
       <c r="D865" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E865" s="4">
-        <v>5603011</v>
+        <v>8029205</v>
       </c>
       <c r="F865" s="4" t="s">
         <v>140</v>
@@ -76804,36 +76777,36 @@
         <v>36</v>
       </c>
       <c r="H865" s="4" t="s">
-        <v>3402</v>
+        <v>3404</v>
       </c>
       <c r="I865" s="4" t="s">
-        <v>3402</v>
+        <v>3405</v>
       </c>
       <c r="J865" s="4" t="s">
-        <v>906</v>
+        <v>3410</v>
       </c>
       <c r="K865" s="4"/>
       <c r="L865" s="4" t="s">
-        <v>122</v>
+        <v>281</v>
       </c>
       <c r="M865" s="4" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="N865" s="4">
         <v>5</v>
       </c>
       <c r="O865" s="4" t="s">
-        <v>3408</v>
+        <v>3411</v>
       </c>
       <c r="P865" s="5"/>
       <c r="Q865" s="4" t="s">
-        <v>3409</v>
+        <v>3412</v>
       </c>
       <c r="R865" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S865" s="4">
-        <v>1892491.87</v>
+        <v>180277.94</v>
       </c>
       <c r="T865" s="4">
         <v>1</v>
@@ -76841,14 +76814,14 @@
       <c r="U865" s="4"/>
       <c r="V865" s="4"/>
       <c r="W865" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X865" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y865" s="4"/>
       <c r="Z865" s="4" t="s">
-        <v>3410</v>
+        <v>3413</v>
       </c>
       <c r="AA865" s="4" t="s">
         <v>79</v>
@@ -76865,13 +76838,13 @@
         <v>33</v>
       </c>
       <c r="C866" s="4">
-        <v>170403907</v>
+        <v>170415204</v>
       </c>
       <c r="D866" s="4" t="s">
-        <v>286</v>
+        <v>103</v>
       </c>
       <c r="E866" s="4">
-        <v>5601040</v>
+        <v>8023961</v>
       </c>
       <c r="F866" s="4" t="s">
         <v>140</v>
@@ -76880,22 +76853,24 @@
         <v>36</v>
       </c>
       <c r="H866" s="4" t="s">
-        <v>3411</v>
+        <v>3404</v>
       </c>
       <c r="I866" s="4" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="J866" s="4" t="s">
-        <v>3413</v>
+        <v>3410</v>
       </c>
       <c r="K866" s="4"/>
       <c r="L866" s="4" t="s">
-        <v>82</v>
+        <v>704</v>
       </c>
       <c r="M866" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="N866" s="4"/>
+        <v>105</v>
+      </c>
+      <c r="N866" s="4">
+        <v>50</v>
+      </c>
       <c r="O866" s="4" t="s">
         <v>3414</v>
       </c>
@@ -76922,11 +76897,9 @@
       </c>
       <c r="Y866" s="4"/>
       <c r="Z866" s="4" t="s">
-        <v>3416</v>
-      </c>
-      <c r="AA866" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="AA866" s="4"/>
       <c r="AB866" s="4" t="s">
         <v>61</v>
       </c>
@@ -76936,16 +76909,16 @@
         <v>1000</v>
       </c>
       <c r="B867" s="4" t="s">
-        <v>33</v>
+        <v>590</v>
       </c>
       <c r="C867" s="4">
-        <v>170323984</v>
+        <v>170486293</v>
       </c>
       <c r="D867" s="4" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="E867" s="4">
-        <v>8029205</v>
+        <v>5659891</v>
       </c>
       <c r="F867" s="4" t="s">
         <v>140</v>
@@ -76954,51 +76927,49 @@
         <v>36</v>
       </c>
       <c r="H867" s="4" t="s">
-        <v>3411</v>
+        <v>3404</v>
       </c>
       <c r="I867" s="4" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="J867" s="4" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="K867" s="4"/>
       <c r="L867" s="4" t="s">
-        <v>281</v>
+        <v>566</v>
       </c>
       <c r="M867" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="N867" s="4">
-        <v>5</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N867" s="4"/>
       <c r="O867" s="4" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="P867" s="5"/>
       <c r="Q867" s="4" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="R867" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S867" s="4">
-        <v>180277.94</v>
+        <v>0</v>
       </c>
       <c r="T867" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U867" s="4"/>
       <c r="V867" s="4"/>
       <c r="W867" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X867" s="4" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="Y867" s="4"/>
       <c r="Z867" s="4" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="AA867" s="4" t="s">
         <v>79</v>
@@ -77015,13 +76986,13 @@
         <v>33</v>
       </c>
       <c r="C868" s="4">
-        <v>170415204</v>
+        <v>170494808</v>
       </c>
       <c r="D868" s="4" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="E868" s="4">
-        <v>8023961</v>
+        <v>7705610</v>
       </c>
       <c r="F868" s="4" t="s">
         <v>140</v>
@@ -77030,53 +77001,57 @@
         <v>36</v>
       </c>
       <c r="H868" s="4" t="s">
-        <v>3411</v>
+        <v>3404</v>
       </c>
       <c r="I868" s="4" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="J868" s="4" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="K868" s="4"/>
       <c r="L868" s="4" t="s">
-        <v>704</v>
+        <v>566</v>
       </c>
       <c r="M868" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="N868" s="4">
-        <v>50</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N868" s="4"/>
       <c r="O868" s="4" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="P868" s="5"/>
       <c r="Q868" s="4" t="s">
+        <v>3421</v>
+      </c>
+      <c r="R868" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="S868" s="4">
+        <v>0</v>
+      </c>
+      <c r="T868" s="4">
+        <v>0</v>
+      </c>
+      <c r="U868" s="4" t="s">
         <v>3422</v>
       </c>
-      <c r="R868" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="S868" s="4">
-        <v>0</v>
-      </c>
-      <c r="T868" s="4">
-        <v>0</v>
-      </c>
-      <c r="U868" s="4"/>
-      <c r="V868" s="4"/>
+      <c r="V868" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="W868" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X868" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y868" s="4"/>
       <c r="Z868" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA868" s="4"/>
+        <v>3423</v>
+      </c>
+      <c r="AA868" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="AB868" s="4" t="s">
         <v>61</v>
       </c>
@@ -77089,13 +77064,13 @@
         <v>590</v>
       </c>
       <c r="C869" s="4">
-        <v>170486293</v>
+        <v>170177663</v>
       </c>
       <c r="D869" s="4" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="E869" s="4">
-        <v>5659891</v>
+        <v>5613560</v>
       </c>
       <c r="F869" s="4" t="s">
         <v>140</v>
@@ -77104,20 +77079,20 @@
         <v>36</v>
       </c>
       <c r="H869" s="4" t="s">
-        <v>3411</v>
+        <v>3404</v>
       </c>
       <c r="I869" s="4" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="J869" s="4" t="s">
-        <v>3423</v>
+        <v>928</v>
       </c>
       <c r="K869" s="4"/>
       <c r="L869" s="4" t="s">
-        <v>566</v>
+        <v>224</v>
       </c>
       <c r="M869" s="4" t="s">
-        <v>177</v>
+        <v>335</v>
       </c>
       <c r="N869" s="4"/>
       <c r="O869" s="4" t="s">
@@ -77131,25 +77106,29 @@
         <v>56</v>
       </c>
       <c r="S869" s="4">
-        <v>0</v>
+        <v>61796.29</v>
       </c>
       <c r="T869" s="4">
-        <v>0</v>
-      </c>
-      <c r="U869" s="4"/>
-      <c r="V869" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="U869" s="4" t="s">
+        <v>3426</v>
+      </c>
+      <c r="V869" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="W869" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X869" s="4" t="s">
         <v>182</v>
       </c>
       <c r="Y869" s="4"/>
       <c r="Z869" s="4" t="s">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="AA869" s="4" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="AB869" s="4" t="s">
         <v>61</v>
@@ -77163,13 +77142,13 @@
         <v>33</v>
       </c>
       <c r="C870" s="4">
-        <v>170494808</v>
+        <v>170399493</v>
       </c>
       <c r="D870" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E870" s="4">
-        <v>7705610</v>
+        <v>5613472</v>
       </c>
       <c r="F870" s="4" t="s">
         <v>140</v>
@@ -77178,59 +77157,59 @@
         <v>36</v>
       </c>
       <c r="H870" s="4" t="s">
-        <v>3411</v>
+        <v>3404</v>
       </c>
       <c r="I870" s="4" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="J870" s="4" t="s">
-        <v>3423</v>
+        <v>928</v>
       </c>
       <c r="K870" s="4"/>
       <c r="L870" s="4" t="s">
         <v>566</v>
       </c>
       <c r="M870" s="4" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="N870" s="4"/>
       <c r="O870" s="4" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="P870" s="5"/>
       <c r="Q870" s="4" t="s">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="R870" s="4" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="S870" s="4">
-        <v>0</v>
+        <v>250707.93</v>
       </c>
       <c r="T870" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U870" s="4" t="s">
-        <v>3429</v>
+        <v>3430</v>
       </c>
       <c r="V870" s="4" t="s">
         <v>45</v>
       </c>
       <c r="W870" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X870" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y870" s="4"/>
       <c r="Z870" s="4" t="s">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="AA870" s="4" t="s">
         <v>60</v>
       </c>
       <c r="AB870" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="871" spans="1:28">
@@ -77241,13 +77220,13 @@
         <v>590</v>
       </c>
       <c r="C871" s="4">
-        <v>170177663</v>
+        <v>170493990</v>
       </c>
       <c r="D871" s="4" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="E871" s="4">
-        <v>5613560</v>
+        <v>5613065</v>
       </c>
       <c r="F871" s="4" t="s">
         <v>140</v>
@@ -77256,46 +77235,42 @@
         <v>36</v>
       </c>
       <c r="H871" s="4" t="s">
-        <v>3411</v>
+        <v>3404</v>
       </c>
       <c r="I871" s="4" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="J871" s="4" t="s">
         <v>928</v>
       </c>
       <c r="K871" s="4"/>
       <c r="L871" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M871" s="4" t="s">
-        <v>335</v>
+        <v>122</v>
       </c>
       <c r="N871" s="4"/>
       <c r="O871" s="4" t="s">
-        <v>3431</v>
+        <v>3432</v>
       </c>
       <c r="P871" s="5"/>
       <c r="Q871" s="4" t="s">
-        <v>3432</v>
+        <v>3433</v>
       </c>
       <c r="R871" s="4" t="s">
         <v>56</v>
       </c>
       <c r="S871" s="4">
-        <v>61796.29</v>
+        <v>0</v>
       </c>
       <c r="T871" s="4">
-        <v>2</v>
-      </c>
-      <c r="U871" s="4" t="s">
-        <v>3433</v>
-      </c>
-      <c r="V871" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U871" s="4"/>
+      <c r="V871" s="4"/>
       <c r="W871" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X871" s="4" t="s">
         <v>182</v>
@@ -77305,7 +77280,7 @@
         <v>3434</v>
       </c>
       <c r="AA871" s="4" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AB871" s="4" t="s">
         <v>61</v>
@@ -77319,13 +77294,13 @@
         <v>33</v>
       </c>
       <c r="C872" s="4">
-        <v>170399493</v>
+        <v>170355425</v>
       </c>
       <c r="D872" s="4" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="E872" s="4">
-        <v>5613472</v>
+        <v>5613029</v>
       </c>
       <c r="F872" s="4" t="s">
         <v>140</v>
@@ -77334,20 +77309,20 @@
         <v>36</v>
       </c>
       <c r="H872" s="4" t="s">
-        <v>3411</v>
+        <v>3404</v>
       </c>
       <c r="I872" s="4" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="J872" s="4" t="s">
         <v>928</v>
       </c>
       <c r="K872" s="4"/>
       <c r="L872" s="4" t="s">
-        <v>566</v>
+        <v>194</v>
       </c>
       <c r="M872" s="4" t="s">
-        <v>194</v>
+        <v>766</v>
       </c>
       <c r="N872" s="4"/>
       <c r="O872" s="4" t="s">
@@ -77361,32 +77336,28 @@
         <v>56</v>
       </c>
       <c r="S872" s="4">
-        <v>250707.93</v>
+        <v>0</v>
       </c>
       <c r="T872" s="4">
+        <v>0</v>
+      </c>
+      <c r="U872" s="4"/>
+      <c r="V872" s="4"/>
+      <c r="W872" s="4">
         <v>3</v>
-      </c>
-      <c r="U872" s="4" t="s">
-        <v>3437</v>
-      </c>
-      <c r="V872" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W872" s="4">
-        <v>2</v>
       </c>
       <c r="X872" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y872" s="4"/>
       <c r="Z872" s="4" t="s">
-        <v>3438</v>
+        <v>174</v>
       </c>
       <c r="AA872" s="4" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="AB872" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="873" spans="1:28">
@@ -77394,16 +77365,16 @@
         <v>1000</v>
       </c>
       <c r="B873" s="4" t="s">
-        <v>590</v>
+        <v>33</v>
       </c>
       <c r="C873" s="4">
-        <v>170493990</v>
+        <v>170406503</v>
       </c>
       <c r="D873" s="4" t="s">
-        <v>115</v>
+        <v>286</v>
       </c>
       <c r="E873" s="4">
-        <v>5613065</v>
+        <v>5613329</v>
       </c>
       <c r="F873" s="4" t="s">
         <v>140</v>
@@ -77412,28 +77383,28 @@
         <v>36</v>
       </c>
       <c r="H873" s="4" t="s">
-        <v>3411</v>
+        <v>3404</v>
       </c>
       <c r="I873" s="4" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="J873" s="4" t="s">
-        <v>928</v>
+        <v>1165</v>
       </c>
       <c r="K873" s="4"/>
       <c r="L873" s="4" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="M873" s="4" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="N873" s="4"/>
       <c r="O873" s="4" t="s">
-        <v>3439</v>
+        <v>3437</v>
       </c>
       <c r="P873" s="5"/>
       <c r="Q873" s="4" t="s">
-        <v>3440</v>
+        <v>3438</v>
       </c>
       <c r="R873" s="4" t="s">
         <v>56</v>
@@ -77447,18 +77418,16 @@
       <c r="U873" s="4"/>
       <c r="V873" s="4"/>
       <c r="W873" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X873" s="4" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="Y873" s="4"/>
       <c r="Z873" s="4" t="s">
-        <v>3441</v>
-      </c>
-      <c r="AA873" s="4" t="s">
-        <v>60</v>
-      </c>
+        <v>3439</v>
+      </c>
+      <c r="AA873" s="4"/>
       <c r="AB873" s="4" t="s">
         <v>61</v>
       </c>
@@ -77471,13 +77440,13 @@
         <v>33</v>
       </c>
       <c r="C874" s="4">
-        <v>170355425</v>
+        <v>170505174</v>
       </c>
       <c r="D874" s="4" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E874" s="4">
-        <v>5613029</v>
+        <v>1098787</v>
       </c>
       <c r="F874" s="4" t="s">
         <v>140</v>
@@ -77486,28 +77455,28 @@
         <v>36</v>
       </c>
       <c r="H874" s="4" t="s">
-        <v>3411</v>
+        <v>3404</v>
       </c>
       <c r="I874" s="4" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="J874" s="4" t="s">
-        <v>928</v>
+        <v>3440</v>
       </c>
       <c r="K874" s="4"/>
       <c r="L874" s="4" t="s">
-        <v>194</v>
+        <v>617</v>
       </c>
       <c r="M874" s="4" t="s">
-        <v>766</v>
+        <v>320</v>
       </c>
       <c r="N874" s="4"/>
       <c r="O874" s="4" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="P874" s="5"/>
       <c r="Q874" s="4" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="R874" s="4" t="s">
         <v>56</v>
@@ -77521,14 +77490,14 @@
       <c r="U874" s="4"/>
       <c r="V874" s="4"/>
       <c r="W874" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X874" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y874" s="4"/>
       <c r="Z874" s="4" t="s">
-        <v>174</v>
+        <v>3443</v>
       </c>
       <c r="AA874" s="4" t="s">
         <v>79</v>
@@ -77545,13 +77514,13 @@
         <v>33</v>
       </c>
       <c r="C875" s="4">
-        <v>170406503</v>
+        <v>170524918</v>
       </c>
       <c r="D875" s="4" t="s">
-        <v>286</v>
+        <v>50</v>
       </c>
       <c r="E875" s="4">
-        <v>5613329</v>
+        <v>5615101</v>
       </c>
       <c r="F875" s="4" t="s">
         <v>140</v>
@@ -77560,22 +77529,24 @@
         <v>36</v>
       </c>
       <c r="H875" s="4" t="s">
-        <v>3411</v>
+        <v>3404</v>
       </c>
       <c r="I875" s="4" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="J875" s="4" t="s">
-        <v>1165</v>
+        <v>3440</v>
       </c>
       <c r="K875" s="4"/>
       <c r="L875" s="4" t="s">
-        <v>193</v>
+        <v>617</v>
       </c>
       <c r="M875" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="N875" s="4"/>
+        <v>320</v>
+      </c>
+      <c r="N875" s="4">
+        <v>88</v>
+      </c>
       <c r="O875" s="4" t="s">
         <v>3444</v>
       </c>
@@ -77595,7 +77566,7 @@
       <c r="U875" s="4"/>
       <c r="V875" s="4"/>
       <c r="W875" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X875" s="4" t="s">
         <v>46</v>
@@ -77604,9 +77575,11 @@
       <c r="Z875" s="4" t="s">
         <v>3446</v>
       </c>
-      <c r="AA875" s="4"/>
+      <c r="AA875" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AB875" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="876" spans="1:28">
@@ -77617,46 +77590,48 @@
         <v>33</v>
       </c>
       <c r="C876" s="4">
-        <v>170505174</v>
+        <v>167227156</v>
       </c>
       <c r="D876" s="4" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="E876" s="4">
-        <v>1098787</v>
+        <v>1130632</v>
       </c>
       <c r="F876" s="4" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="G876" s="4" t="s">
-        <v>36</v>
+        <v>3447</v>
       </c>
       <c r="H876" s="4" t="s">
-        <v>3411</v>
+        <v>3448</v>
       </c>
       <c r="I876" s="4" t="s">
-        <v>3412</v>
+        <v>3448</v>
       </c>
       <c r="J876" s="4" t="s">
-        <v>3447</v>
+        <v>411</v>
       </c>
       <c r="K876" s="4"/>
       <c r="L876" s="4" t="s">
-        <v>617</v>
+        <v>352</v>
       </c>
       <c r="M876" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="N876" s="4"/>
+        <v>105</v>
+      </c>
+      <c r="N876" s="4">
+        <v>49</v>
+      </c>
       <c r="O876" s="4" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="P876" s="5"/>
       <c r="Q876" s="4" t="s">
-        <v>3449</v>
+        <v>3450</v>
       </c>
       <c r="R876" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S876" s="4">
         <v>0</v>
@@ -77664,20 +77639,24 @@
       <c r="T876" s="4">
         <v>0</v>
       </c>
-      <c r="U876" s="4"/>
-      <c r="V876" s="4"/>
+      <c r="U876" s="4" t="s">
+        <v>3451</v>
+      </c>
+      <c r="V876" s="4" t="s">
+        <v>217</v>
+      </c>
       <c r="W876" s="4">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="X876" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y876" s="4"/>
       <c r="Z876" s="4" t="s">
-        <v>3450</v>
+        <v>3452</v>
       </c>
       <c r="AA876" s="4" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="AB876" s="4" t="s">
         <v>61</v>
@@ -77691,231 +77670,75 @@
         <v>33</v>
       </c>
       <c r="C877" s="4">
-        <v>170524918</v>
+        <v>168526053</v>
       </c>
       <c r="D877" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E877" s="4">
-        <v>5615101</v>
+        <v>1131068</v>
       </c>
       <c r="F877" s="4" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="G877" s="4" t="s">
-        <v>36</v>
+        <v>3447</v>
       </c>
       <c r="H877" s="4" t="s">
-        <v>3411</v>
+        <v>3448</v>
       </c>
       <c r="I877" s="4" t="s">
-        <v>3412</v>
+        <v>3448</v>
       </c>
       <c r="J877" s="4" t="s">
-        <v>3447</v>
+        <v>411</v>
       </c>
       <c r="K877" s="4"/>
       <c r="L877" s="4" t="s">
-        <v>617</v>
+        <v>105</v>
       </c>
       <c r="M877" s="4" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="N877" s="4">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="O877" s="4" t="s">
-        <v>3451</v>
+        <v>3453</v>
       </c>
       <c r="P877" s="5"/>
       <c r="Q877" s="4" t="s">
-        <v>3452</v>
+        <v>3454</v>
       </c>
       <c r="R877" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="S877" s="4">
-        <v>0</v>
+        <v>40673.87</v>
       </c>
       <c r="T877" s="4">
-        <v>0</v>
-      </c>
-      <c r="U877" s="4"/>
-      <c r="V877" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="U877" s="4" t="s">
+        <v>3455</v>
+      </c>
+      <c r="V877" s="4" t="s">
+        <v>217</v>
+      </c>
       <c r="W877" s="4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X877" s="4" t="s">
         <v>46</v>
       </c>
       <c r="Y877" s="4"/>
       <c r="Z877" s="4" t="s">
-        <v>3453</v>
+        <v>3456</v>
       </c>
       <c r="AA877" s="4" t="s">
         <v>79</v>
       </c>
       <c r="AB877" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="878" spans="1:28">
-      <c r="A878" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B878" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C878" s="4">
-        <v>167227156</v>
-      </c>
-      <c r="D878" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E878" s="4">
-        <v>1130632</v>
-      </c>
-      <c r="F878" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G878" s="4" t="s">
-        <v>3454</v>
-      </c>
-      <c r="H878" s="4" t="s">
-        <v>3455</v>
-      </c>
-      <c r="I878" s="4" t="s">
-        <v>3455</v>
-      </c>
-      <c r="J878" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="K878" s="4"/>
-      <c r="L878" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="M878" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="N878" s="4">
-        <v>49</v>
-      </c>
-      <c r="O878" s="4" t="s">
-        <v>3456</v>
-      </c>
-      <c r="P878" s="5"/>
-      <c r="Q878" s="4" t="s">
-        <v>3457</v>
-      </c>
-      <c r="R878" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="S878" s="4">
-        <v>0</v>
-      </c>
-      <c r="T878" s="4">
-        <v>0</v>
-      </c>
-      <c r="U878" s="4" t="s">
-        <v>3458</v>
-      </c>
-      <c r="V878" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="W878" s="4">
-        <v>38</v>
-      </c>
-      <c r="X878" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y878" s="4"/>
-      <c r="Z878" s="4" t="s">
-        <v>3459</v>
-      </c>
-      <c r="AA878" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB878" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="879" spans="1:28">
-      <c r="A879" s="4">
-        <v>1000</v>
-      </c>
-      <c r="B879" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C879" s="4">
-        <v>168526053</v>
-      </c>
-      <c r="D879" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E879" s="4">
-        <v>1131068</v>
-      </c>
-      <c r="F879" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G879" s="4" t="s">
-        <v>3454</v>
-      </c>
-      <c r="H879" s="4" t="s">
-        <v>3455</v>
-      </c>
-      <c r="I879" s="4" t="s">
-        <v>3455</v>
-      </c>
-      <c r="J879" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="K879" s="4"/>
-      <c r="L879" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="M879" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="N879" s="4">
-        <v>5</v>
-      </c>
-      <c r="O879" s="4" t="s">
-        <v>3460</v>
-      </c>
-      <c r="P879" s="5"/>
-      <c r="Q879" s="4" t="s">
-        <v>3461</v>
-      </c>
-      <c r="R879" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="S879" s="4">
-        <v>40673.87</v>
-      </c>
-      <c r="T879" s="4">
-        <v>1</v>
-      </c>
-      <c r="U879" s="4" t="s">
-        <v>3462</v>
-      </c>
-      <c r="V879" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="W879" s="4">
-        <v>24</v>
-      </c>
-      <c r="X879" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y879" s="4"/>
-      <c r="Z879" s="4" t="s">
-        <v>3463</v>
-      </c>
-      <c r="AA879" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB879" s="4" t="s">
         <v>61</v>
       </c>
     </row>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>30/10/2026 a las 07:31:14</t>
+    <t>30/10/2026 a las 07:33:08</t>
   </si>
   <si>
     <t>Num_Lote</t>

--- a/siprem_latest.xlsx
+++ b/siprem_latest.xlsx
@@ -29,7 +29,7 @@
     <t>FECHA</t>
   </si>
   <si>
-    <t>31/10/2026 a las 08:31:00</t>
+    <t>31/10/2026 a las 08:32:14</t>
   </si>
   <si>
     <t>Num_Lote</t>
